--- a/marker_summary/results/Literature_31_marker_summary_statistics_public.xlsx
+++ b/marker_summary/results/Literature_31_marker_summary_statistics_public.xlsx
@@ -850,7 +850,7 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>H-new1 Fawkner Visium (GSE158328) [Human]</t>
+          <t>H-new1 Fawkner Visium (GSE158328) [DROPPED: QC record] [Human]</t>
         </is>
       </c>
       <c r="AK2" s="3" t="n"/>
@@ -864,7 +864,7 @@
       <c r="AO2" s="3" t="n"/>
       <c r="AP2" s="5" t="inlineStr">
         <is>
-          <t>H-new2 Fawkner fetal + Burclaff adult [Human]</t>
+          <t>H-new2 Fawkner fetal + Burclaff adult [HUMAN PRIMARY, cross-study] [Human]</t>
         </is>
       </c>
       <c r="AQ2" s="3" t="n"/>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="K1" s="12" t="inlineStr">
         <is>
-          <t>S2 (benchmark v2) | H-new1 Fawkner Visium (GSE158328)</t>
+          <t>S2 (benchmark v2) | H-new1 Fawkner Visium (GSE158328) [DROPPED: QC record]</t>
         </is>
       </c>
       <c r="L1" s="12" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="M1" s="12" t="inlineStr">
         <is>
-          <t>S2 (benchmark v2) | H-new2 Fawkner fetal + Burclaff adult</t>
+          <t>S2 (benchmark v2) | H-new2 Fawkner fetal + Burclaff adult [HUMAN PRIMARY, cross-study]</t>
         </is>
       </c>
       <c r="N1" s="12" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="L1" s="12" t="inlineStr">
         <is>
-          <t>S2 (benchmark v2) | H-new1 Fawkner Visium (GSE158328)</t>
+          <t>S2 (benchmark v2) | H-new1 Fawkner Visium (GSE158328) [DROPPED: QC record]</t>
         </is>
       </c>
       <c r="M1" s="12" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="N1" s="12" t="inlineStr">
         <is>
-          <t>S2 (benchmark v2) | H-new2 Fawkner fetal + Burclaff adult</t>
+          <t>S2 (benchmark v2) | H-new2 Fawkner fetal + Burclaff adult [HUMAN PRIMARY, cross-study]</t>
         </is>
       </c>
       <c r="O1" s="12" t="inlineStr">
@@ -12756,7 +12756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -12793,47 +12793,54 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Benchmark v2 (purple headers): H-new1 Visium (adult n = 2 sections; fetal spots less epithelial), H-new2 (study confounded with stage), H-new3 and Gao-original recomputed (cross-platform, effect-only; Welch P descriptive). See step2_benchmark_v2/docs.</t>
+          <t>Review 2026-10-02: H-new2 is the human primary developmental contrast (cross-study; needs independent validation). H-new1 Visium is dropped from quantitative Step 2 and shown only as a failed QC record.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Step 2 primary datasets (HGCA, Gao, GSE230581) belong to an INVALIDATED analysis (failed biological QA); values are reported for audit, not as evidence.</t>
+          <t>Benchmark v2 (purple headers): H-new1 Visium (adult n = 2 sections; fetal spots less epithelial), H-new2 (study confounded with stage), H-new3 and Gao-original recomputed (cross-platform, effect-only; Welch P descriptive). See step2_benchmark_v2/docs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Symbols: CCN1/CCN2 are looked up as CYR61/CTGF in annotations that predate the HGNC rename (HGCA, Gao, Senger, Fawkner, TCGA/GENCODE v26, Pelka, Joanito).</t>
+          <t>Step 2 primary datasets (HGCA, Gao, GSE230581) belong to an INVALIDATED analysis (failed biological QA); values are reported for audit, not as evidence.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Mouse: Ensembl 116 one2one orthologues; LY6A/REG3B use the mouse-defined genes Ly6a/Reg3b; CXADR uses high-confidence Cxadr (one2many). Benchmarks map by one2one Entrez only, so these are blank there.</t>
+          <t>Symbols: CCN1/CCN2 are looked up as CYR61/CTGF in annotations that predate the HGNC rename (HGCA, Gao, Senger, Fawkner, TCGA/GENCODE v26, Pelka, Joanito).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>TCGA paired: 50 patients with tumour and normal; TCGA vs GTEx: source fully confounded, direction only.</t>
+          <t>Mouse: Ensembl 116 one2one orthologues; LY6A/REG3B use the mouse-defined genes Ly6a/Reg3b; CXADR uses high-confidence Cxadr (one2many). Benchmarks map by one2one Entrez only, so these are blank there.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Public version: Joanito (Synapse syn26844071) columns and the Joanito-derived Step 3 final label are omitted under its data-use terms.</t>
+          <t>TCGA paired: 50 patients with tumour and normal; TCGA vs GTEx: source fully confounded, direction only.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Public version: Joanito (Synapse syn26844071) columns and the Joanito-derived Step 3 final label are omitted under its data-use terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Regenerate: python3 marker_summary/scripts/build_marker_summary.py</t>
         </is>

--- a/marker_summary/results/Literature_31_marker_summary_statistics_public.xlsx
+++ b/marker_summary/results/Literature_31_marker_summary_statistics_public.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BV35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -585,9 +585,15 @@
     <col width="11" customWidth="1" min="63" max="63"/>
     <col width="11" customWidth="1" min="64" max="64"/>
     <col width="11" customWidth="1" min="65" max="65"/>
-    <col width="22" customWidth="1" min="66" max="66"/>
-    <col width="22" customWidth="1" min="67" max="67"/>
-    <col width="22" customWidth="1" min="68" max="68"/>
+    <col width="11" customWidth="1" min="66" max="66"/>
+    <col width="11" customWidth="1" min="67" max="67"/>
+    <col width="11" customWidth="1" min="68" max="68"/>
+    <col width="11" customWidth="1" min="69" max="69"/>
+    <col width="11" customWidth="1" min="70" max="70"/>
+    <col width="11" customWidth="1" min="71" max="71"/>
+    <col width="22" customWidth="1" min="72" max="72"/>
+    <col width="22" customWidth="1" min="73" max="73"/>
+    <col width="22" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,16 +727,16 @@
       </c>
       <c r="AW1" s="3" t="n"/>
       <c r="AX1" s="3" t="n"/>
-      <c r="AY1" s="6" t="inlineStr">
-        <is>
-          <t>Step 3</t>
+      <c r="AY1" s="5" t="inlineStr">
+        <is>
+          <t>Step 2 (benchmark v2)</t>
         </is>
       </c>
       <c r="AZ1" s="3" t="n"/>
       <c r="BA1" s="3" t="n"/>
-      <c r="BB1" s="6" t="inlineStr">
-        <is>
-          <t>Step 3</t>
+      <c r="BB1" s="5" t="inlineStr">
+        <is>
+          <t>Step 2 (benchmark v2)</t>
         </is>
       </c>
       <c r="BC1" s="3" t="n"/>
@@ -756,17 +762,31 @@
       </c>
       <c r="BL1" s="3" t="n"/>
       <c r="BM1" s="3" t="n"/>
-      <c r="BN1" s="7" t="inlineStr">
+      <c r="BN1" s="6" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="BO1" s="3" t="n"/>
+      <c r="BP1" s="3" t="n"/>
+      <c r="BQ1" s="6" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="BR1" s="3" t="n"/>
+      <c r="BS1" s="3" t="n"/>
+      <c r="BT1" s="7" t="inlineStr">
         <is>
           <t>Step2_final_(invalidated)</t>
         </is>
       </c>
-      <c r="BO1" s="7" t="inlineStr">
+      <c r="BU1" s="7" t="inlineStr">
         <is>
           <t>Step2_first_failed_gate</t>
         </is>
       </c>
-      <c r="BP1" s="7" t="inlineStr">
+      <c r="BV1" s="7" t="inlineStr">
         <is>
           <t>Step3_bulk_support</t>
         </is>
@@ -871,56 +891,70 @@
       <c r="AR2" s="3" t="n"/>
       <c r="AS2" s="5" t="inlineStr">
         <is>
-          <t>H-new3 Gao fetal + Wang adult [Human]</t>
+          <t>H-bulk1 Roadmap fetal SI vs HPA adult SI [tier B] [Human]</t>
         </is>
       </c>
       <c r="AT2" s="3" t="n"/>
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="5" t="inlineStr">
         <is>
-          <t>H-new3-debug [Human]</t>
+          <t>H-bulk2 Roadmap fetal SI vs HPA duodenum [tier B subset] [Human]</t>
         </is>
       </c>
       <c r="AW2" s="3" t="n"/>
       <c r="AX2" s="3" t="n"/>
-      <c r="AY2" s="6" t="inlineStr">
-        <is>
-          <t>TCGA COAD+READ (T1) [Human]</t>
+      <c r="AY2" s="5" t="inlineStr">
+        <is>
+          <t>H-new3 Gao fetal + Wang adult [Human]</t>
         </is>
       </c>
       <c r="AZ2" s="3" t="n"/>
       <c r="BA2" s="3" t="n"/>
-      <c r="BB2" s="6" t="inlineStr">
-        <is>
-          <t>TCGA paired [Human]</t>
+      <c r="BB2" s="5" t="inlineStr">
+        <is>
+          <t>H-new3-debug [Human]</t>
         </is>
       </c>
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="3" t="n"/>
       <c r="BE2" s="6" t="inlineStr">
         <is>
-          <t>TCGA vs GTEx [Human]</t>
+          <t>TCGA COAD+READ (T1) [Human]</t>
         </is>
       </c>
       <c r="BF2" s="3" t="n"/>
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="6" t="inlineStr">
         <is>
-          <t>Pelka 2021 (S2, GSE178341) [Human]</t>
+          <t>TCGA paired [Human]</t>
         </is>
       </c>
       <c r="BI2" s="3" t="n"/>
       <c r="BJ2" s="3" t="n"/>
       <c r="BK2" s="6" t="inlineStr">
         <is>
-          <t>Pelka progenitor check (P) [Human]</t>
+          <t>TCGA vs GTEx [Human]</t>
         </is>
       </c>
       <c r="BL2" s="3" t="n"/>
       <c r="BM2" s="3" t="n"/>
-      <c r="BN2" s="3" t="n"/>
+      <c r="BN2" s="6" t="inlineStr">
+        <is>
+          <t>Pelka 2021 (S2, GSE178341) [Human]</t>
+        </is>
+      </c>
       <c r="BO2" s="3" t="n"/>
       <c r="BP2" s="3" t="n"/>
+      <c r="BQ2" s="6" t="inlineStr">
+        <is>
+          <t>Pelka progenitor check (P) [Human]</t>
+        </is>
+      </c>
+      <c r="BR2" s="3" t="n"/>
+      <c r="BS2" s="3" t="n"/>
+      <c r="BT2" s="3" t="n"/>
+      <c r="BU2" s="3" t="n"/>
+      <c r="BV2" s="3" t="n"/>
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="3" t="n"/>
@@ -1021,56 +1055,70 @@
       <c r="AR3" s="3" t="n"/>
       <c r="AS3" s="5" t="inlineStr">
         <is>
-          <t>Gao fetal SI+LI vs Wang ileum/colon/rectum, effect-only (GSE95630 / GSE125970); + = fetal-high</t>
+          <t>primary-tissue bulk, recount3 counts, edgeR (Finkbeiner 2015 design); + = fetal-high</t>
         </is>
       </c>
       <c r="AT3" s="3" t="n"/>
       <c r="AU3" s="3" t="n"/>
       <c r="AV3" s="5" t="inlineStr">
         <is>
-          <t>Gao fetal LI vs Wang colon+rectum (adult arm swapped); + = fetal-high</t>
+          <t>duodenum-only subset of H-bulk1 (Senger 2018 primary-tissue comparison); + = fetal-high</t>
         </is>
       </c>
       <c r="AW3" s="3" t="n"/>
       <c r="AX3" s="3" t="n"/>
-      <c r="AY3" s="6" t="inlineStr">
-        <is>
-          <t>primary tumour vs normal, ~ tissue + project; + = tumour-high</t>
+      <c r="AY3" s="5" t="inlineStr">
+        <is>
+          <t>Gao fetal SI+LI vs Wang ileum/colon/rectum, effect-only (GSE95630 / GSE125970); + = fetal-high</t>
         </is>
       </c>
       <c r="AZ3" s="3" t="n"/>
       <c r="BA3" s="3" t="n"/>
-      <c r="BB3" s="6" t="inlineStr">
-        <is>
-          <t>tumour vs matched normal (50 pairs); + = tumour-high</t>
+      <c r="BB3" s="5" t="inlineStr">
+        <is>
+          <t>Gao fetal LI vs Wang colon+rectum (adult arm swapped); + = fetal-high</t>
         </is>
       </c>
       <c r="BC3" s="3" t="n"/>
       <c r="BD3" s="3" t="n"/>
       <c r="BE3" s="6" t="inlineStr">
         <is>
-          <t>TCGA tumour vs GTEx transverse colon (direction only); + = tumour-high</t>
+          <t>primary tumour vs normal, ~ tissue + project; + = tumour-high</t>
         </is>
       </c>
       <c r="BF3" s="3" t="n"/>
       <c r="BG3" s="3" t="n"/>
       <c r="BH3" s="6" t="inlineStr">
         <is>
-          <t>tumour vs normal epithelium; + = tumour-high</t>
+          <t>tumour vs matched normal (50 pairs); + = tumour-high</t>
         </is>
       </c>
       <c r="BI3" s="3" t="n"/>
       <c r="BJ3" s="3" t="n"/>
       <c r="BK3" s="6" t="inlineStr">
         <is>
-          <t>tumour epithelium vs normal stem/TA (cE01-03); + = tumour-high</t>
+          <t>TCGA tumour vs GTEx transverse colon (direction only); + = tumour-high</t>
         </is>
       </c>
       <c r="BL3" s="3" t="n"/>
       <c r="BM3" s="3" t="n"/>
-      <c r="BN3" s="3" t="n"/>
+      <c r="BN3" s="6" t="inlineStr">
+        <is>
+          <t>tumour vs normal epithelium; + = tumour-high</t>
+        </is>
+      </c>
       <c r="BO3" s="3" t="n"/>
       <c r="BP3" s="3" t="n"/>
+      <c r="BQ3" s="6" t="inlineStr">
+        <is>
+          <t>tumour epithelium vs normal stem/TA (cE01-03); + = tumour-high</t>
+        </is>
+      </c>
+      <c r="BR3" s="3" t="n"/>
+      <c r="BS3" s="3" t="n"/>
+      <c r="BT3" s="3" t="n"/>
+      <c r="BU3" s="3" t="n"/>
+      <c r="BV3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -1378,9 +1426,39 @@
           <t>FDR</t>
         </is>
       </c>
-      <c r="BN4" s="3" t="n"/>
-      <c r="BO4" s="3" t="n"/>
-      <c r="BP4" s="3" t="n"/>
+      <c r="BN4" s="8" t="inlineStr">
+        <is>
+          <t>log2FC</t>
+        </is>
+      </c>
+      <c r="BO4" s="8" t="inlineStr">
+        <is>
+          <t>P value</t>
+        </is>
+      </c>
+      <c r="BP4" s="8" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="BQ4" s="8" t="inlineStr">
+        <is>
+          <t>log2FC</t>
+        </is>
+      </c>
+      <c r="BR4" s="8" t="inlineStr">
+        <is>
+          <t>P value</t>
+        </is>
+      </c>
+      <c r="BS4" s="8" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="BT4" s="3" t="n"/>
+      <c r="BU4" s="3" t="n"/>
+      <c r="BV4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1502,73 +1580,91 @@
         <v>2.08472063506422e-05</v>
       </c>
       <c r="AS5" s="10" t="n">
+        <v>2.49150763377401</v>
+      </c>
+      <c r="AT5" s="11" t="n">
+        <v>0.000145012637322</v>
+      </c>
+      <c r="AU5" s="11" t="n">
+        <v>0.0005239185172331001</v>
+      </c>
+      <c r="AV5" s="10" t="n">
+        <v>2.38341298830727</v>
+      </c>
+      <c r="AW5" s="11" t="n">
+        <v>0.0263370208929352</v>
+      </c>
+      <c r="AX5" s="11" t="n">
+        <v>0.0528977373496142</v>
+      </c>
+      <c r="AY5" s="10" t="n">
         <v>1.809666668472633</v>
       </c>
-      <c r="AT5" s="11" t="n">
+      <c r="AZ5" s="11" t="n">
         <v>0.0060782038211724</v>
       </c>
-      <c r="AU5" s="11" t="n">
+      <c r="BA5" s="11" t="n">
         <v>0.0105107227311799</v>
       </c>
-      <c r="AV5" s="10" t="n">
+      <c r="BB5" s="10" t="n">
         <v>1.225924077307709</v>
       </c>
-      <c r="AW5" s="11" t="n">
+      <c r="BC5" s="11" t="n">
         <v>0.068100693950154</v>
       </c>
-      <c r="AX5" s="11" t="n">
+      <c r="BD5" s="11" t="n">
         <v>0.1016297479265519</v>
       </c>
-      <c r="AY5" s="10" t="n">
+      <c r="BE5" s="10" t="n">
         <v>5.05028632487126</v>
       </c>
-      <c r="AZ5" s="11" t="n">
+      <c r="BF5" s="11" t="n">
         <v>5.475203508004971e-25</v>
       </c>
-      <c r="BA5" s="11" t="n">
+      <c r="BG5" s="11" t="n">
         <v>3.99218920044355e-24</v>
       </c>
-      <c r="BB5" s="10" t="n">
+      <c r="BH5" s="10" t="n">
         <v>3.73497284492898</v>
       </c>
-      <c r="BC5" s="9" t="n"/>
-      <c r="BD5" s="11" t="n">
+      <c r="BI5" s="9" t="n"/>
+      <c r="BJ5" s="11" t="n">
         <v>2.21079248401646e-11</v>
       </c>
-      <c r="BE5" s="10" t="n">
+      <c r="BK5" s="10" t="n">
         <v>4.69300181571387</v>
       </c>
-      <c r="BF5" s="9" t="n"/>
-      <c r="BG5" s="11" t="n">
+      <c r="BL5" s="9" t="n"/>
+      <c r="BM5" s="11" t="n">
         <v>2.01876716899463e-167</v>
       </c>
-      <c r="BH5" s="10" t="n">
+      <c r="BN5" s="10" t="n">
         <v>4.25904379124654</v>
       </c>
-      <c r="BI5" s="11" t="n">
+      <c r="BO5" s="11" t="n">
         <v>7.182211571553239e-12</v>
       </c>
-      <c r="BJ5" s="11" t="n">
+      <c r="BP5" s="11" t="n">
         <v>3.76963504484094e-11</v>
       </c>
-      <c r="BK5" s="10" t="n">
+      <c r="BQ5" s="10" t="n">
         <v>6.05919277196155</v>
       </c>
-      <c r="BL5" s="11" t="n">
+      <c r="BR5" s="11" t="n">
         <v>1.16264903658604e-17</v>
       </c>
-      <c r="BM5" s="11" t="n">
+      <c r="BS5" s="11" t="n">
         <v>3.99566507033922e-16</v>
       </c>
-      <c r="BN5" s="9" t="b">
+      <c r="BT5" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO5" s="9" t="inlineStr">
+      <c r="BU5" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP5" s="9" t="b">
+      <c r="BV5" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1704,61 +1800,79 @@
         <v>0.0097236309386209</v>
       </c>
       <c r="AS6" s="10" t="n">
+        <v>0.551810476317118</v>
+      </c>
+      <c r="AT6" s="11" t="n">
+        <v>0.180446635405104</v>
+      </c>
+      <c r="AU6" s="11" t="n">
+        <v>0.236938620954523</v>
+      </c>
+      <c r="AV6" s="10" t="n">
+        <v>0.582171411052016</v>
+      </c>
+      <c r="AW6" s="11" t="n">
+        <v>0.418332224100744</v>
+      </c>
+      <c r="AX6" s="11" t="n">
+        <v>0.5015306333094109</v>
+      </c>
+      <c r="AY6" s="10" t="n">
         <v>4.649560425991364</v>
       </c>
-      <c r="AT6" s="11" t="n">
+      <c r="AZ6" s="11" t="n">
         <v>2.296370838842607e-11</v>
       </c>
-      <c r="AU6" s="11" t="n">
+      <c r="BA6" s="11" t="n">
         <v>1.175210233794821e-09</v>
       </c>
-      <c r="AV6" s="10" t="n">
+      <c r="BB6" s="10" t="n">
         <v>3.542088757094501</v>
       </c>
-      <c r="AW6" s="11" t="n">
+      <c r="BC6" s="11" t="n">
         <v>6.177079893091584e-05</v>
       </c>
-      <c r="AX6" s="11" t="n">
+      <c r="BD6" s="11" t="n">
         <v>0.000290291696011</v>
       </c>
-      <c r="AY6" s="10" t="n">
+      <c r="BE6" s="10" t="n">
         <v>-0.0025247870000847</v>
       </c>
-      <c r="AZ6" s="11" t="n">
+      <c r="BF6" s="11" t="n">
         <v>0.98611755278992</v>
       </c>
-      <c r="BA6" s="11" t="n">
+      <c r="BG6" s="11" t="n">
         <v>0.98730775501906</v>
       </c>
-      <c r="BB6" s="10" t="n">
+      <c r="BH6" s="10" t="n">
         <v>-0.222650205328684</v>
       </c>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="11" t="n">
+      <c r="BI6" s="9" t="n"/>
+      <c r="BJ6" s="11" t="n">
         <v>0.151845230271159</v>
       </c>
-      <c r="BE6" s="10" t="n">
+      <c r="BK6" s="10" t="n">
         <v>-0.433294511714691</v>
       </c>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="11" t="n">
+      <c r="BL6" s="9" t="n"/>
+      <c r="BM6" s="11" t="n">
         <v>5.3412885963428e-12</v>
       </c>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="9" t="n"/>
-      <c r="BK6" s="9" t="n"/>
-      <c r="BL6" s="9" t="n"/>
-      <c r="BM6" s="9" t="n"/>
-      <c r="BN6" s="9" t="b">
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="9" t="n"/>
+      <c r="BQ6" s="9" t="n"/>
+      <c r="BR6" s="9" t="n"/>
+      <c r="BS6" s="9" t="n"/>
+      <c r="BT6" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="BO6" s="9" t="inlineStr">
+      <c r="BU6" s="9" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="BP6" s="9" t="b">
+      <c r="BV6" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1894,73 +2008,91 @@
         <v>0.217171984084308</v>
       </c>
       <c r="AS7" s="10" t="n">
+        <v>-2.66331617979916</v>
+      </c>
+      <c r="AT7" s="11" t="n">
+        <v>1.94672400444821e-08</v>
+      </c>
+      <c r="AU7" s="11" t="n">
+        <v>9.22716184736483e-07</v>
+      </c>
+      <c r="AV7" s="10" t="n">
+        <v>-2.42300499114636</v>
+      </c>
+      <c r="AW7" s="11" t="n">
+        <v>6.61797889279638e-06</v>
+      </c>
+      <c r="AX7" s="11" t="n">
+        <v>0.0002438156609907</v>
+      </c>
+      <c r="AY7" s="10" t="n">
         <v>2.822503672938254</v>
       </c>
-      <c r="AT7" s="11" t="n">
+      <c r="AZ7" s="11" t="n">
         <v>3.470641955525805e-05</v>
       </c>
-      <c r="AU7" s="11" t="n">
+      <c r="BA7" s="11" t="n">
         <v>0.0001135198055161</v>
       </c>
-      <c r="AV7" s="10" t="n">
+      <c r="BB7" s="10" t="n">
         <v>2.831192780929209</v>
       </c>
-      <c r="AW7" s="11" t="n">
+      <c r="BC7" s="11" t="n">
         <v>0.0014638331768107</v>
       </c>
-      <c r="AX7" s="11" t="n">
+      <c r="BD7" s="11" t="n">
         <v>0.0038242100207738</v>
       </c>
-      <c r="AY7" s="10" t="n">
+      <c r="BE7" s="10" t="n">
         <v>0.208594387468698</v>
       </c>
-      <c r="AZ7" s="11" t="n">
+      <c r="BF7" s="11" t="n">
         <v>0.255907709246128</v>
       </c>
-      <c r="BA7" s="11" t="n">
+      <c r="BG7" s="11" t="n">
         <v>0.288255163208507</v>
       </c>
-      <c r="BB7" s="10" t="n">
+      <c r="BH7" s="10" t="n">
         <v>-0.246222685380311</v>
       </c>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="11" t="n">
+      <c r="BI7" s="9" t="n"/>
+      <c r="BJ7" s="11" t="n">
         <v>0.154816687052447</v>
       </c>
-      <c r="BE7" s="10" t="n">
+      <c r="BK7" s="10" t="n">
         <v>-0.643732616070441</v>
       </c>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="11" t="n">
+      <c r="BL7" s="9" t="n"/>
+      <c r="BM7" s="11" t="n">
         <v>1.07492828195462e-17</v>
       </c>
-      <c r="BH7" s="10" t="n">
+      <c r="BN7" s="10" t="n">
         <v>2.84220968978987</v>
       </c>
-      <c r="BI7" s="11" t="n">
+      <c r="BO7" s="11" t="n">
         <v>1.17188992894437e-12</v>
       </c>
-      <c r="BJ7" s="11" t="n">
+      <c r="BP7" s="11" t="n">
         <v>6.82874480403112e-12</v>
       </c>
-      <c r="BK7" s="10" t="n">
+      <c r="BQ7" s="10" t="n">
         <v>4.55185303250578</v>
       </c>
-      <c r="BL7" s="11" t="n">
+      <c r="BR7" s="11" t="n">
         <v>2.91721323965648e-22</v>
       </c>
-      <c r="BM7" s="11" t="n">
+      <c r="BS7" s="11" t="n">
         <v>2.41656548771775e-20</v>
       </c>
-      <c r="BN7" s="9" t="b">
+      <c r="BT7" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO7" s="9" t="inlineStr">
+      <c r="BU7" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP7" s="9" t="b">
+      <c r="BV7" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2096,73 +2228,91 @@
         <v>0.0001834916908938</v>
       </c>
       <c r="AS8" s="10" t="n">
+        <v>0.144071265340153</v>
+      </c>
+      <c r="AT8" s="11" t="n">
+        <v>0.6567572158253</v>
+      </c>
+      <c r="AU8" s="11" t="n">
+        <v>0.713034726216294</v>
+      </c>
+      <c r="AV8" s="10" t="n">
+        <v>0.0263466855177204</v>
+      </c>
+      <c r="AW8" s="11" t="n">
+        <v>0.957905345329477</v>
+      </c>
+      <c r="AX8" s="11" t="n">
+        <v>0.968355817462175</v>
+      </c>
+      <c r="AY8" s="10" t="n">
         <v>4.728578253609251</v>
       </c>
-      <c r="AT8" s="11" t="n">
+      <c r="AZ8" s="11" t="n">
         <v>4.456781594047944e-05</v>
       </c>
-      <c r="AU8" s="11" t="n">
+      <c r="BA8" s="11" t="n">
         <v>0.0001406865050592</v>
       </c>
-      <c r="AV8" s="10" t="n">
+      <c r="BB8" s="10" t="n">
         <v>4.036794130783478</v>
       </c>
-      <c r="AW8" s="11" t="n">
+      <c r="BC8" s="11" t="n">
         <v>4.451762678103928e-08</v>
       </c>
-      <c r="AX8" s="11" t="n">
+      <c r="BD8" s="11" t="n">
         <v>1.196027843680776e-06</v>
       </c>
-      <c r="AY8" s="10" t="n">
+      <c r="BE8" s="10" t="n">
         <v>-2.31154743014523</v>
       </c>
-      <c r="AZ8" s="11" t="n">
+      <c r="BF8" s="11" t="n">
         <v>6.76752711472934e-38</v>
       </c>
-      <c r="BA8" s="11" t="n">
+      <c r="BG8" s="11" t="n">
         <v>1.00194926374712e-36</v>
       </c>
-      <c r="BB8" s="10" t="n">
+      <c r="BH8" s="10" t="n">
         <v>-2.65163850649463</v>
       </c>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="11" t="n">
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="11" t="n">
         <v>5.5825482944821e-16</v>
       </c>
-      <c r="BE8" s="10" t="n">
+      <c r="BK8" s="10" t="n">
         <v>-2.77393099960309</v>
       </c>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="11" t="n">
+      <c r="BL8" s="9" t="n"/>
+      <c r="BM8" s="11" t="n">
         <v>5.18098494684006e-151</v>
       </c>
-      <c r="BH8" s="10" t="n">
+      <c r="BN8" s="10" t="n">
         <v>1.49510505291086</v>
       </c>
-      <c r="BI8" s="11" t="n">
+      <c r="BO8" s="11" t="n">
         <v>1.96773871980725e-06</v>
       </c>
-      <c r="BJ8" s="11" t="n">
+      <c r="BP8" s="11" t="n">
         <v>4.95593628556767e-06</v>
       </c>
-      <c r="BK8" s="10" t="n">
+      <c r="BQ8" s="10" t="n">
         <v>1.48820795285742</v>
       </c>
-      <c r="BL8" s="11" t="n">
+      <c r="BR8" s="11" t="n">
         <v>2.9929607006367e-06</v>
       </c>
-      <c r="BM8" s="11" t="n">
+      <c r="BS8" s="11" t="n">
         <v>1.03056510814091e-05</v>
       </c>
-      <c r="BN8" s="9" t="b">
+      <c r="BT8" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="BO8" s="9" t="inlineStr">
+      <c r="BU8" s="9" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="BP8" s="9" t="b">
+      <c r="BV8" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2298,73 +2448,91 @@
         <v>0.0050187777015285</v>
       </c>
       <c r="AS9" s="10" t="n">
+        <v>2.10328940421391</v>
+      </c>
+      <c r="AT9" s="11" t="n">
+        <v>6.54458462987261e-07</v>
+      </c>
+      <c r="AU9" s="11" t="n">
+        <v>1.02614218232766e-05</v>
+      </c>
+      <c r="AV9" s="10" t="n">
+        <v>1.85976014712011</v>
+      </c>
+      <c r="AW9" s="11" t="n">
+        <v>0.0006349981175575999</v>
+      </c>
+      <c r="AX9" s="11" t="n">
+        <v>0.0046907712104861</v>
+      </c>
+      <c r="AY9" s="10" t="n">
         <v>1.274542365098686</v>
       </c>
-      <c r="AT9" s="11" t="n">
+      <c r="AZ9" s="11" t="n">
         <v>0.0018234706211649</v>
       </c>
-      <c r="AU9" s="11" t="n">
+      <c r="BA9" s="11" t="n">
         <v>0.0036151418044918</v>
       </c>
-      <c r="AV9" s="10" t="n">
+      <c r="BB9" s="10" t="n">
         <v>1.286101407764752</v>
       </c>
-      <c r="AW9" s="11" t="n">
+      <c r="BC9" s="11" t="n">
         <v>0.0046694466855431</v>
       </c>
-      <c r="AX9" s="11" t="n">
+      <c r="BD9" s="11" t="n">
         <v>0.0102391441328451</v>
       </c>
-      <c r="AY9" s="10" t="n">
+      <c r="BE9" s="10" t="n">
         <v>1.67776809443425</v>
       </c>
-      <c r="AZ9" s="11" t="n">
+      <c r="BF9" s="11" t="n">
         <v>2.17096833252776e-28</v>
       </c>
-      <c r="BA9" s="11" t="n">
+      <c r="BG9" s="11" t="n">
         <v>1.94937888731656e-27</v>
       </c>
-      <c r="BB9" s="10" t="n">
+      <c r="BH9" s="10" t="n">
         <v>1.35884211776825</v>
       </c>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="11" t="n">
+      <c r="BI9" s="9" t="n"/>
+      <c r="BJ9" s="11" t="n">
         <v>6.64233857783558e-10</v>
       </c>
-      <c r="BE9" s="10" t="n">
+      <c r="BK9" s="10" t="n">
         <v>1.93451996054779</v>
       </c>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="11" t="n">
+      <c r="BL9" s="9" t="n"/>
+      <c r="BM9" s="11" t="n">
         <v>5.53827226523876e-182</v>
       </c>
-      <c r="BH9" s="10" t="n">
+      <c r="BN9" s="10" t="n">
         <v>1.65228981386363</v>
       </c>
-      <c r="BI9" s="11" t="n">
+      <c r="BO9" s="11" t="n">
         <v>3.14204380887234e-18</v>
       </c>
-      <c r="BJ9" s="11" t="n">
+      <c r="BP9" s="11" t="n">
         <v>4.53590135709114e-17</v>
       </c>
-      <c r="BK9" s="10" t="n">
+      <c r="BQ9" s="10" t="n">
         <v>2.02638428887108</v>
       </c>
-      <c r="BL9" s="11" t="n">
+      <c r="BR9" s="11" t="n">
         <v>3.95123181281533e-24</v>
       </c>
-      <c r="BM9" s="11" t="n">
+      <c r="BS9" s="11" t="n">
         <v>4.96711430784706e-22</v>
       </c>
-      <c r="BN9" s="9" t="b">
+      <c r="BT9" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO9" s="9" t="inlineStr">
+      <c r="BU9" s="9" t="inlineStr">
         <is>
           <t>Mouse_M1</t>
         </is>
       </c>
-      <c r="BP9" s="9" t="b">
+      <c r="BV9" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2500,73 +2668,91 @@
         <v>0.0005208664004851</v>
       </c>
       <c r="AS10" s="10" t="n">
+        <v>-0.0250470388771509</v>
+      </c>
+      <c r="AT10" s="11" t="n">
+        <v>0.881534196752973</v>
+      </c>
+      <c r="AU10" s="11" t="n">
+        <v>0.90421085476408</v>
+      </c>
+      <c r="AV10" s="10" t="n">
+        <v>0.244118586704112</v>
+      </c>
+      <c r="AW10" s="11" t="n">
+        <v>0.299403064524162</v>
+      </c>
+      <c r="AX10" s="11" t="n">
+        <v>0.381278463503258</v>
+      </c>
+      <c r="AY10" s="10" t="n">
         <v>5.289242341489805</v>
       </c>
-      <c r="AT10" s="11" t="n">
+      <c r="AZ10" s="11" t="n">
         <v>1.242157568077835e-10</v>
       </c>
-      <c r="AU10" s="11" t="n">
+      <c r="BA10" s="11" t="n">
         <v>4.094040494988101e-09</v>
       </c>
-      <c r="AV10" s="10" t="n">
+      <c r="BB10" s="10" t="n">
         <v>5.606537428292589</v>
       </c>
-      <c r="AW10" s="11" t="n">
+      <c r="BC10" s="11" t="n">
         <v>1.159851798099134e-08</v>
       </c>
-      <c r="AX10" s="11" t="n">
+      <c r="BD10" s="11" t="n">
         <v>4.718465028346608e-07</v>
       </c>
-      <c r="AY10" s="10" t="n">
+      <c r="BE10" s="10" t="n">
         <v>-0.332774350351039</v>
       </c>
-      <c r="AZ10" s="11" t="n">
+      <c r="BF10" s="11" t="n">
         <v>0.004030261670043</v>
       </c>
-      <c r="BA10" s="11" t="n">
+      <c r="BG10" s="11" t="n">
         <v>0.0056108149534475</v>
       </c>
-      <c r="BB10" s="10" t="n">
+      <c r="BH10" s="10" t="n">
         <v>-0.287899078091318</v>
       </c>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="11" t="n">
+      <c r="BI10" s="9" t="n"/>
+      <c r="BJ10" s="11" t="n">
         <v>0.0630958634561159</v>
       </c>
-      <c r="BE10" s="10" t="n">
+      <c r="BK10" s="10" t="n">
         <v>-0.870991369969248</v>
       </c>
-      <c r="BF10" s="9" t="n"/>
-      <c r="BG10" s="11" t="n">
+      <c r="BL10" s="9" t="n"/>
+      <c r="BM10" s="11" t="n">
         <v>1.96360039927566e-53</v>
       </c>
-      <c r="BH10" s="10" t="n">
+      <c r="BN10" s="10" t="n">
         <v>2.95811168926125</v>
       </c>
-      <c r="BI10" s="11" t="n">
+      <c r="BO10" s="11" t="n">
         <v>9.498025206415731e-15</v>
       </c>
-      <c r="BJ10" s="11" t="n">
+      <c r="BP10" s="11" t="n">
         <v>7.4843420071574e-14</v>
       </c>
-      <c r="BK10" s="10" t="n">
+      <c r="BQ10" s="10" t="n">
         <v>3.09931636991049</v>
       </c>
-      <c r="BL10" s="11" t="n">
+      <c r="BR10" s="11" t="n">
         <v>5.8326135795105e-14</v>
       </c>
-      <c r="BM10" s="11" t="n">
+      <c r="BS10" s="11" t="n">
         <v>8.90172366432001e-13</v>
       </c>
-      <c r="BN10" s="9" t="b">
+      <c r="BT10" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="BO10" s="9" t="inlineStr">
+      <c r="BU10" s="9" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="BP10" s="9" t="b">
+      <c r="BV10" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2653,12 +2839,18 @@
       <c r="BL11" s="9" t="n"/>
       <c r="BM11" s="9" t="n"/>
       <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="inlineStr">
+      <c r="BO11" s="9" t="n"/>
+      <c r="BP11" s="9" t="n"/>
+      <c r="BQ11" s="9" t="n"/>
+      <c r="BR11" s="9" t="n"/>
+      <c r="BS11" s="9" t="n"/>
+      <c r="BT11" s="9" t="n"/>
+      <c r="BU11" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP11" s="9" t="n"/>
+      <c r="BV11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -2791,62 +2983,80 @@
       <c r="AR12" s="11" t="n">
         <v>0.0014339534699905</v>
       </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="9" t="n"/>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="9" t="n"/>
-      <c r="AY12" s="10" t="n">
+      <c r="AS12" s="10" t="n">
+        <v>0.309396815473826</v>
+      </c>
+      <c r="AT12" s="11" t="n">
+        <v>0.59062362856405</v>
+      </c>
+      <c r="AU12" s="11" t="n">
+        <v>0.652442137630096</v>
+      </c>
+      <c r="AV12" s="10" t="n">
+        <v>0.296063355092614</v>
+      </c>
+      <c r="AW12" s="11" t="n">
+        <v>0.745436750200087</v>
+      </c>
+      <c r="AX12" s="11" t="n">
+        <v>0.7989460994146</v>
+      </c>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="9" t="n"/>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="9" t="n"/>
+      <c r="BE12" s="10" t="n">
         <v>3.87915708772113</v>
       </c>
-      <c r="AZ12" s="11" t="n">
+      <c r="BF12" s="11" t="n">
         <v>1.30269848302403e-18</v>
       </c>
-      <c r="BA12" s="11" t="n">
+      <c r="BG12" s="11" t="n">
         <v>6.29239733091449e-18</v>
       </c>
-      <c r="BB12" s="10" t="n">
+      <c r="BH12" s="10" t="n">
         <v>3.31849537880916</v>
       </c>
-      <c r="BC12" s="9" t="n"/>
-      <c r="BD12" s="11" t="n">
+      <c r="BI12" s="9" t="n"/>
+      <c r="BJ12" s="11" t="n">
         <v>1.2530172240449e-09</v>
       </c>
-      <c r="BE12" s="10" t="n">
+      <c r="BK12" s="10" t="n">
         <v>2.96080985389408</v>
       </c>
-      <c r="BF12" s="9" t="n"/>
-      <c r="BG12" s="11" t="n">
+      <c r="BL12" s="9" t="n"/>
+      <c r="BM12" s="11" t="n">
         <v>1.26928993221417e-89</v>
       </c>
-      <c r="BH12" s="10" t="n">
+      <c r="BN12" s="10" t="n">
         <v>6.12870673194068</v>
       </c>
-      <c r="BI12" s="11" t="n">
+      <c r="BO12" s="11" t="n">
         <v>3.861565125239149e-18</v>
       </c>
-      <c r="BJ12" s="11" t="n">
+      <c r="BP12" s="11" t="n">
         <v>5.47771298197193e-17</v>
       </c>
-      <c r="BK12" s="10" t="n">
+      <c r="BQ12" s="10" t="n">
         <v>6.65778199848213</v>
       </c>
-      <c r="BL12" s="11" t="n">
+      <c r="BR12" s="11" t="n">
         <v>1.07801469203076e-15</v>
       </c>
-      <c r="BM12" s="11" t="n">
+      <c r="BS12" s="11" t="n">
         <v>2.40264829727727e-14</v>
       </c>
-      <c r="BN12" s="9" t="b">
+      <c r="BT12" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO12" s="9" t="inlineStr">
+      <c r="BU12" s="9" t="inlineStr">
         <is>
           <t>Gao_effect_size</t>
         </is>
       </c>
-      <c r="BP12" s="9" t="b">
+      <c r="BV12" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2933,21 +3143,21 @@
       <c r="AV13" s="9" t="n"/>
       <c r="AW13" s="9" t="n"/>
       <c r="AX13" s="9" t="n"/>
-      <c r="AY13" s="10" t="n">
-        <v>7.36478688339062</v>
-      </c>
-      <c r="AZ13" s="11" t="n">
-        <v>2.75951809166302e-12</v>
-      </c>
-      <c r="BA13" s="11" t="n">
-        <v>8.22286827863327e-12</v>
-      </c>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="9" t="n"/>
       <c r="BB13" s="9" t="n"/>
       <c r="BC13" s="9" t="n"/>
       <c r="BD13" s="9" t="n"/>
-      <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n"/>
-      <c r="BG13" s="9" t="n"/>
+      <c r="BE13" s="10" t="n">
+        <v>7.36478688339062</v>
+      </c>
+      <c r="BF13" s="11" t="n">
+        <v>2.75951809166302e-12</v>
+      </c>
+      <c r="BG13" s="11" t="n">
+        <v>8.22286827863327e-12</v>
+      </c>
       <c r="BH13" s="9" t="n"/>
       <c r="BI13" s="9" t="n"/>
       <c r="BJ13" s="9" t="n"/>
@@ -2955,12 +3165,18 @@
       <c r="BL13" s="9" t="n"/>
       <c r="BM13" s="9" t="n"/>
       <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="inlineStr">
+      <c r="BO13" s="9" t="n"/>
+      <c r="BP13" s="9" t="n"/>
+      <c r="BQ13" s="9" t="n"/>
+      <c r="BR13" s="9" t="n"/>
+      <c r="BS13" s="9" t="n"/>
+      <c r="BT13" s="9" t="n"/>
+      <c r="BU13" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP13" s="9" t="b">
+      <c r="BV13" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3090,73 +3306,91 @@
       <c r="AQ14" s="9" t="n"/>
       <c r="AR14" s="9" t="n"/>
       <c r="AS14" s="10" t="n">
+        <v>-0.934250626130547</v>
+      </c>
+      <c r="AT14" s="11" t="n">
+        <v>0.002773950276439</v>
+      </c>
+      <c r="AU14" s="11" t="n">
+        <v>0.006316046015612</v>
+      </c>
+      <c r="AV14" s="10" t="n">
+        <v>-0.686465475508208</v>
+      </c>
+      <c r="AW14" s="11" t="n">
+        <v>0.0278903581910029</v>
+      </c>
+      <c r="AX14" s="11" t="n">
+        <v>0.0554188691696594</v>
+      </c>
+      <c r="AY14" s="10" t="n">
         <v>1.361607086331125</v>
       </c>
-      <c r="AT14" s="11" t="n">
+      <c r="AZ14" s="11" t="n">
         <v>8.519737701802551e-05</v>
       </c>
-      <c r="AU14" s="11" t="n">
+      <c r="BA14" s="11" t="n">
         <v>0.0002466802715333</v>
       </c>
-      <c r="AV14" s="10" t="n">
+      <c r="BB14" s="10" t="n">
         <v>0.7149986708156708</v>
       </c>
-      <c r="AW14" s="11" t="n">
+      <c r="BC14" s="11" t="n">
         <v>0.0268916322646983</v>
       </c>
-      <c r="AX14" s="11" t="n">
+      <c r="BD14" s="11" t="n">
         <v>0.045776852909127</v>
       </c>
-      <c r="AY14" s="10" t="n">
+      <c r="BE14" s="10" t="n">
         <v>0.745426223148137</v>
       </c>
-      <c r="AZ14" s="11" t="n">
+      <c r="BF14" s="11" t="n">
         <v>0.004762342849978</v>
       </c>
-      <c r="BA14" s="11" t="n">
+      <c r="BG14" s="11" t="n">
         <v>0.0065844952076465</v>
       </c>
-      <c r="BB14" s="10" t="n">
+      <c r="BH14" s="10" t="n">
         <v>-0.0554276379201352</v>
       </c>
-      <c r="BC14" s="9" t="n"/>
-      <c r="BD14" s="11" t="n">
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="11" t="n">
         <v>0.877606667692742</v>
       </c>
-      <c r="BE14" s="10" t="n">
+      <c r="BK14" s="10" t="n">
         <v>0.654734068205669</v>
       </c>
-      <c r="BF14" s="9" t="n"/>
-      <c r="BG14" s="11" t="n">
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="11" t="n">
         <v>2.91727193989458e-10</v>
       </c>
-      <c r="BH14" s="10" t="n">
+      <c r="BN14" s="10" t="n">
         <v>4.55190891741079</v>
       </c>
-      <c r="BI14" s="11" t="n">
+      <c r="BO14" s="11" t="n">
         <v>3.26690738255902e-17</v>
       </c>
-      <c r="BJ14" s="11" t="n">
+      <c r="BP14" s="11" t="n">
         <v>3.90964746694522e-16</v>
       </c>
-      <c r="BK14" s="10" t="n">
+      <c r="BQ14" s="10" t="n">
         <v>4.66154103734362</v>
       </c>
-      <c r="BL14" s="11" t="n">
+      <c r="BR14" s="11" t="n">
         <v>1.95087802642985e-16</v>
       </c>
-      <c r="BM14" s="11" t="n">
+      <c r="BS14" s="11" t="n">
         <v>5.083278726684771e-15</v>
       </c>
-      <c r="BN14" s="9" t="b">
+      <c r="BT14" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO14" s="9" t="inlineStr">
+      <c r="BU14" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP14" s="9" t="b">
+      <c r="BV14" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3280,73 +3514,91 @@
         <v>0.0137187569540527</v>
       </c>
       <c r="AS15" s="10" t="n">
+        <v>1.78110727990936</v>
+      </c>
+      <c r="AT15" s="11" t="n">
+        <v>2.44604460778667e-06</v>
+      </c>
+      <c r="AU15" s="11" t="n">
+        <v>2.53860020739192e-05</v>
+      </c>
+      <c r="AV15" s="10" t="n">
+        <v>2.01131734338605</v>
+      </c>
+      <c r="AW15" s="11" t="n">
+        <v>0.0004930674155742</v>
+      </c>
+      <c r="AX15" s="11" t="n">
+        <v>0.0039572575989571</v>
+      </c>
+      <c r="AY15" s="10" t="n">
         <v>-8.152040929132102</v>
       </c>
-      <c r="AT15" s="11" t="n">
+      <c r="AZ15" s="11" t="n">
         <v>3.689515190286267e-08</v>
       </c>
-      <c r="AU15" s="11" t="n">
+      <c r="BA15" s="11" t="n">
         <v>3.660992753653132e-07</v>
       </c>
-      <c r="AV15" s="10" t="n">
+      <c r="BB15" s="10" t="n">
         <v>-8.152040929132102</v>
       </c>
-      <c r="AW15" s="11" t="n">
+      <c r="BC15" s="11" t="n">
         <v>2.341432644225264e-05</v>
       </c>
-      <c r="AX15" s="11" t="n">
+      <c r="BD15" s="11" t="n">
         <v>0.0001329154100896</v>
       </c>
-      <c r="AY15" s="10" t="n">
+      <c r="BE15" s="10" t="n">
         <v>2.02713488622674</v>
       </c>
-      <c r="AZ15" s="11" t="n">
+      <c r="BF15" s="11" t="n">
         <v>3.37605515080753e-27</v>
       </c>
-      <c r="BA15" s="11" t="n">
+      <c r="BG15" s="11" t="n">
         <v>2.81710826844307e-26</v>
       </c>
-      <c r="BB15" s="10" t="n">
+      <c r="BH15" s="10" t="n">
         <v>1.67806283998944</v>
       </c>
-      <c r="BC15" s="9" t="n"/>
-      <c r="BD15" s="11" t="n">
+      <c r="BI15" s="9" t="n"/>
+      <c r="BJ15" s="11" t="n">
         <v>1.54280444497508e-13</v>
       </c>
-      <c r="BE15" s="10" t="n">
+      <c r="BK15" s="10" t="n">
         <v>2.23031464377784</v>
       </c>
-      <c r="BF15" s="9" t="n"/>
-      <c r="BG15" s="11" t="n">
+      <c r="BL15" s="9" t="n"/>
+      <c r="BM15" s="11" t="n">
         <v>2.8032069092347e-196</v>
       </c>
-      <c r="BH15" s="10" t="n">
+      <c r="BN15" s="10" t="n">
         <v>1.34994899681148</v>
       </c>
-      <c r="BI15" s="11" t="n">
+      <c r="BO15" s="11" t="n">
         <v>3.55649118340587e-07</v>
       </c>
-      <c r="BJ15" s="11" t="n">
+      <c r="BP15" s="11" t="n">
         <v>9.80972117705192e-07</v>
       </c>
-      <c r="BK15" s="10" t="n">
+      <c r="BQ15" s="10" t="n">
         <v>0.819685047138303</v>
       </c>
-      <c r="BL15" s="11" t="n">
+      <c r="BR15" s="11" t="n">
         <v>0.0008348816534986</v>
       </c>
-      <c r="BM15" s="11" t="n">
+      <c r="BS15" s="11" t="n">
         <v>0.0018452635682124</v>
       </c>
-      <c r="BN15" s="9" t="b">
+      <c r="BT15" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO15" s="9" t="inlineStr">
+      <c r="BU15" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP15" s="9" t="b">
+      <c r="BV15" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3482,71 +3734,89 @@
         <v>3.61547555606571e-06</v>
       </c>
       <c r="AS16" s="10" t="n">
+        <v>-1.20048396253347</v>
+      </c>
+      <c r="AT16" s="11" t="n">
+        <v>0.0121864585857422</v>
+      </c>
+      <c r="AU16" s="11" t="n">
+        <v>0.0225618716817834</v>
+      </c>
+      <c r="AV16" s="10" t="n">
+        <v>-0.158803457090108</v>
+      </c>
+      <c r="AW16" s="11" t="n">
+        <v>0.743998014674472</v>
+      </c>
+      <c r="AX16" s="11" t="n">
+        <v>0.79758594696851</v>
+      </c>
+      <c r="AY16" s="10" t="n">
         <v>3.838225434786347</v>
       </c>
-      <c r="AT16" s="11" t="n">
+      <c r="AZ16" s="11" t="n">
         <v>9.046493512490024e-05</v>
       </c>
-      <c r="AU16" s="11" t="n">
+      <c r="BA16" s="11" t="n">
         <v>0.000259851995569</v>
       </c>
-      <c r="AV16" s="10" t="n">
+      <c r="BB16" s="10" t="n">
         <v>3.145383862021159</v>
       </c>
-      <c r="AW16" s="11" t="n">
+      <c r="BC16" s="11" t="n">
         <v>5.548230609831816e-06</v>
       </c>
-      <c r="AX16" s="11" t="n">
+      <c r="BD16" s="11" t="n">
         <v>4.338377763760714e-05</v>
       </c>
-      <c r="AY16" s="10" t="n">
+      <c r="BE16" s="10" t="n">
         <v>0.221508245845491</v>
       </c>
-      <c r="AZ16" s="11" t="n">
+      <c r="BF16" s="11" t="n">
         <v>0.173742792077452</v>
       </c>
-      <c r="BA16" s="11" t="n">
+      <c r="BG16" s="11" t="n">
         <v>0.200599382174245</v>
       </c>
-      <c r="BB16" s="10" t="n">
+      <c r="BH16" s="10" t="n">
         <v>0.438961218681568</v>
       </c>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="11" t="n">
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="11" t="n">
         <v>0.0134024246828029</v>
       </c>
-      <c r="BE16" s="10" t="n">
+      <c r="BK16" s="10" t="n">
         <v>-0.963225217532367</v>
       </c>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="11" t="n">
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="11" t="n">
         <v>3.40497651840545e-39</v>
       </c>
-      <c r="BH16" s="10" t="n">
+      <c r="BN16" s="10" t="n">
         <v>0.628181546646409</v>
       </c>
-      <c r="BI16" s="11" t="n">
+      <c r="BO16" s="11" t="n">
         <v>0.0182260506391194</v>
       </c>
-      <c r="BJ16" s="11" t="n">
+      <c r="BP16" s="11" t="n">
         <v>0.0265645185155706</v>
       </c>
-      <c r="BK16" s="10" t="n">
+      <c r="BQ16" s="10" t="n">
         <v>2.5517728210184</v>
       </c>
-      <c r="BL16" s="11" t="n">
+      <c r="BR16" s="11" t="n">
         <v>3.87588161752696e-16</v>
       </c>
-      <c r="BM16" s="11" t="n">
+      <c r="BS16" s="11" t="n">
         <v>9.52748875828112e-15</v>
       </c>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="inlineStr">
+      <c r="BT16" s="9" t="n"/>
+      <c r="BU16" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP16" s="9" t="b">
+      <c r="BV16" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3676,71 +3946,89 @@
         <v>2.74096014048803e-12</v>
       </c>
       <c r="AS17" s="10" t="n">
+        <v>-0.801733413525815</v>
+      </c>
+      <c r="AT17" s="11" t="n">
+        <v>0.106842503749278</v>
+      </c>
+      <c r="AU17" s="11" t="n">
+        <v>0.15007907810292</v>
+      </c>
+      <c r="AV17" s="10" t="n">
+        <v>0.428096534941324</v>
+      </c>
+      <c r="AW17" s="11" t="n">
+        <v>0.478956998634684</v>
+      </c>
+      <c r="AX17" s="11" t="n">
+        <v>0.559982988792129</v>
+      </c>
+      <c r="AY17" s="10" t="n">
         <v>3.887910913645635</v>
       </c>
-      <c r="AT17" s="11" t="n">
+      <c r="AZ17" s="11" t="n">
         <v>7.64232444302366e-06</v>
       </c>
-      <c r="AU17" s="11" t="n">
+      <c r="BA17" s="11" t="n">
         <v>3.118852200901656e-05</v>
       </c>
-      <c r="AV17" s="10" t="n">
+      <c r="BB17" s="10" t="n">
         <v>3.507968918764376</v>
       </c>
-      <c r="AW17" s="11" t="n">
+      <c r="BC17" s="11" t="n">
         <v>9.697074038965819e-07</v>
       </c>
-      <c r="AX17" s="11" t="n">
+      <c r="BD17" s="11" t="n">
         <v>1.144701407170341e-05</v>
       </c>
-      <c r="AY17" s="10" t="n">
+      <c r="BE17" s="10" t="n">
         <v>-0.0713325886046302</v>
       </c>
-      <c r="AZ17" s="11" t="n">
+      <c r="BF17" s="11" t="n">
         <v>0.6986181224745009</v>
       </c>
-      <c r="BA17" s="11" t="n">
+      <c r="BG17" s="11" t="n">
         <v>0.727776668621956</v>
       </c>
-      <c r="BB17" s="10" t="n">
+      <c r="BH17" s="10" t="n">
         <v>0.163688982157025</v>
       </c>
-      <c r="BC17" s="9" t="n"/>
-      <c r="BD17" s="11" t="n">
+      <c r="BI17" s="9" t="n"/>
+      <c r="BJ17" s="11" t="n">
         <v>0.469274589335398</v>
       </c>
-      <c r="BE17" s="10" t="n">
+      <c r="BK17" s="10" t="n">
         <v>-2.00691071894571</v>
       </c>
-      <c r="BF17" s="9" t="n"/>
-      <c r="BG17" s="11" t="n">
+      <c r="BL17" s="9" t="n"/>
+      <c r="BM17" s="11" t="n">
         <v>2.59613475442048e-87</v>
       </c>
-      <c r="BH17" s="10" t="n">
+      <c r="BN17" s="10" t="n">
         <v>1.01939227713914</v>
       </c>
-      <c r="BI17" s="11" t="n">
+      <c r="BO17" s="11" t="n">
         <v>0.0004851373297352</v>
       </c>
-      <c r="BJ17" s="11" t="n">
+      <c r="BP17" s="11" t="n">
         <v>0.0008941031098306</v>
       </c>
-      <c r="BK17" s="10" t="n">
+      <c r="BQ17" s="10" t="n">
         <v>2.00247177995832</v>
       </c>
-      <c r="BL17" s="11" t="n">
+      <c r="BR17" s="11" t="n">
         <v>1.54928482128321e-09</v>
       </c>
-      <c r="BM17" s="11" t="n">
+      <c r="BS17" s="11" t="n">
         <v>1.01475323463481e-08</v>
       </c>
-      <c r="BN17" s="9" t="n"/>
-      <c r="BO17" s="9" t="inlineStr">
+      <c r="BT17" s="9" t="n"/>
+      <c r="BU17" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP17" s="9" t="b">
+      <c r="BV17" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3857,40 +4145,46 @@
       <c r="AV18" s="9" t="n"/>
       <c r="AW18" s="9" t="n"/>
       <c r="AX18" s="9" t="n"/>
-      <c r="AY18" s="10" t="n">
-        <v>2.49237551608169</v>
-      </c>
-      <c r="AZ18" s="11" t="n">
-        <v>4.66122658012639e-08</v>
-      </c>
-      <c r="BA18" s="11" t="n">
-        <v>9.89278609871959e-08</v>
-      </c>
+      <c r="AY18" s="9" t="n"/>
+      <c r="AZ18" s="9" t="n"/>
+      <c r="BA18" s="9" t="n"/>
       <c r="BB18" s="9" t="n"/>
       <c r="BC18" s="9" t="n"/>
       <c r="BD18" s="9" t="n"/>
       <c r="BE18" s="10" t="n">
-        <v>-5.1390419411966</v>
-      </c>
-      <c r="BF18" s="9" t="n"/>
+        <v>2.49237551608169</v>
+      </c>
+      <c r="BF18" s="11" t="n">
+        <v>4.66122658012639e-08</v>
+      </c>
       <c r="BG18" s="11" t="n">
-        <v>2.06267277087821e-141</v>
+        <v>9.89278609871959e-08</v>
       </c>
       <c r="BH18" s="9" t="n"/>
       <c r="BI18" s="9" t="n"/>
       <c r="BJ18" s="9" t="n"/>
-      <c r="BK18" s="9" t="n"/>
+      <c r="BK18" s="10" t="n">
+        <v>-5.1390419411966</v>
+      </c>
       <c r="BL18" s="9" t="n"/>
-      <c r="BM18" s="9" t="n"/>
-      <c r="BN18" s="9" t="b">
+      <c r="BM18" s="11" t="n">
+        <v>2.06267277087821e-141</v>
+      </c>
+      <c r="BN18" s="9" t="n"/>
+      <c r="BO18" s="9" t="n"/>
+      <c r="BP18" s="9" t="n"/>
+      <c r="BQ18" s="9" t="n"/>
+      <c r="BR18" s="9" t="n"/>
+      <c r="BS18" s="9" t="n"/>
+      <c r="BT18" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO18" s="9" t="inlineStr">
+      <c r="BU18" s="9" t="inlineStr">
         <is>
           <t>Gao_effect_size</t>
         </is>
       </c>
-      <c r="BP18" s="9" t="b">
+      <c r="BV18" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4026,73 +4320,91 @@
         <v>6.52881718069265e-05</v>
       </c>
       <c r="AS19" s="10" t="n">
+        <v>-0.498800404647518</v>
+      </c>
+      <c r="AT19" s="11" t="n">
+        <v>0.201890205111104</v>
+      </c>
+      <c r="AU19" s="11" t="n">
+        <v>0.261142289299091</v>
+      </c>
+      <c r="AV19" s="10" t="n">
+        <v>-0.900045837536846</v>
+      </c>
+      <c r="AW19" s="11" t="n">
+        <v>0.115180607855027</v>
+      </c>
+      <c r="AX19" s="11" t="n">
+        <v>0.173438056185215</v>
+      </c>
+      <c r="AY19" s="10" t="n">
         <v>0.3108106713744344</v>
       </c>
-      <c r="AT19" s="11" t="n">
+      <c r="AZ19" s="11" t="n">
         <v>0.8129219522251536</v>
       </c>
-      <c r="AU19" s="11" t="n">
+      <c r="BA19" s="11" t="n">
         <v>0.837712255850796</v>
       </c>
-      <c r="AV19" s="10" t="n">
+      <c r="BB19" s="10" t="n">
         <v>0.7013714511280346</v>
       </c>
-      <c r="AW19" s="11" t="n">
+      <c r="BC19" s="11" t="n">
         <v>0.4135520539426656</v>
       </c>
-      <c r="AX19" s="11" t="n">
+      <c r="BD19" s="11" t="n">
         <v>0.4748466964225331</v>
       </c>
-      <c r="AY19" s="10" t="n">
+      <c r="BE19" s="10" t="n">
         <v>2.29482738823638</v>
       </c>
-      <c r="AZ19" s="11" t="n">
+      <c r="BF19" s="11" t="n">
         <v>6.31076114404677e-47</v>
       </c>
-      <c r="BA19" s="11" t="n">
+      <c r="BG19" s="11" t="n">
         <v>1.42962817113811e-45</v>
       </c>
-      <c r="BB19" s="10" t="n">
+      <c r="BH19" s="10" t="n">
         <v>2.52306766993452</v>
       </c>
-      <c r="BC19" s="9" t="n"/>
-      <c r="BD19" s="11" t="n">
+      <c r="BI19" s="9" t="n"/>
+      <c r="BJ19" s="11" t="n">
         <v>2.4050331831309e-18</v>
       </c>
-      <c r="BE19" s="10" t="n">
+      <c r="BK19" s="10" t="n">
         <v>1.81120060518907</v>
       </c>
-      <c r="BF19" s="9" t="n"/>
-      <c r="BG19" s="11" t="n">
+      <c r="BL19" s="9" t="n"/>
+      <c r="BM19" s="11" t="n">
         <v>1.18830611185907e-99</v>
       </c>
-      <c r="BH19" s="10" t="n">
+      <c r="BN19" s="10" t="n">
         <v>2.68701270314905</v>
       </c>
-      <c r="BI19" s="11" t="n">
+      <c r="BO19" s="11" t="n">
         <v>1.48745023055985e-22</v>
       </c>
-      <c r="BJ19" s="11" t="n">
+      <c r="BP19" s="11" t="n">
         <v>4.66088882479906e-21</v>
       </c>
-      <c r="BK19" s="10" t="n">
+      <c r="BQ19" s="10" t="n">
         <v>2.78121905025346</v>
       </c>
-      <c r="BL19" s="11" t="n">
+      <c r="BR19" s="11" t="n">
         <v>6.22873200049136e-24</v>
       </c>
-      <c r="BM19" s="11" t="n">
+      <c r="BS19" s="11" t="n">
         <v>7.438663191586801e-22</v>
       </c>
-      <c r="BN19" s="9" t="b">
+      <c r="BT19" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO19" s="9" t="inlineStr">
+      <c r="BU19" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP19" s="9" t="b">
+      <c r="BV19" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4191,48 +4503,66 @@
       <c r="AP20" s="9" t="n"/>
       <c r="AQ20" s="9" t="n"/>
       <c r="AR20" s="9" t="n"/>
-      <c r="AS20" s="9" t="n"/>
-      <c r="AT20" s="9" t="n"/>
-      <c r="AU20" s="9" t="n"/>
-      <c r="AV20" s="9" t="n"/>
-      <c r="AW20" s="9" t="n"/>
-      <c r="AX20" s="9" t="n"/>
-      <c r="AY20" s="10" t="n">
+      <c r="AS20" s="10" t="n">
+        <v>-0.262095295947848</v>
+      </c>
+      <c r="AT20" s="11" t="n">
+        <v>0.394205174741443</v>
+      </c>
+      <c r="AU20" s="11" t="n">
+        <v>0.46400404408093</v>
+      </c>
+      <c r="AV20" s="10" t="n">
+        <v>0.339152339616014</v>
+      </c>
+      <c r="AW20" s="11" t="n">
+        <v>0.390396160422794</v>
+      </c>
+      <c r="AX20" s="11" t="n">
+        <v>0.474358536027351</v>
+      </c>
+      <c r="AY20" s="9" t="n"/>
+      <c r="AZ20" s="9" t="n"/>
+      <c r="BA20" s="9" t="n"/>
+      <c r="BB20" s="9" t="n"/>
+      <c r="BC20" s="9" t="n"/>
+      <c r="BD20" s="9" t="n"/>
+      <c r="BE20" s="10" t="n">
         <v>-1.02954992492292</v>
       </c>
-      <c r="AZ20" s="11" t="n">
+      <c r="BF20" s="11" t="n">
         <v>6.752440950602e-15</v>
       </c>
-      <c r="BA20" s="11" t="n">
+      <c r="BG20" s="11" t="n">
         <v>2.46117659047272e-14</v>
       </c>
-      <c r="BB20" s="10" t="n">
+      <c r="BH20" s="10" t="n">
         <v>-0.931053223313861</v>
       </c>
-      <c r="BC20" s="9" t="n"/>
-      <c r="BD20" s="11" t="n">
+      <c r="BI20" s="9" t="n"/>
+      <c r="BJ20" s="11" t="n">
         <v>1.39662055300777e-05</v>
       </c>
-      <c r="BE20" s="10" t="n">
+      <c r="BK20" s="10" t="n">
         <v>-2.59671603848386</v>
       </c>
-      <c r="BF20" s="9" t="n"/>
-      <c r="BG20" s="11" t="n">
+      <c r="BL20" s="9" t="n"/>
+      <c r="BM20" s="11" t="n">
         <v>9.064306931149109e-176</v>
       </c>
-      <c r="BH20" s="9" t="n"/>
-      <c r="BI20" s="9" t="n"/>
-      <c r="BJ20" s="9" t="n"/>
-      <c r="BK20" s="9" t="n"/>
-      <c r="BL20" s="9" t="n"/>
-      <c r="BM20" s="9" t="n"/>
       <c r="BN20" s="9" t="n"/>
-      <c r="BO20" s="9" t="inlineStr">
+      <c r="BO20" s="9" t="n"/>
+      <c r="BP20" s="9" t="n"/>
+      <c r="BQ20" s="9" t="n"/>
+      <c r="BR20" s="9" t="n"/>
+      <c r="BS20" s="9" t="n"/>
+      <c r="BT20" s="9" t="n"/>
+      <c r="BU20" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP20" s="9" t="b">
+      <c r="BV20" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4368,73 +4698,91 @@
         <v>0.100137273275775</v>
       </c>
       <c r="AS21" s="10" t="n">
+        <v>1.49619971837867</v>
+      </c>
+      <c r="AT21" s="11" t="n">
+        <v>1.32242285054691e-05</v>
+      </c>
+      <c r="AU21" s="11" t="n">
+        <v>8.38546264223985e-05</v>
+      </c>
+      <c r="AV21" s="10" t="n">
+        <v>1.32716981195492</v>
+      </c>
+      <c r="AW21" s="11" t="n">
+        <v>0.003763198104537</v>
+      </c>
+      <c r="AX21" s="11" t="n">
+        <v>0.0145720359533074</v>
+      </c>
+      <c r="AY21" s="10" t="n">
         <v>7.946666973442184</v>
       </c>
-      <c r="AT21" s="11" t="n">
+      <c r="AZ21" s="11" t="n">
         <v>4.579328308942674e-09</v>
       </c>
-      <c r="AU21" s="11" t="n">
+      <c r="BA21" s="11" t="n">
         <v>6.742330191039002e-08</v>
       </c>
-      <c r="AV21" s="10" t="n">
+      <c r="BB21" s="10" t="n">
         <v>8.119267175920886</v>
       </c>
-      <c r="AW21" s="11" t="n">
+      <c r="BC21" s="11" t="n">
         <v>6.720134099839369e-06</v>
       </c>
-      <c r="AX21" s="11" t="n">
+      <c r="BD21" s="11" t="n">
         <v>5.01798732255194e-05</v>
       </c>
-      <c r="AY21" s="10" t="n">
+      <c r="BE21" s="10" t="n">
         <v>1.57367534695579</v>
       </c>
-      <c r="AZ21" s="11" t="n">
+      <c r="BF21" s="11" t="n">
         <v>3.54012813986684e-07</v>
       </c>
-      <c r="BA21" s="11" t="n">
+      <c r="BG21" s="11" t="n">
         <v>6.97929358708266e-07</v>
       </c>
-      <c r="BB21" s="10" t="n">
+      <c r="BH21" s="10" t="n">
         <v>0.646924522534852</v>
       </c>
-      <c r="BC21" s="9" t="n"/>
-      <c r="BD21" s="11" t="n">
+      <c r="BI21" s="9" t="n"/>
+      <c r="BJ21" s="11" t="n">
         <v>0.06882136244602841</v>
       </c>
-      <c r="BE21" s="10" t="n">
+      <c r="BK21" s="10" t="n">
         <v>1.11067385875638</v>
       </c>
-      <c r="BF21" s="9" t="n"/>
-      <c r="BG21" s="11" t="n">
+      <c r="BL21" s="9" t="n"/>
+      <c r="BM21" s="11" t="n">
         <v>6.36402812386608e-27</v>
       </c>
-      <c r="BH21" s="10" t="n">
+      <c r="BN21" s="10" t="n">
         <v>6.30648245228024</v>
       </c>
-      <c r="BI21" s="11" t="n">
+      <c r="BO21" s="11" t="n">
         <v>5.560599802299899e-12</v>
       </c>
-      <c r="BJ21" s="11" t="n">
+      <c r="BP21" s="11" t="n">
         <v>2.97050435094872e-11</v>
       </c>
-      <c r="BK21" s="10" t="n">
+      <c r="BQ21" s="10" t="n">
         <v>6.19072201370017</v>
       </c>
-      <c r="BL21" s="11" t="n">
+      <c r="BR21" s="11" t="n">
         <v>1.99201660424675e-09</v>
       </c>
-      <c r="BM21" s="11" t="n">
+      <c r="BS21" s="11" t="n">
         <v>1.28188549418321e-08</v>
       </c>
-      <c r="BN21" s="9" t="b">
+      <c r="BT21" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="BO21" s="9" t="inlineStr">
+      <c r="BU21" s="9" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="BP21" s="9" t="b">
+      <c r="BV21" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4570,73 +4918,91 @@
         <v>5.70073021485393e-09</v>
       </c>
       <c r="AS22" s="10" t="n">
+        <v>-2.3134926643114</v>
+      </c>
+      <c r="AT22" s="11" t="n">
+        <v>0.0008971869518687</v>
+      </c>
+      <c r="AU22" s="11" t="n">
+        <v>0.0024075624623698</v>
+      </c>
+      <c r="AV22" s="10" t="n">
+        <v>-1.09040495666661</v>
+      </c>
+      <c r="AW22" s="11" t="n">
+        <v>0.0648630285782663</v>
+      </c>
+      <c r="AX22" s="11" t="n">
+        <v>0.108144738889317</v>
+      </c>
+      <c r="AY22" s="10" t="n">
         <v>-5.468603170718869</v>
       </c>
-      <c r="AT22" s="11" t="n">
+      <c r="AZ22" s="11" t="n">
         <v>1.020203626466686e-08</v>
       </c>
-      <c r="AU22" s="11" t="n">
+      <c r="BA22" s="11" t="n">
         <v>1.294861317292167e-07</v>
       </c>
-      <c r="AV22" s="10" t="n">
+      <c r="BB22" s="10" t="n">
         <v>-5.673953807314062</v>
       </c>
-      <c r="AW22" s="11" t="n">
+      <c r="BC22" s="11" t="n">
         <v>6.214573379547933e-10</v>
       </c>
-      <c r="AX22" s="11" t="n">
+      <c r="BD22" s="11" t="n">
         <v>6.193930268023222e-08</v>
       </c>
-      <c r="AY22" s="10" t="n">
+      <c r="BE22" s="10" t="n">
         <v>1.88873842413568</v>
       </c>
-      <c r="AZ22" s="11" t="n">
+      <c r="BF22" s="11" t="n">
         <v>8.052214826593391e-14</v>
       </c>
-      <c r="BA22" s="11" t="n">
+      <c r="BG22" s="11" t="n">
         <v>2.71558850854047e-13</v>
       </c>
-      <c r="BB22" s="10" t="n">
+      <c r="BH22" s="10" t="n">
         <v>1.55366222585167</v>
       </c>
-      <c r="BC22" s="9" t="n"/>
-      <c r="BD22" s="11" t="n">
+      <c r="BI22" s="9" t="n"/>
+      <c r="BJ22" s="11" t="n">
         <v>4.34957901097087e-06</v>
       </c>
-      <c r="BE22" s="10" t="n">
+      <c r="BK22" s="10" t="n">
         <v>3.31365052381195</v>
       </c>
-      <c r="BF22" s="9" t="n"/>
-      <c r="BG22" s="11" t="n">
+      <c r="BL22" s="9" t="n"/>
+      <c r="BM22" s="11" t="n">
         <v>2.57161144762956e-140</v>
       </c>
-      <c r="BH22" s="10" t="n">
+      <c r="BN22" s="10" t="n">
         <v>0.89453255383055</v>
       </c>
-      <c r="BI22" s="11" t="n">
+      <c r="BO22" s="11" t="n">
         <v>0.0194193753110822</v>
       </c>
-      <c r="BJ22" s="11" t="n">
+      <c r="BP22" s="11" t="n">
         <v>0.0282086724890446</v>
       </c>
-      <c r="BK22" s="10" t="n">
+      <c r="BQ22" s="10" t="n">
         <v>3.08813339050379</v>
       </c>
-      <c r="BL22" s="11" t="n">
+      <c r="BR22" s="11" t="n">
         <v>7.167108070420469e-11</v>
       </c>
-      <c r="BM22" s="11" t="n">
+      <c r="BS22" s="11" t="n">
         <v>6.03832015033484e-10</v>
       </c>
-      <c r="BN22" s="9" t="b">
+      <c r="BT22" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO22" s="9" t="inlineStr">
+      <c r="BU22" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP22" s="9" t="b">
+      <c r="BV22" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4772,73 +5138,91 @@
         <v>4.18959895670715e-06</v>
       </c>
       <c r="AS23" s="10" t="n">
+        <v>1.34503769070429</v>
+      </c>
+      <c r="AT23" s="11" t="n">
+        <v>0.198124156346869</v>
+      </c>
+      <c r="AU23" s="11" t="n">
+        <v>0.256827255109667</v>
+      </c>
+      <c r="AV23" s="10" t="n">
+        <v>4.09212164800002</v>
+      </c>
+      <c r="AW23" s="11" t="n">
+        <v>0.020932657243233</v>
+      </c>
+      <c r="AX23" s="11" t="n">
+        <v>0.0443261276203686</v>
+      </c>
+      <c r="AY23" s="10" t="n">
         <v>-0.2903214224688967</v>
       </c>
-      <c r="AT23" s="11" t="n">
+      <c r="AZ23" s="11" t="n">
         <v>0.441581587716711</v>
       </c>
-      <c r="AU23" s="11" t="n">
+      <c r="BA23" s="11" t="n">
         <v>0.4903860277769448</v>
       </c>
-      <c r="AV23" s="10" t="n">
+      <c r="BB23" s="10" t="n">
         <v>-1.579623077199753</v>
       </c>
-      <c r="AW23" s="11" t="n">
+      <c r="BC23" s="11" t="n">
         <v>0.0386305398225972</v>
       </c>
-      <c r="AX23" s="11" t="n">
+      <c r="BD23" s="11" t="n">
         <v>0.0623464344582272</v>
       </c>
-      <c r="AY23" s="10" t="n">
+      <c r="BE23" s="10" t="n">
         <v>2.9979635592165</v>
       </c>
-      <c r="AZ23" s="11" t="n">
+      <c r="BF23" s="11" t="n">
         <v>2.4024716743736e-15</v>
       </c>
-      <c r="BA23" s="11" t="n">
+      <c r="BG23" s="11" t="n">
         <v>9.1037634158314e-15</v>
       </c>
-      <c r="BB23" s="10" t="n">
+      <c r="BH23" s="10" t="n">
         <v>1.76009229587045</v>
       </c>
-      <c r="BC23" s="9" t="n"/>
-      <c r="BD23" s="11" t="n">
+      <c r="BI23" s="9" t="n"/>
+      <c r="BJ23" s="11" t="n">
         <v>0.0003603481422587</v>
       </c>
-      <c r="BE23" s="10" t="n">
+      <c r="BK23" s="10" t="n">
         <v>4.21890908178643</v>
       </c>
-      <c r="BF23" s="9" t="n"/>
-      <c r="BG23" s="11" t="n">
+      <c r="BL23" s="9" t="n"/>
+      <c r="BM23" s="11" t="n">
         <v>6.612153004650101e-150</v>
       </c>
-      <c r="BH23" s="10" t="n">
+      <c r="BN23" s="10" t="n">
         <v>1.51085977279679</v>
       </c>
-      <c r="BI23" s="11" t="n">
+      <c r="BO23" s="11" t="n">
         <v>0.001401194065142</v>
       </c>
-      <c r="BJ23" s="11" t="n">
+      <c r="BP23" s="11" t="n">
         <v>0.0024078517284058</v>
       </c>
-      <c r="BK23" s="10" t="n">
+      <c r="BQ23" s="10" t="n">
         <v>3.74403292270937</v>
       </c>
-      <c r="BL23" s="11" t="n">
+      <c r="BR23" s="11" t="n">
         <v>3.13405927259939e-10</v>
       </c>
-      <c r="BM23" s="11" t="n">
+      <c r="BS23" s="11" t="n">
         <v>2.34294227624527e-09</v>
       </c>
-      <c r="BN23" s="9" t="b">
+      <c r="BT23" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO23" s="9" t="inlineStr">
+      <c r="BU23" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP23" s="9" t="b">
+      <c r="BV23" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4974,73 +5358,91 @@
         <v>3.04134092328169e-10</v>
       </c>
       <c r="AS24" s="10" t="n">
+        <v>-2.04918691972589</v>
+      </c>
+      <c r="AT24" s="11" t="n">
+        <v>2.00062950559855e-07</v>
+      </c>
+      <c r="AU24" s="11" t="n">
+        <v>4.46013884039304e-06</v>
+      </c>
+      <c r="AV24" s="10" t="n">
+        <v>-1.97898297875365</v>
+      </c>
+      <c r="AW24" s="11" t="n">
+        <v>6.878943769319351e-05</v>
+      </c>
+      <c r="AX24" s="11" t="n">
+        <v>0.0011139021140714</v>
+      </c>
+      <c r="AY24" s="10" t="n">
         <v>0.0717301669226646</v>
       </c>
-      <c r="AT24" s="11" t="n">
+      <c r="AZ24" s="11" t="n">
         <v>0.8568448013937665</v>
       </c>
-      <c r="AU24" s="11" t="n">
+      <c r="BA24" s="11" t="n">
         <v>0.8763923821723018</v>
       </c>
-      <c r="AV24" s="10" t="n">
+      <c r="BB24" s="10" t="n">
         <v>-0.4016092905692264</v>
       </c>
-      <c r="AW24" s="11" t="n">
+      <c r="BC24" s="11" t="n">
         <v>0.261972407687722</v>
       </c>
-      <c r="AX24" s="11" t="n">
+      <c r="BD24" s="11" t="n">
         <v>0.3224759414124916</v>
       </c>
-      <c r="AY24" s="10" t="n">
+      <c r="BE24" s="10" t="n">
         <v>1.36639206277824</v>
       </c>
-      <c r="AZ24" s="11" t="n">
+      <c r="BF24" s="11" t="n">
         <v>2.03372402737343e-41</v>
       </c>
-      <c r="BA24" s="11" t="n">
+      <c r="BG24" s="11" t="n">
         <v>3.52762315301601e-40</v>
       </c>
-      <c r="BB24" s="10" t="n">
+      <c r="BH24" s="10" t="n">
         <v>1.26799737584483</v>
       </c>
-      <c r="BC24" s="9" t="n"/>
-      <c r="BD24" s="11" t="n">
+      <c r="BI24" s="9" t="n"/>
+      <c r="BJ24" s="11" t="n">
         <v>1.49985004748258e-15</v>
       </c>
-      <c r="BE24" s="10" t="n">
+      <c r="BK24" s="10" t="n">
         <v>1.14584323905699</v>
       </c>
-      <c r="BF24" s="9" t="n"/>
-      <c r="BG24" s="11" t="n">
+      <c r="BL24" s="9" t="n"/>
+      <c r="BM24" s="11" t="n">
         <v>1.14963661364459e-101</v>
       </c>
-      <c r="BH24" s="10" t="n">
+      <c r="BN24" s="10" t="n">
         <v>2.10989447178502</v>
       </c>
-      <c r="BI24" s="11" t="n">
+      <c r="BO24" s="11" t="n">
         <v>2.88137668850818e-25</v>
       </c>
-      <c r="BJ24" s="11" t="n">
+      <c r="BP24" s="11" t="n">
         <v>1.66711463835891e-23</v>
       </c>
-      <c r="BK24" s="10" t="n">
+      <c r="BQ24" s="10" t="n">
         <v>1.38530001359927</v>
       </c>
-      <c r="BL24" s="11" t="n">
+      <c r="BR24" s="11" t="n">
         <v>6.65930047988967e-16</v>
       </c>
-      <c r="BM24" s="11" t="n">
+      <c r="BS24" s="11" t="n">
         <v>1.57482566299173e-14</v>
       </c>
-      <c r="BN24" s="9" t="b">
+      <c r="BT24" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO24" s="9" t="inlineStr">
+      <c r="BU24" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP24" s="9" t="b">
+      <c r="BV24" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5162,71 +5564,89 @@
         <v>0.120719760299218</v>
       </c>
       <c r="AS25" s="10" t="n">
+        <v>-0.7377291661961241</v>
+      </c>
+      <c r="AT25" s="11" t="n">
+        <v>0.0009956193680639</v>
+      </c>
+      <c r="AU25" s="11" t="n">
+        <v>0.0026321637930159</v>
+      </c>
+      <c r="AV25" s="10" t="n">
+        <v>-0.847243338918636</v>
+      </c>
+      <c r="AW25" s="11" t="n">
+        <v>0.0123887713544279</v>
+      </c>
+      <c r="AX25" s="11" t="n">
+        <v>0.0299146688919496</v>
+      </c>
+      <c r="AY25" s="10" t="n">
         <v>0.0992328917916334</v>
       </c>
-      <c r="AT25" s="11" t="n">
+      <c r="AZ25" s="11" t="n">
         <v>0.6344666916946917</v>
       </c>
-      <c r="AU25" s="11" t="n">
+      <c r="BA25" s="11" t="n">
         <v>0.6754630010041949</v>
       </c>
-      <c r="AV25" s="10" t="n">
+      <c r="BB25" s="10" t="n">
         <v>0.1413527387392914</v>
       </c>
-      <c r="AW25" s="11" t="n">
+      <c r="BC25" s="11" t="n">
         <v>0.7513037284652111</v>
       </c>
-      <c r="AX25" s="11" t="n">
+      <c r="BD25" s="11" t="n">
         <v>0.7896193240894125</v>
       </c>
-      <c r="AY25" s="10" t="n">
+      <c r="BE25" s="10" t="n">
         <v>0.159515216698385</v>
       </c>
-      <c r="AZ25" s="11" t="n">
+      <c r="BF25" s="11" t="n">
         <v>0.168997138922345</v>
       </c>
-      <c r="BA25" s="11" t="n">
+      <c r="BG25" s="11" t="n">
         <v>0.195416149652159</v>
       </c>
-      <c r="BB25" s="10" t="n">
+      <c r="BH25" s="10" t="n">
         <v>-0.153171304696138</v>
       </c>
-      <c r="BC25" s="9" t="n"/>
-      <c r="BD25" s="11" t="n">
+      <c r="BI25" s="9" t="n"/>
+      <c r="BJ25" s="11" t="n">
         <v>0.394727350213552</v>
       </c>
-      <c r="BE25" s="10" t="n">
+      <c r="BK25" s="10" t="n">
         <v>1.74866833860967</v>
       </c>
-      <c r="BF25" s="9" t="n"/>
-      <c r="BG25" s="11" t="n">
+      <c r="BL25" s="9" t="n"/>
+      <c r="BM25" s="11" t="n">
         <v>7.290050415594039e-80</v>
       </c>
-      <c r="BH25" s="10" t="n">
+      <c r="BN25" s="10" t="n">
         <v>-0.200608496306742</v>
       </c>
-      <c r="BI25" s="11" t="n">
+      <c r="BO25" s="11" t="n">
         <v>0.0597691631926591</v>
       </c>
-      <c r="BJ25" s="11" t="n">
+      <c r="BP25" s="11" t="n">
         <v>0.079764586113269</v>
       </c>
-      <c r="BK25" s="10" t="n">
+      <c r="BQ25" s="10" t="n">
         <v>0.633311174348519</v>
       </c>
-      <c r="BL25" s="11" t="n">
+      <c r="BR25" s="11" t="n">
         <v>4.709231364377331e-09</v>
       </c>
-      <c r="BM25" s="11" t="n">
+      <c r="BS25" s="11" t="n">
         <v>2.78530725063523e-08</v>
       </c>
-      <c r="BN25" s="9" t="n"/>
-      <c r="BO25" s="9" t="inlineStr">
+      <c r="BT25" s="9" t="n"/>
+      <c r="BU25" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP25" s="9" t="b">
+      <c r="BV25" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5356,73 +5776,91 @@
         <v>0.0013887178423849</v>
       </c>
       <c r="AS26" s="10" t="n">
+        <v>1.10187890032299</v>
+      </c>
+      <c r="AT26" s="11" t="n">
+        <v>0.0341755702468795</v>
+      </c>
+      <c r="AU26" s="11" t="n">
+        <v>0.0554326466863767</v>
+      </c>
+      <c r="AV26" s="10" t="n">
+        <v>1.63942106505118</v>
+      </c>
+      <c r="AW26" s="11" t="n">
+        <v>0.0734365728347043</v>
+      </c>
+      <c r="AX26" s="11" t="n">
+        <v>0.119750187919734</v>
+      </c>
+      <c r="AY26" s="10" t="n">
         <v>5.062415359539015</v>
       </c>
-      <c r="AT26" s="11" t="n">
+      <c r="AZ26" s="11" t="n">
         <v>1.341096917759262e-07</v>
       </c>
-      <c r="AU26" s="11" t="n">
+      <c r="BA26" s="11" t="n">
         <v>1.043278017160178e-06</v>
       </c>
-      <c r="AV26" s="10" t="n">
+      <c r="BB26" s="10" t="n">
         <v>5.036671232260984</v>
       </c>
-      <c r="AW26" s="11" t="n">
+      <c r="BC26" s="11" t="n">
         <v>4.911783202710196e-06</v>
       </c>
-      <c r="AX26" s="11" t="n">
+      <c r="BD26" s="11" t="n">
         <v>3.973692632783213e-05</v>
       </c>
-      <c r="AY26" s="10" t="n">
+      <c r="BE26" s="10" t="n">
         <v>-0.455321176539081</v>
       </c>
-      <c r="AZ26" s="11" t="n">
+      <c r="BF26" s="11" t="n">
         <v>0.0035334500330038</v>
       </c>
-      <c r="BA26" s="11" t="n">
+      <c r="BG26" s="11" t="n">
         <v>0.0049482336013326</v>
       </c>
-      <c r="BB26" s="10" t="n">
+      <c r="BH26" s="10" t="n">
         <v>-0.729541570166073</v>
       </c>
-      <c r="BC26" s="9" t="n"/>
-      <c r="BD26" s="11" t="n">
+      <c r="BI26" s="9" t="n"/>
+      <c r="BJ26" s="11" t="n">
         <v>0.0002479126459842</v>
       </c>
-      <c r="BE26" s="10" t="n">
+      <c r="BK26" s="10" t="n">
         <v>-0.447888686877304</v>
       </c>
-      <c r="BF26" s="9" t="n"/>
-      <c r="BG26" s="11" t="n">
+      <c r="BL26" s="9" t="n"/>
+      <c r="BM26" s="11" t="n">
         <v>4.791976846312429e-11</v>
       </c>
-      <c r="BH26" s="10" t="n">
+      <c r="BN26" s="10" t="n">
         <v>-1.80161423745876</v>
       </c>
-      <c r="BI26" s="11" t="n">
+      <c r="BO26" s="11" t="n">
         <v>1.87116695254079e-07</v>
       </c>
-      <c r="BJ26" s="11" t="n">
+      <c r="BP26" s="11" t="n">
         <v>5.3261029507146e-07</v>
       </c>
-      <c r="BK26" s="10" t="n">
+      <c r="BQ26" s="10" t="n">
         <v>-2.212691629844</v>
       </c>
-      <c r="BL26" s="11" t="n">
+      <c r="BR26" s="11" t="n">
         <v>2.36840318624402e-09</v>
       </c>
-      <c r="BM26" s="11" t="n">
+      <c r="BS26" s="11" t="n">
         <v>1.49852477095201e-08</v>
       </c>
-      <c r="BN26" s="9" t="b">
+      <c r="BT26" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="BO26" s="9" t="inlineStr">
+      <c r="BU26" s="9" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="BP26" s="9" t="b">
+      <c r="BV26" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5558,73 +5996,91 @@
         <v>4.470467049953401e-10</v>
       </c>
       <c r="AS27" s="10" t="n">
+        <v>0.767356720032175</v>
+      </c>
+      <c r="AT27" s="11" t="n">
+        <v>0.0026205329189469</v>
+      </c>
+      <c r="AU27" s="11" t="n">
+        <v>0.0060121935470051</v>
+      </c>
+      <c r="AV27" s="10" t="n">
+        <v>0.546799971024799</v>
+      </c>
+      <c r="AW27" s="11" t="n">
+        <v>0.0790460651889861</v>
+      </c>
+      <c r="AX27" s="11" t="n">
+        <v>0.127088530917663</v>
+      </c>
+      <c r="AY27" s="10" t="n">
         <v>-0.1918363813113215</v>
       </c>
-      <c r="AT27" s="11" t="n">
+      <c r="AZ27" s="11" t="n">
         <v>0.2151818716878313</v>
       </c>
-      <c r="AU27" s="11" t="n">
+      <c r="BA27" s="11" t="n">
         <v>0.2590646497566962</v>
       </c>
-      <c r="AV27" s="10" t="n">
+      <c r="BB27" s="10" t="n">
         <v>0.3569919020809229</v>
       </c>
-      <c r="AW27" s="11" t="n">
+      <c r="BC27" s="11" t="n">
         <v>0.8876670359353867</v>
       </c>
-      <c r="AX27" s="11" t="n">
+      <c r="BD27" s="11" t="n">
         <v>0.905979186527516</v>
       </c>
-      <c r="AY27" s="10" t="n">
+      <c r="BE27" s="10" t="n">
         <v>0.128296775049852</v>
       </c>
-      <c r="AZ27" s="11" t="n">
+      <c r="BF27" s="11" t="n">
         <v>0.470593663854106</v>
       </c>
-      <c r="BA27" s="11" t="n">
+      <c r="BG27" s="11" t="n">
         <v>0.50825445868746</v>
       </c>
-      <c r="BB27" s="10" t="n">
+      <c r="BH27" s="10" t="n">
         <v>-0.6703771259474079</v>
       </c>
-      <c r="BC27" s="9" t="n"/>
-      <c r="BD27" s="11" t="n">
+      <c r="BI27" s="9" t="n"/>
+      <c r="BJ27" s="11" t="n">
         <v>0.0049436734448703</v>
       </c>
-      <c r="BE27" s="10" t="n">
+      <c r="BK27" s="10" t="n">
         <v>0.47680047150071</v>
       </c>
-      <c r="BF27" s="9" t="n"/>
-      <c r="BG27" s="11" t="n">
+      <c r="BL27" s="9" t="n"/>
+      <c r="BM27" s="11" t="n">
         <v>1.29820904827584e-11</v>
       </c>
-      <c r="BH27" s="10" t="n">
+      <c r="BN27" s="10" t="n">
         <v>0.306216610417165</v>
       </c>
-      <c r="BI27" s="11" t="n">
+      <c r="BO27" s="11" t="n">
         <v>0.245848928862128</v>
       </c>
-      <c r="BJ27" s="11" t="n">
+      <c r="BP27" s="11" t="n">
         <v>0.291959261297603</v>
       </c>
-      <c r="BK27" s="10" t="n">
+      <c r="BQ27" s="10" t="n">
         <v>1.19639719691927</v>
       </c>
-      <c r="BL27" s="11" t="n">
+      <c r="BR27" s="11" t="n">
         <v>5.94894257428176e-05</v>
       </c>
-      <c r="BM27" s="11" t="n">
+      <c r="BS27" s="11" t="n">
         <v>0.000162699038229</v>
       </c>
-      <c r="BN27" s="9" t="b">
+      <c r="BT27" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO27" s="9" t="inlineStr">
+      <c r="BU27" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP27" s="9" t="b">
+      <c r="BV27" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5754,73 +6210,91 @@
         <v>4.22011221401253e-14</v>
       </c>
       <c r="AS28" s="10" t="n">
+        <v>-4.42313704186632</v>
+      </c>
+      <c r="AT28" s="11" t="n">
+        <v>0.0001105929974669</v>
+      </c>
+      <c r="AU28" s="11" t="n">
+        <v>0.000420721259671</v>
+      </c>
+      <c r="AV28" s="10" t="n">
+        <v>-5.36898559914467</v>
+      </c>
+      <c r="AW28" s="11" t="n">
+        <v>5.2417600981097e-07</v>
+      </c>
+      <c r="AX28" s="11" t="n">
+        <v>4.34008926442646e-05</v>
+      </c>
+      <c r="AY28" s="10" t="n">
         <v>-0.6552177121301619</v>
       </c>
-      <c r="AT28" s="11" t="n">
+      <c r="AZ28" s="11" t="n">
         <v>0.8896214474357068</v>
       </c>
-      <c r="AU28" s="11" t="n">
+      <c r="BA28" s="11" t="n">
         <v>0.9048578065814614</v>
       </c>
-      <c r="AV28" s="10" t="n">
+      <c r="BB28" s="10" t="n">
         <v>-0.5672384978231418</v>
       </c>
-      <c r="AW28" s="11" t="n">
+      <c r="BC28" s="11" t="n">
         <v>0.5682541849402357</v>
       </c>
-      <c r="AX28" s="11" t="n">
+      <c r="BD28" s="11" t="n">
         <v>0.6228608405432813</v>
       </c>
-      <c r="AY28" s="10" t="n">
+      <c r="BE28" s="10" t="n">
         <v>1.86614372016981</v>
       </c>
-      <c r="AZ28" s="11" t="n">
+      <c r="BF28" s="11" t="n">
         <v>2.35138149658914e-12</v>
       </c>
-      <c r="BA28" s="11" t="n">
+      <c r="BG28" s="11" t="n">
         <v>7.043156725764669e-12</v>
       </c>
-      <c r="BB28" s="10" t="n">
+      <c r="BH28" s="10" t="n">
         <v>1.5877270721957</v>
       </c>
-      <c r="BC28" s="9" t="n"/>
-      <c r="BD28" s="11" t="n">
+      <c r="BI28" s="9" t="n"/>
+      <c r="BJ28" s="11" t="n">
         <v>2.52111838606823e-06</v>
       </c>
-      <c r="BE28" s="10" t="n">
+      <c r="BK28" s="10" t="n">
         <v>2.44730481665509</v>
       </c>
-      <c r="BF28" s="9" t="n"/>
-      <c r="BG28" s="11" t="n">
+      <c r="BL28" s="9" t="n"/>
+      <c r="BM28" s="11" t="n">
         <v>1.66570347973818e-90</v>
       </c>
-      <c r="BH28" s="10" t="n">
+      <c r="BN28" s="10" t="n">
         <v>2.79300302421463</v>
       </c>
-      <c r="BI28" s="11" t="n">
+      <c r="BO28" s="11" t="n">
         <v>3.00157626785448e-10</v>
       </c>
-      <c r="BJ28" s="11" t="n">
+      <c r="BP28" s="11" t="n">
         <v>1.23803437643529e-09</v>
       </c>
-      <c r="BK28" s="10" t="n">
+      <c r="BQ28" s="10" t="n">
         <v>3.02209759317698</v>
       </c>
-      <c r="BL28" s="11" t="n">
+      <c r="BR28" s="11" t="n">
         <v>3.94351021309102e-11</v>
       </c>
-      <c r="BM28" s="11" t="n">
+      <c r="BS28" s="11" t="n">
         <v>3.49501823523855e-10</v>
       </c>
-      <c r="BN28" s="9" t="b">
+      <c r="BT28" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO28" s="9" t="inlineStr">
+      <c r="BU28" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP28" s="9" t="b">
+      <c r="BV28" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5950,73 +6424,91 @@
         <v>0.0001579913205222</v>
       </c>
       <c r="AS29" s="10" t="n">
+        <v>4.60870340081624</v>
+      </c>
+      <c r="AT29" s="11" t="n">
+        <v>0.0009938882062471</v>
+      </c>
+      <c r="AU29" s="11" t="n">
+        <v>0.0026278463012141</v>
+      </c>
+      <c r="AV29" s="10" t="n">
+        <v>3.77244850880328</v>
+      </c>
+      <c r="AW29" s="11" t="n">
+        <v>0.0487053185833195</v>
+      </c>
+      <c r="AX29" s="11" t="n">
+        <v>0.085894666905575</v>
+      </c>
+      <c r="AY29" s="10" t="n">
         <v>0.5492432189145007</v>
       </c>
-      <c r="AT29" s="11" t="n">
+      <c r="AZ29" s="11" t="n">
         <v>0.8563902952311907</v>
       </c>
-      <c r="AU29" s="11" t="n">
+      <c r="BA29" s="11" t="n">
         <v>0.8760964094934844</v>
       </c>
-      <c r="AV29" s="10" t="n">
+      <c r="BB29" s="10" t="n">
         <v>0.5301680661914108</v>
       </c>
-      <c r="AW29" s="11" t="n">
+      <c r="BC29" s="11" t="n">
         <v>0.8471226044731817</v>
       </c>
-      <c r="AX29" s="11" t="n">
+      <c r="BD29" s="11" t="n">
         <v>0.8721505542507694</v>
       </c>
-      <c r="AY29" s="10" t="n">
+      <c r="BE29" s="10" t="n">
         <v>3.09412145953728</v>
       </c>
-      <c r="AZ29" s="11" t="n">
+      <c r="BF29" s="11" t="n">
         <v>1.13067327573803e-14</v>
       </c>
-      <c r="BA29" s="11" t="n">
+      <c r="BG29" s="11" t="n">
         <v>4.06154837206612e-14</v>
       </c>
-      <c r="BB29" s="10" t="n">
+      <c r="BH29" s="10" t="n">
         <v>1.84488141293706</v>
       </c>
-      <c r="BC29" s="9" t="n"/>
-      <c r="BD29" s="11" t="n">
+      <c r="BI29" s="9" t="n"/>
+      <c r="BJ29" s="11" t="n">
         <v>3.94250145793433e-05</v>
       </c>
-      <c r="BE29" s="10" t="n">
+      <c r="BK29" s="10" t="n">
         <v>4.30167686903167</v>
       </c>
-      <c r="BF29" s="9" t="n"/>
-      <c r="BG29" s="11" t="n">
+      <c r="BL29" s="9" t="n"/>
+      <c r="BM29" s="11" t="n">
         <v>4.35337184170717e-125</v>
       </c>
-      <c r="BH29" s="10" t="n">
+      <c r="BN29" s="10" t="n">
         <v>1.07357998097036</v>
       </c>
-      <c r="BI29" s="11" t="n">
+      <c r="BO29" s="11" t="n">
         <v>0.0078012924588847</v>
       </c>
-      <c r="BJ29" s="11" t="n">
+      <c r="BP29" s="11" t="n">
         <v>0.0120441006382782</v>
       </c>
-      <c r="BK29" s="10" t="n">
+      <c r="BQ29" s="10" t="n">
         <v>3.77985191517593</v>
       </c>
-      <c r="BL29" s="11" t="n">
+      <c r="BR29" s="11" t="n">
         <v>5.517907573401879e-13</v>
       </c>
-      <c r="BM29" s="11" t="n">
+      <c r="BS29" s="11" t="n">
         <v>7.060458342359139e-12</v>
       </c>
-      <c r="BN29" s="9" t="b">
+      <c r="BT29" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO29" s="9" t="inlineStr">
+      <c r="BU29" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP29" s="9" t="b">
+      <c r="BV29" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6109,12 +6601,18 @@
       <c r="BL30" s="9" t="n"/>
       <c r="BM30" s="9" t="n"/>
       <c r="BN30" s="9" t="n"/>
-      <c r="BO30" s="9" t="inlineStr">
+      <c r="BO30" s="9" t="n"/>
+      <c r="BP30" s="9" t="n"/>
+      <c r="BQ30" s="9" t="n"/>
+      <c r="BR30" s="9" t="n"/>
+      <c r="BS30" s="9" t="n"/>
+      <c r="BT30" s="9" t="n"/>
+      <c r="BU30" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP30" s="9" t="n"/>
+      <c r="BV30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -6248,73 +6746,91 @@
         <v>0.963728799299727</v>
       </c>
       <c r="AS31" s="10" t="n">
+        <v>-1.75635149569843</v>
+      </c>
+      <c r="AT31" s="11" t="n">
+        <v>5.75378576490692e-07</v>
+      </c>
+      <c r="AU31" s="11" t="n">
+        <v>9.344496796497621e-06</v>
+      </c>
+      <c r="AV31" s="10" t="n">
+        <v>-1.94461463743154</v>
+      </c>
+      <c r="AW31" s="11" t="n">
+        <v>4.3012987716501e-05</v>
+      </c>
+      <c r="AX31" s="11" t="n">
+        <v>0.0008272094365075</v>
+      </c>
+      <c r="AY31" s="10" t="n">
         <v>-1.178109639071032</v>
       </c>
-      <c r="AT31" s="11" t="n">
+      <c r="AZ31" s="11" t="n">
         <v>0.0319049923104646</v>
       </c>
-      <c r="AU31" s="11" t="n">
+      <c r="BA31" s="11" t="n">
         <v>0.0465145971982554</v>
       </c>
-      <c r="AV31" s="10" t="n">
+      <c r="BB31" s="10" t="n">
         <v>-1.231963995023502</v>
       </c>
-      <c r="AW31" s="11" t="n">
+      <c r="BC31" s="11" t="n">
         <v>0.2318240367298447</v>
       </c>
-      <c r="AX31" s="11" t="n">
+      <c r="BD31" s="11" t="n">
         <v>0.2908141575557005</v>
       </c>
-      <c r="AY31" s="10" t="n">
+      <c r="BE31" s="10" t="n">
         <v>-1.74925086901342</v>
       </c>
-      <c r="AZ31" s="11" t="n">
+      <c r="BF31" s="11" t="n">
         <v>6.36003999521039e-38</v>
       </c>
-      <c r="BA31" s="11" t="n">
+      <c r="BG31" s="11" t="n">
         <v>9.431049843581169e-37</v>
       </c>
-      <c r="BB31" s="10" t="n">
+      <c r="BH31" s="10" t="n">
         <v>-1.88846389833827</v>
       </c>
-      <c r="BC31" s="9" t="n"/>
-      <c r="BD31" s="11" t="n">
+      <c r="BI31" s="9" t="n"/>
+      <c r="BJ31" s="11" t="n">
         <v>2.95314931935462e-13</v>
       </c>
-      <c r="BE31" s="10" t="n">
+      <c r="BK31" s="10" t="n">
         <v>-0.6410066519484749</v>
       </c>
-      <c r="BF31" s="9" t="n"/>
-      <c r="BG31" s="11" t="n">
+      <c r="BL31" s="9" t="n"/>
+      <c r="BM31" s="11" t="n">
         <v>7.929595445820981e-23</v>
       </c>
-      <c r="BH31" s="10" t="n">
+      <c r="BN31" s="10" t="n">
         <v>-2.35874899425477</v>
       </c>
-      <c r="BI31" s="11" t="n">
+      <c r="BO31" s="11" t="n">
         <v>2.72833850957663e-16</v>
       </c>
-      <c r="BJ31" s="11" t="n">
+      <c r="BP31" s="11" t="n">
         <v>2.80978715744486e-15</v>
       </c>
-      <c r="BK31" s="10" t="n">
+      <c r="BQ31" s="10" t="n">
         <v>2.91285918504908</v>
       </c>
-      <c r="BL31" s="11" t="n">
+      <c r="BR31" s="11" t="n">
         <v>1.96116945597289e-18</v>
       </c>
-      <c r="BM31" s="11" t="n">
+      <c r="BS31" s="11" t="n">
         <v>7.82883550795194e-17</v>
       </c>
-      <c r="BN31" s="9" t="b">
+      <c r="BT31" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO31" s="9" t="inlineStr">
+      <c r="BU31" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP31" s="9" t="b">
+      <c r="BV31" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6450,73 +6966,91 @@
         <v>0.0989616230115437</v>
       </c>
       <c r="AS32" s="10" t="n">
+        <v>1.21874507189201</v>
+      </c>
+      <c r="AT32" s="11" t="n">
+        <v>0.0323689747991591</v>
+      </c>
+      <c r="AU32" s="11" t="n">
+        <v>0.0528768238047468</v>
+      </c>
+      <c r="AV32" s="10" t="n">
+        <v>3.25558751458416</v>
+      </c>
+      <c r="AW32" s="11" t="n">
+        <v>1.17729796818674e-05</v>
+      </c>
+      <c r="AX32" s="11" t="n">
+        <v>0.0003613681271197</v>
+      </c>
+      <c r="AY32" s="10" t="n">
         <v>1.66989295710482</v>
       </c>
-      <c r="AT32" s="11" t="n">
+      <c r="AZ32" s="11" t="n">
         <v>0.0059489757735426</v>
       </c>
-      <c r="AU32" s="11" t="n">
+      <c r="BA32" s="11" t="n">
         <v>0.0103141501537805</v>
       </c>
-      <c r="AV32" s="10" t="n">
+      <c r="BB32" s="10" t="n">
         <v>1.515895609620146</v>
       </c>
-      <c r="AW32" s="11" t="n">
+      <c r="BC32" s="11" t="n">
         <v>0.0470673900072015</v>
       </c>
-      <c r="AX32" s="11" t="n">
+      <c r="BD32" s="11" t="n">
         <v>0.0738912913570226</v>
       </c>
-      <c r="AY32" s="10" t="n">
+      <c r="BE32" s="10" t="n">
         <v>0.858694131588708</v>
       </c>
-      <c r="AZ32" s="11" t="n">
+      <c r="BF32" s="11" t="n">
         <v>1.2510591854259e-09</v>
       </c>
-      <c r="BA32" s="11" t="n">
+      <c r="BG32" s="11" t="n">
         <v>3.02692573267152e-09</v>
       </c>
-      <c r="BB32" s="10" t="n">
+      <c r="BH32" s="10" t="n">
         <v>0.792217431423037</v>
       </c>
-      <c r="BC32" s="9" t="n"/>
-      <c r="BD32" s="11" t="n">
+      <c r="BI32" s="9" t="n"/>
+      <c r="BJ32" s="11" t="n">
         <v>8.7223659275522e-06</v>
       </c>
-      <c r="BE32" s="10" t="n">
+      <c r="BK32" s="10" t="n">
         <v>2.82911022583707</v>
       </c>
-      <c r="BF32" s="9" t="n"/>
-      <c r="BG32" s="11" t="n">
+      <c r="BL32" s="9" t="n"/>
+      <c r="BM32" s="11" t="n">
         <v>6.671838293558619e-192</v>
       </c>
-      <c r="BH32" s="10" t="n">
+      <c r="BN32" s="10" t="n">
         <v>0.489424717717857</v>
       </c>
-      <c r="BI32" s="11" t="n">
+      <c r="BO32" s="11" t="n">
         <v>0.0045040967367715</v>
       </c>
-      <c r="BJ32" s="11" t="n">
+      <c r="BP32" s="11" t="n">
         <v>0.0071971518586055</v>
       </c>
-      <c r="BK32" s="10" t="n">
+      <c r="BQ32" s="10" t="n">
         <v>2.2350450017259</v>
       </c>
-      <c r="BL32" s="11" t="n">
+      <c r="BR32" s="11" t="n">
         <v>2.04608210820322e-25</v>
       </c>
-      <c r="BM32" s="11" t="n">
+      <c r="BS32" s="11" t="n">
         <v>3.71169654337473e-23</v>
       </c>
-      <c r="BN32" s="9" t="b">
+      <c r="BT32" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO32" s="9" t="inlineStr">
+      <c r="BU32" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP32" s="9" t="b">
+      <c r="BV32" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6621,72 +7155,84 @@
       <c r="AP33" s="9" t="n"/>
       <c r="AQ33" s="9" t="n"/>
       <c r="AR33" s="9" t="n"/>
-      <c r="AS33" s="10" t="n">
+      <c r="AS33" s="9" t="n"/>
+      <c r="AT33" s="9" t="n"/>
+      <c r="AU33" s="9" t="n"/>
+      <c r="AV33" s="10" t="n">
+        <v>-5.57720947557638</v>
+      </c>
+      <c r="AW33" s="11" t="n">
+        <v>1.70221974429232e-05</v>
+      </c>
+      <c r="AX33" s="11" t="n">
+        <v>0.0004611907737996</v>
+      </c>
+      <c r="AY33" s="10" t="n">
         <v>0.6677299608911785</v>
       </c>
-      <c r="AT33" s="11" t="n">
+      <c r="AZ33" s="11" t="n">
         <v>0.0090076162369357</v>
       </c>
-      <c r="AU33" s="11" t="n">
+      <c r="BA33" s="11" t="n">
         <v>0.0149139762765367</v>
       </c>
-      <c r="AV33" s="10" t="n">
+      <c r="BB33" s="10" t="n">
         <v>0.0775316054593175</v>
       </c>
-      <c r="AW33" s="11" t="n">
+      <c r="BC33" s="11" t="n">
         <v>0.0340117473177784</v>
       </c>
-      <c r="AX33" s="11" t="n">
+      <c r="BD33" s="11" t="n">
         <v>0.0560361523363937</v>
       </c>
-      <c r="AY33" s="10" t="n">
+      <c r="BE33" s="10" t="n">
         <v>7.50348409592738</v>
       </c>
-      <c r="AZ33" s="11" t="n">
+      <c r="BF33" s="11" t="n">
         <v>2.07979190648398e-41</v>
       </c>
-      <c r="BA33" s="11" t="n">
+      <c r="BG33" s="11" t="n">
         <v>3.60531351754604e-40</v>
       </c>
-      <c r="BB33" s="10" t="n">
+      <c r="BH33" s="10" t="n">
         <v>6.2725821018296</v>
       </c>
-      <c r="BC33" s="9" t="n"/>
-      <c r="BD33" s="11" t="n">
+      <c r="BI33" s="9" t="n"/>
+      <c r="BJ33" s="11" t="n">
         <v>1.16929054210059e-23</v>
       </c>
-      <c r="BE33" s="10" t="n">
+      <c r="BK33" s="10" t="n">
         <v>8.87923777216338</v>
       </c>
-      <c r="BF33" s="9" t="n"/>
-      <c r="BG33" s="11" t="n">
+      <c r="BL33" s="9" t="n"/>
+      <c r="BM33" s="11" t="n">
         <v>3.019877447075451e-319</v>
       </c>
-      <c r="BH33" s="10" t="n">
+      <c r="BN33" s="10" t="n">
         <v>12.3327491631417</v>
       </c>
-      <c r="BI33" s="11" t="n">
+      <c r="BO33" s="11" t="n">
         <v>3.986399857367541e-15</v>
       </c>
-      <c r="BJ33" s="11" t="n">
+      <c r="BP33" s="11" t="n">
         <v>3.34003034799734e-14</v>
       </c>
-      <c r="BK33" s="10" t="n">
+      <c r="BQ33" s="10" t="n">
         <v>11.8477425359168</v>
       </c>
-      <c r="BL33" s="11" t="n">
+      <c r="BR33" s="11" t="n">
         <v>6.19578584296296e-13</v>
       </c>
-      <c r="BM33" s="11" t="n">
+      <c r="BS33" s="11" t="n">
         <v>7.843799197482519e-12</v>
       </c>
-      <c r="BN33" s="9" t="n"/>
-      <c r="BO33" s="9" t="inlineStr">
+      <c r="BT33" s="9" t="n"/>
+      <c r="BU33" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP33" s="9" t="b">
+      <c r="BV33" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6809,48 +7355,66 @@
       <c r="AR34" s="11" t="n">
         <v>0.0020650361945235</v>
       </c>
-      <c r="AS34" s="9" t="n"/>
-      <c r="AT34" s="9" t="n"/>
-      <c r="AU34" s="9" t="n"/>
-      <c r="AV34" s="9" t="n"/>
-      <c r="AW34" s="9" t="n"/>
-      <c r="AX34" s="9" t="n"/>
-      <c r="AY34" s="10" t="n">
+      <c r="AS34" s="10" t="n">
+        <v>1.04618873282607</v>
+      </c>
+      <c r="AT34" s="11" t="n">
+        <v>0.11438310570669</v>
+      </c>
+      <c r="AU34" s="11" t="n">
+        <v>0.159260318176358</v>
+      </c>
+      <c r="AV34" s="10" t="n">
+        <v>1.57156777466251</v>
+      </c>
+      <c r="AW34" s="11" t="n">
+        <v>0.156706514076548</v>
+      </c>
+      <c r="AX34" s="11" t="n">
+        <v>0.223739933806149</v>
+      </c>
+      <c r="AY34" s="9" t="n"/>
+      <c r="AZ34" s="9" t="n"/>
+      <c r="BA34" s="9" t="n"/>
+      <c r="BB34" s="9" t="n"/>
+      <c r="BC34" s="9" t="n"/>
+      <c r="BD34" s="9" t="n"/>
+      <c r="BE34" s="10" t="n">
         <v>-1.27178811089417</v>
       </c>
-      <c r="AZ34" s="11" t="n">
+      <c r="BF34" s="11" t="n">
         <v>3.47533264264383e-08</v>
       </c>
-      <c r="BA34" s="11" t="n">
+      <c r="BG34" s="11" t="n">
         <v>7.454995577511909e-08</v>
       </c>
-      <c r="BB34" s="10" t="n">
+      <c r="BH34" s="10" t="n">
         <v>-1.9394683901759</v>
       </c>
-      <c r="BC34" s="9" t="n"/>
-      <c r="BD34" s="11" t="n">
+      <c r="BI34" s="9" t="n"/>
+      <c r="BJ34" s="11" t="n">
         <v>3.93681519092414e-09</v>
       </c>
-      <c r="BE34" s="10" t="n">
+      <c r="BK34" s="10" t="n">
         <v>-2.33466929424159</v>
       </c>
-      <c r="BF34" s="9" t="n"/>
-      <c r="BG34" s="11" t="n">
+      <c r="BL34" s="9" t="n"/>
+      <c r="BM34" s="11" t="n">
         <v>2.04373879451104e-93</v>
       </c>
-      <c r="BH34" s="9" t="n"/>
-      <c r="BI34" s="9" t="n"/>
-      <c r="BJ34" s="9" t="n"/>
-      <c r="BK34" s="9" t="n"/>
-      <c r="BL34" s="9" t="n"/>
-      <c r="BM34" s="9" t="n"/>
       <c r="BN34" s="9" t="n"/>
-      <c r="BO34" s="9" t="inlineStr">
+      <c r="BO34" s="9" t="n"/>
+      <c r="BP34" s="9" t="n"/>
+      <c r="BQ34" s="9" t="n"/>
+      <c r="BR34" s="9" t="n"/>
+      <c r="BS34" s="9" t="n"/>
+      <c r="BT34" s="9" t="n"/>
+      <c r="BU34" s="9" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="BP34" s="9" t="b">
+      <c r="BV34" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6980,84 +7544,104 @@
         <v>0.469746578667011</v>
       </c>
       <c r="AS35" s="10" t="n">
+        <v>-0.579020339417653</v>
+      </c>
+      <c r="AT35" s="11" t="n">
+        <v>0.0168173382314359</v>
+      </c>
+      <c r="AU35" s="11" t="n">
+        <v>0.0299736755961283</v>
+      </c>
+      <c r="AV35" s="10" t="n">
+        <v>-0.958417392223053</v>
+      </c>
+      <c r="AW35" s="11" t="n">
+        <v>0.009575904943963799</v>
+      </c>
+      <c r="AX35" s="11" t="n">
+        <v>0.0250143299308482</v>
+      </c>
+      <c r="AY35" s="10" t="n">
         <v>-1.13213135656537</v>
       </c>
-      <c r="AT35" s="11" t="n">
+      <c r="AZ35" s="11" t="n">
         <v>0.0061878899008261</v>
       </c>
-      <c r="AU35" s="11" t="n">
+      <c r="BA35" s="11" t="n">
         <v>0.0106806697388081</v>
       </c>
-      <c r="AV35" s="10" t="n">
+      <c r="BB35" s="10" t="n">
         <v>-1.169406912519067</v>
       </c>
-      <c r="AW35" s="11" t="n">
+      <c r="BC35" s="11" t="n">
         <v>0.012042090787275</v>
       </c>
-      <c r="AX35" s="11" t="n">
+      <c r="BD35" s="11" t="n">
         <v>0.0229889199229861</v>
       </c>
-      <c r="AY35" s="10" t="n">
+      <c r="BE35" s="10" t="n">
         <v>0.634213019981918</v>
       </c>
-      <c r="AZ35" s="11" t="n">
+      <c r="BF35" s="11" t="n">
         <v>1.60323395018238e-07</v>
       </c>
-      <c r="BA35" s="11" t="n">
+      <c r="BG35" s="11" t="n">
         <v>3.25470455128078e-07</v>
       </c>
-      <c r="BB35" s="10" t="n">
+      <c r="BH35" s="10" t="n">
         <v>0.6112254293068889</v>
       </c>
-      <c r="BC35" s="9" t="n"/>
-      <c r="BD35" s="11" t="n">
+      <c r="BI35" s="9" t="n"/>
+      <c r="BJ35" s="11" t="n">
         <v>0.000321774337265</v>
       </c>
-      <c r="BE35" s="10" t="n">
+      <c r="BK35" s="10" t="n">
         <v>1.3898930738796</v>
       </c>
-      <c r="BF35" s="9" t="n"/>
-      <c r="BG35" s="11" t="n">
+      <c r="BL35" s="9" t="n"/>
+      <c r="BM35" s="11" t="n">
         <v>4.01779084547098e-66</v>
       </c>
-      <c r="BH35" s="10" t="n">
+      <c r="BN35" s="10" t="n">
         <v>-0.236428784750778</v>
       </c>
-      <c r="BI35" s="11" t="n">
+      <c r="BO35" s="11" t="n">
         <v>0.184853802115731</v>
       </c>
-      <c r="BJ35" s="11" t="n">
+      <c r="BP35" s="11" t="n">
         <v>0.225201979266582</v>
       </c>
-      <c r="BK35" s="10" t="n">
+      <c r="BQ35" s="10" t="n">
         <v>1.47555776466522</v>
       </c>
-      <c r="BL35" s="11" t="n">
+      <c r="BR35" s="11" t="n">
         <v>2.71003026009481e-14</v>
       </c>
-      <c r="BM35" s="11" t="n">
+      <c r="BS35" s="11" t="n">
         <v>4.41418137350751e-13</v>
       </c>
-      <c r="BN35" s="9" t="b">
+      <c r="BT35" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="BO35" s="9" t="inlineStr">
+      <c r="BU35" s="9" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="BP35" s="9" t="b">
+      <c r="BV35" s="9" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="74">
     <mergeCell ref="U2:W2"/>
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="BE1:BG1"/>
     <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="BQ1:BS1"/>
     <mergeCell ref="AP1:AR1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="X3:Z3"/>
@@ -7070,6 +7654,7 @@
     <mergeCell ref="AM1:AO1"/>
     <mergeCell ref="AS2:AU2"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BV1:BV4"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="AY2:BA2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -7078,9 +7663,11 @@
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="BE2:BG2"/>
     <mergeCell ref="AY1:BA1"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="BH1:BJ1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="BO1:BO4"/>
+    <mergeCell ref="BQ2:BS2"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="O2:Q2"/>
@@ -7089,15 +7676,15 @@
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BU1:BU4"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="BB2:BD2"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="BK1:BM1"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="U1:W1"/>
-    <mergeCell ref="BN1:BN4"/>
-    <mergeCell ref="BP1:BP4"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="BN2:BP2"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="BH3:BJ3"/>
     <mergeCell ref="R1:T1"/>
@@ -7107,6 +7694,7 @@
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="BT1:BT4"/>
     <mergeCell ref="AV1:AX1"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA1:AC1"/>
@@ -7349,6 +7937,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BN5:BN35">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="num" val="-3"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="002166AC"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00B2182B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BQ5:BQ35">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="num" val="-3"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="002166AC"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00B2182B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7359,7 +7971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7382,6 +7994,8 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -7452,35 +8066,45 @@
       </c>
       <c r="N1" s="12" t="inlineStr">
         <is>
+          <t>S2 (benchmark v2) | H-bulk1 Roadmap fetal SI vs HPA adult SI [tier B]</t>
+        </is>
+      </c>
+      <c r="O1" s="12" t="inlineStr">
+        <is>
+          <t>S2 (benchmark v2) | H-bulk2 Roadmap fetal SI vs HPA duodenum [tier B subset]</t>
+        </is>
+      </c>
+      <c r="P1" s="12" t="inlineStr">
+        <is>
           <t>S2 (benchmark v2) | H-new3 Gao fetal + Wang adult</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="Q1" s="12" t="inlineStr">
         <is>
           <t>S2 (benchmark v2) | H-new3-debug</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>S3 | TCGA COAD+READ (T1)</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>S3 | TCGA paired</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>S3 | TCGA vs GTEx</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>S3 | Pelka 2021 (S2, GSE178341)</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="V1" s="12" t="inlineStr">
         <is>
           <t>S3 | Pelka progenitor check (P)</t>
         </is>
@@ -7525,24 +8149,30 @@
         <v>3.97442756852635</v>
       </c>
       <c r="N2" s="10" t="n">
+        <v>2.49150763377401</v>
+      </c>
+      <c r="O2" s="10" t="n">
+        <v>2.38341298830727</v>
+      </c>
+      <c r="P2" s="10" t="n">
         <v>1.809666668472633</v>
       </c>
-      <c r="O2" s="10" t="n">
+      <c r="Q2" s="10" t="n">
         <v>1.225924077307709</v>
       </c>
-      <c r="P2" s="10" t="n">
+      <c r="R2" s="10" t="n">
         <v>5.05028632487126</v>
       </c>
-      <c r="Q2" s="10" t="n">
+      <c r="S2" s="10" t="n">
         <v>3.73497284492898</v>
       </c>
-      <c r="R2" s="10" t="n">
+      <c r="T2" s="10" t="n">
         <v>4.69300181571387</v>
       </c>
-      <c r="S2" s="10" t="n">
+      <c r="U2" s="10" t="n">
         <v>4.25904379124654</v>
       </c>
-      <c r="T2" s="10" t="n">
+      <c r="V2" s="10" t="n">
         <v>6.05919277196155</v>
       </c>
     </row>
@@ -7589,22 +8219,28 @@
         <v>2.91235682288114</v>
       </c>
       <c r="N3" s="10" t="n">
+        <v>0.551810476317118</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>0.582171411052016</v>
+      </c>
+      <c r="P3" s="10" t="n">
         <v>4.649560425991364</v>
       </c>
-      <c r="O3" s="10" t="n">
+      <c r="Q3" s="10" t="n">
         <v>3.542088757094501</v>
       </c>
-      <c r="P3" s="10" t="n">
+      <c r="R3" s="10" t="n">
         <v>-0.0025247870000847</v>
       </c>
-      <c r="Q3" s="10" t="n">
+      <c r="S3" s="10" t="n">
         <v>-0.222650205328684</v>
       </c>
-      <c r="R3" s="10" t="n">
+      <c r="T3" s="10" t="n">
         <v>-0.433294511714691</v>
       </c>
-      <c r="S3" s="9" t="n"/>
-      <c r="T3" s="9" t="n"/>
+      <c r="U3" s="9" t="n"/>
+      <c r="V3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -7649,24 +8285,30 @@
         <v>-0.951123854344823</v>
       </c>
       <c r="N4" s="10" t="n">
+        <v>-2.66331617979916</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>-2.42300499114636</v>
+      </c>
+      <c r="P4" s="10" t="n">
         <v>2.822503672938254</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="Q4" s="10" t="n">
         <v>2.831192780929209</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="R4" s="10" t="n">
         <v>0.208594387468698</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="S4" s="10" t="n">
         <v>-0.246222685380311</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="T4" s="10" t="n">
         <v>-0.643732616070441</v>
       </c>
-      <c r="S4" s="10" t="n">
+      <c r="U4" s="10" t="n">
         <v>2.84220968978987</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="V4" s="10" t="n">
         <v>4.55185303250578</v>
       </c>
     </row>
@@ -7713,24 +8355,30 @@
         <v>2.25215980022266</v>
       </c>
       <c r="N5" s="10" t="n">
+        <v>0.144071265340153</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>0.0263466855177204</v>
+      </c>
+      <c r="P5" s="10" t="n">
         <v>4.728578253609251</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="Q5" s="10" t="n">
         <v>4.036794130783478</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="R5" s="10" t="n">
         <v>-2.31154743014523</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="S5" s="10" t="n">
         <v>-2.65163850649463</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="T5" s="10" t="n">
         <v>-2.77393099960309</v>
       </c>
-      <c r="S5" s="10" t="n">
+      <c r="U5" s="10" t="n">
         <v>1.49510505291086</v>
       </c>
-      <c r="T5" s="10" t="n">
+      <c r="V5" s="10" t="n">
         <v>1.48820795285742</v>
       </c>
     </row>
@@ -7777,24 +8425,30 @@
         <v>1.68545772462972</v>
       </c>
       <c r="N6" s="10" t="n">
+        <v>2.10328940421391</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>1.85976014712011</v>
+      </c>
+      <c r="P6" s="10" t="n">
         <v>1.274542365098686</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="Q6" s="10" t="n">
         <v>1.286101407764752</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="R6" s="10" t="n">
         <v>1.67776809443425</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="S6" s="10" t="n">
         <v>1.35884211776825</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="T6" s="10" t="n">
         <v>1.93451996054779</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="U6" s="10" t="n">
         <v>1.65228981386363</v>
       </c>
-      <c r="T6" s="10" t="n">
+      <c r="V6" s="10" t="n">
         <v>2.02638428887108</v>
       </c>
     </row>
@@ -7841,24 +8495,30 @@
         <v>2.70116554192647</v>
       </c>
       <c r="N7" s="10" t="n">
+        <v>-0.0250470388771509</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.244118586704112</v>
+      </c>
+      <c r="P7" s="10" t="n">
         <v>5.289242341489805</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="Q7" s="10" t="n">
         <v>5.606537428292589</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="R7" s="10" t="n">
         <v>-0.332774350351039</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="S7" s="10" t="n">
         <v>-0.287899078091318</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="T7" s="10" t="n">
         <v>-0.870991369969248</v>
       </c>
-      <c r="S7" s="10" t="n">
+      <c r="U7" s="10" t="n">
         <v>2.95811168926125</v>
       </c>
-      <c r="T7" s="10" t="n">
+      <c r="V7" s="10" t="n">
         <v>3.09931636991049</v>
       </c>
     </row>
@@ -7887,6 +8547,8 @@
       <c r="R8" s="9" t="n"/>
       <c r="S8" s="9" t="n"/>
       <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -7930,21 +8592,27 @@
       <c r="M9" s="10" t="n">
         <v>7.22803330357202</v>
       </c>
-      <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="10" t="n">
+      <c r="N9" s="10" t="n">
+        <v>0.309396815473826</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>0.296063355092614</v>
+      </c>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="10" t="n">
         <v>3.87915708772113</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="S9" s="10" t="n">
         <v>3.31849537880916</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="T9" s="10" t="n">
         <v>2.96080985389408</v>
       </c>
-      <c r="S9" s="10" t="n">
+      <c r="U9" s="10" t="n">
         <v>6.12870673194068</v>
       </c>
-      <c r="T9" s="10" t="n">
+      <c r="V9" s="10" t="n">
         <v>6.65778199848213</v>
       </c>
     </row>
@@ -7974,13 +8642,15 @@
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="10" t="n">
         <v>7.36478688339062</v>
       </c>
-      <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="9" t="n"/>
       <c r="S10" s="9" t="n"/>
       <c r="T10" s="9" t="n"/>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -8023,24 +8693,30 @@
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="10" t="n">
+        <v>-0.934250626130547</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>-0.686465475508208</v>
+      </c>
+      <c r="P11" s="10" t="n">
         <v>1.361607086331125</v>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="Q11" s="10" t="n">
         <v>0.7149986708156708</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="R11" s="10" t="n">
         <v>0.745426223148137</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="S11" s="10" t="n">
         <v>-0.0554276379201352</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="T11" s="10" t="n">
         <v>0.654734068205669</v>
       </c>
-      <c r="S11" s="10" t="n">
+      <c r="U11" s="10" t="n">
         <v>4.55190891741079</v>
       </c>
-      <c r="T11" s="10" t="n">
+      <c r="V11" s="10" t="n">
         <v>4.66154103734362</v>
       </c>
     </row>
@@ -8083,24 +8759,30 @@
         <v>-1.13058823529903</v>
       </c>
       <c r="N12" s="10" t="n">
+        <v>1.78110727990936</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>2.01131734338605</v>
+      </c>
+      <c r="P12" s="10" t="n">
         <v>-8.152040929132102</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="Q12" s="10" t="n">
         <v>-8.152040929132102</v>
       </c>
-      <c r="P12" s="10" t="n">
+      <c r="R12" s="10" t="n">
         <v>2.02713488622674</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="S12" s="10" t="n">
         <v>1.67806283998944</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="T12" s="10" t="n">
         <v>2.23031464377784</v>
       </c>
-      <c r="S12" s="10" t="n">
+      <c r="U12" s="10" t="n">
         <v>1.34994899681148</v>
       </c>
-      <c r="T12" s="10" t="n">
+      <c r="V12" s="10" t="n">
         <v>0.819685047138303</v>
       </c>
     </row>
@@ -8147,24 +8829,30 @@
         <v>6.34182672745528</v>
       </c>
       <c r="N13" s="10" t="n">
+        <v>-1.20048396253347</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>-0.158803457090108</v>
+      </c>
+      <c r="P13" s="10" t="n">
         <v>3.838225434786347</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="Q13" s="10" t="n">
         <v>3.145383862021159</v>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>0.221508245845491</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="S13" s="10" t="n">
         <v>0.438961218681568</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="T13" s="10" t="n">
         <v>-0.963225217532367</v>
       </c>
-      <c r="S13" s="10" t="n">
+      <c r="U13" s="10" t="n">
         <v>0.628181546646409</v>
       </c>
-      <c r="T13" s="10" t="n">
+      <c r="V13" s="10" t="n">
         <v>2.5517728210184</v>
       </c>
     </row>
@@ -8209,24 +8897,30 @@
         <v>7.37664878046619</v>
       </c>
       <c r="N14" s="10" t="n">
+        <v>-0.801733413525815</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>0.428096534941324</v>
+      </c>
+      <c r="P14" s="10" t="n">
         <v>3.887910913645635</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="Q14" s="10" t="n">
         <v>3.507968918764376</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="R14" s="10" t="n">
         <v>-0.0713325886046302</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="S14" s="10" t="n">
         <v>0.163688982157025</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="T14" s="10" t="n">
         <v>-2.00691071894571</v>
       </c>
-      <c r="S14" s="10" t="n">
+      <c r="U14" s="10" t="n">
         <v>1.01939227713914</v>
       </c>
-      <c r="T14" s="10" t="n">
+      <c r="V14" s="10" t="n">
         <v>2.00247177995832</v>
       </c>
     </row>
@@ -8266,15 +8960,17 @@
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
-      <c r="P15" s="10" t="n">
-        <v>2.49237551608169</v>
-      </c>
+      <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="10" t="n">
+        <v>2.49237551608169</v>
+      </c>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="10" t="n">
         <v>-5.1390419411966</v>
       </c>
-      <c r="S15" s="9" t="n"/>
-      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -8319,24 +9015,30 @@
         <v>1.8322802951921</v>
       </c>
       <c r="N16" s="10" t="n">
+        <v>-0.498800404647518</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>-0.900045837536846</v>
+      </c>
+      <c r="P16" s="10" t="n">
         <v>0.3108106713744344</v>
       </c>
-      <c r="O16" s="10" t="n">
+      <c r="Q16" s="10" t="n">
         <v>0.7013714511280346</v>
       </c>
-      <c r="P16" s="10" t="n">
+      <c r="R16" s="10" t="n">
         <v>2.29482738823638</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="S16" s="10" t="n">
         <v>2.52306766993452</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="T16" s="10" t="n">
         <v>1.81120060518907</v>
       </c>
-      <c r="S16" s="10" t="n">
+      <c r="U16" s="10" t="n">
         <v>2.68701270314905</v>
       </c>
-      <c r="T16" s="10" t="n">
+      <c r="V16" s="10" t="n">
         <v>2.78121905025346</v>
       </c>
     </row>
@@ -8370,19 +9072,25 @@
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="10" t="n">
+      <c r="N17" s="10" t="n">
+        <v>-0.262095295947848</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>0.339152339616014</v>
+      </c>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="10" t="n">
         <v>-1.02954992492292</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="S17" s="10" t="n">
         <v>-0.931053223313861</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="T17" s="10" t="n">
         <v>-2.59671603848386</v>
       </c>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -8427,24 +9135,30 @@
         <v>2.18787078609348</v>
       </c>
       <c r="N18" s="10" t="n">
+        <v>1.49619971837867</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>1.32716981195492</v>
+      </c>
+      <c r="P18" s="10" t="n">
         <v>7.946666973442184</v>
       </c>
-      <c r="O18" s="10" t="n">
+      <c r="Q18" s="10" t="n">
         <v>8.119267175920886</v>
       </c>
-      <c r="P18" s="10" t="n">
+      <c r="R18" s="10" t="n">
         <v>1.57367534695579</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="S18" s="10" t="n">
         <v>0.646924522534852</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="T18" s="10" t="n">
         <v>1.11067385875638</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="U18" s="10" t="n">
         <v>6.30648245228024</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="V18" s="10" t="n">
         <v>6.19072201370017</v>
       </c>
     </row>
@@ -8491,24 +9205,30 @@
         <v>3.77386850549249</v>
       </c>
       <c r="N19" s="10" t="n">
+        <v>-2.3134926643114</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>-1.09040495666661</v>
+      </c>
+      <c r="P19" s="10" t="n">
         <v>-5.468603170718869</v>
       </c>
-      <c r="O19" s="10" t="n">
+      <c r="Q19" s="10" t="n">
         <v>-5.673953807314062</v>
       </c>
-      <c r="P19" s="10" t="n">
+      <c r="R19" s="10" t="n">
         <v>1.88873842413568</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="S19" s="10" t="n">
         <v>1.55366222585167</v>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="T19" s="10" t="n">
         <v>3.31365052381195</v>
       </c>
-      <c r="S19" s="10" t="n">
+      <c r="U19" s="10" t="n">
         <v>0.89453255383055</v>
       </c>
-      <c r="T19" s="10" t="n">
+      <c r="V19" s="10" t="n">
         <v>3.08813339050379</v>
       </c>
     </row>
@@ -8555,24 +9275,30 @@
         <v>7.31666406345089</v>
       </c>
       <c r="N20" s="10" t="n">
+        <v>1.34503769070429</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>4.09212164800002</v>
+      </c>
+      <c r="P20" s="10" t="n">
         <v>-0.2903214224688967</v>
       </c>
-      <c r="O20" s="10" t="n">
+      <c r="Q20" s="10" t="n">
         <v>-1.579623077199753</v>
       </c>
-      <c r="P20" s="10" t="n">
+      <c r="R20" s="10" t="n">
         <v>2.9979635592165</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="S20" s="10" t="n">
         <v>1.76009229587045</v>
       </c>
-      <c r="R20" s="10" t="n">
+      <c r="T20" s="10" t="n">
         <v>4.21890908178643</v>
       </c>
-      <c r="S20" s="10" t="n">
+      <c r="U20" s="10" t="n">
         <v>1.51085977279679</v>
       </c>
-      <c r="T20" s="10" t="n">
+      <c r="V20" s="10" t="n">
         <v>3.74403292270937</v>
       </c>
     </row>
@@ -8619,24 +9345,30 @@
         <v>-3.96497547821137</v>
       </c>
       <c r="N21" s="10" t="n">
+        <v>-2.04918691972589</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>-1.97898297875365</v>
+      </c>
+      <c r="P21" s="10" t="n">
         <v>0.0717301669226646</v>
       </c>
-      <c r="O21" s="10" t="n">
+      <c r="Q21" s="10" t="n">
         <v>-0.4016092905692264</v>
       </c>
-      <c r="P21" s="10" t="n">
+      <c r="R21" s="10" t="n">
         <v>1.36639206277824</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="S21" s="10" t="n">
         <v>1.26799737584483</v>
       </c>
-      <c r="R21" s="10" t="n">
+      <c r="T21" s="10" t="n">
         <v>1.14584323905699</v>
       </c>
-      <c r="S21" s="10" t="n">
+      <c r="U21" s="10" t="n">
         <v>2.10989447178502</v>
       </c>
-      <c r="T21" s="10" t="n">
+      <c r="V21" s="10" t="n">
         <v>1.38530001359927</v>
       </c>
     </row>
@@ -8677,24 +9409,30 @@
         <v>-0.298385782924601</v>
       </c>
       <c r="N22" s="10" t="n">
+        <v>-0.7377291661961241</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>-0.847243338918636</v>
+      </c>
+      <c r="P22" s="10" t="n">
         <v>0.0992328917916334</v>
       </c>
-      <c r="O22" s="10" t="n">
+      <c r="Q22" s="10" t="n">
         <v>0.1413527387392914</v>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="R22" s="10" t="n">
         <v>0.159515216698385</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="S22" s="10" t="n">
         <v>-0.153171304696138</v>
       </c>
-      <c r="R22" s="10" t="n">
+      <c r="T22" s="10" t="n">
         <v>1.74866833860967</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="U22" s="10" t="n">
         <v>-0.200608496306742</v>
       </c>
-      <c r="T22" s="10" t="n">
+      <c r="V22" s="10" t="n">
         <v>0.633311174348519</v>
       </c>
     </row>
@@ -8739,24 +9477,30 @@
         <v>3.56076502874487</v>
       </c>
       <c r="N23" s="10" t="n">
+        <v>1.10187890032299</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>1.63942106505118</v>
+      </c>
+      <c r="P23" s="10" t="n">
         <v>5.062415359539015</v>
       </c>
-      <c r="O23" s="10" t="n">
+      <c r="Q23" s="10" t="n">
         <v>5.036671232260984</v>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="R23" s="10" t="n">
         <v>-0.455321176539081</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="S23" s="10" t="n">
         <v>-0.729541570166073</v>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="T23" s="10" t="n">
         <v>-0.447888686877304</v>
       </c>
-      <c r="S23" s="10" t="n">
+      <c r="U23" s="10" t="n">
         <v>-1.80161423745876</v>
       </c>
-      <c r="T23" s="10" t="n">
+      <c r="V23" s="10" t="n">
         <v>-2.212691629844</v>
       </c>
     </row>
@@ -8803,24 +9547,30 @@
         <v>5.69734361796148</v>
       </c>
       <c r="N24" s="10" t="n">
+        <v>0.767356720032175</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>0.546799971024799</v>
+      </c>
+      <c r="P24" s="10" t="n">
         <v>-0.1918363813113215</v>
       </c>
-      <c r="O24" s="10" t="n">
+      <c r="Q24" s="10" t="n">
         <v>0.3569919020809229</v>
       </c>
-      <c r="P24" s="10" t="n">
+      <c r="R24" s="10" t="n">
         <v>0.128296775049852</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="S24" s="10" t="n">
         <v>-0.6703771259474079</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="T24" s="10" t="n">
         <v>0.47680047150071</v>
       </c>
-      <c r="S24" s="10" t="n">
+      <c r="U24" s="10" t="n">
         <v>0.306216610417165</v>
       </c>
-      <c r="T24" s="10" t="n">
+      <c r="V24" s="10" t="n">
         <v>1.19639719691927</v>
       </c>
     </row>
@@ -8865,24 +9615,30 @@
         <v>-4.247743486903</v>
       </c>
       <c r="N25" s="10" t="n">
+        <v>-4.42313704186632</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>-5.36898559914467</v>
+      </c>
+      <c r="P25" s="10" t="n">
         <v>-0.6552177121301619</v>
       </c>
-      <c r="O25" s="10" t="n">
+      <c r="Q25" s="10" t="n">
         <v>-0.5672384978231418</v>
       </c>
-      <c r="P25" s="10" t="n">
+      <c r="R25" s="10" t="n">
         <v>1.86614372016981</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="S25" s="10" t="n">
         <v>1.5877270721957</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="T25" s="10" t="n">
         <v>2.44730481665509</v>
       </c>
-      <c r="S25" s="10" t="n">
+      <c r="U25" s="10" t="n">
         <v>2.79300302421463</v>
       </c>
-      <c r="T25" s="10" t="n">
+      <c r="V25" s="10" t="n">
         <v>3.02209759317698</v>
       </c>
     </row>
@@ -8927,24 +9683,30 @@
         <v>3.70422063063712</v>
       </c>
       <c r="N26" s="10" t="n">
+        <v>4.60870340081624</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>3.77244850880328</v>
+      </c>
+      <c r="P26" s="10" t="n">
         <v>0.5492432189145007</v>
       </c>
-      <c r="O26" s="10" t="n">
+      <c r="Q26" s="10" t="n">
         <v>0.5301680661914108</v>
       </c>
-      <c r="P26" s="10" t="n">
+      <c r="R26" s="10" t="n">
         <v>3.09412145953728</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="S26" s="10" t="n">
         <v>1.84488141293706</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="T26" s="10" t="n">
         <v>4.30167686903167</v>
       </c>
-      <c r="S26" s="10" t="n">
+      <c r="U26" s="10" t="n">
         <v>1.07357998097036</v>
       </c>
-      <c r="T26" s="10" t="n">
+      <c r="V26" s="10" t="n">
         <v>3.77985191517593</v>
       </c>
     </row>
@@ -8975,6 +9737,8 @@
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="9" t="n"/>
       <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -9019,24 +9783,30 @@
         <v>0.0396326729301191</v>
       </c>
       <c r="N28" s="10" t="n">
+        <v>-1.75635149569843</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>-1.94461463743154</v>
+      </c>
+      <c r="P28" s="10" t="n">
         <v>-1.178109639071032</v>
       </c>
-      <c r="O28" s="10" t="n">
+      <c r="Q28" s="10" t="n">
         <v>-1.231963995023502</v>
       </c>
-      <c r="P28" s="10" t="n">
+      <c r="R28" s="10" t="n">
         <v>-1.74925086901342</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="S28" s="10" t="n">
         <v>-1.88846389833827</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="T28" s="10" t="n">
         <v>-0.6410066519484749</v>
       </c>
-      <c r="S28" s="10" t="n">
+      <c r="U28" s="10" t="n">
         <v>-2.35874899425477</v>
       </c>
-      <c r="T28" s="10" t="n">
+      <c r="V28" s="10" t="n">
         <v>2.91285918504908</v>
       </c>
     </row>
@@ -9083,24 +9853,30 @@
         <v>0.756775568681752</v>
       </c>
       <c r="N29" s="10" t="n">
+        <v>1.21874507189201</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>3.25558751458416</v>
+      </c>
+      <c r="P29" s="10" t="n">
         <v>1.66989295710482</v>
       </c>
-      <c r="O29" s="10" t="n">
+      <c r="Q29" s="10" t="n">
         <v>1.515895609620146</v>
       </c>
-      <c r="P29" s="10" t="n">
+      <c r="R29" s="10" t="n">
         <v>0.858694131588708</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="S29" s="10" t="n">
         <v>0.792217431423037</v>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="T29" s="10" t="n">
         <v>2.82911022583707</v>
       </c>
-      <c r="S29" s="10" t="n">
+      <c r="U29" s="10" t="n">
         <v>0.489424717717857</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="V29" s="10" t="n">
         <v>2.2350450017259</v>
       </c>
     </row>
@@ -9136,25 +9912,29 @@
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="9" t="n"/>
-      <c r="N30" s="10" t="n">
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="10" t="n">
+        <v>-5.57720947557638</v>
+      </c>
+      <c r="P30" s="10" t="n">
         <v>0.6677299608911785</v>
       </c>
-      <c r="O30" s="10" t="n">
+      <c r="Q30" s="10" t="n">
         <v>0.0775316054593175</v>
       </c>
-      <c r="P30" s="10" t="n">
+      <c r="R30" s="10" t="n">
         <v>7.50348409592738</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="S30" s="10" t="n">
         <v>6.2725821018296</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="T30" s="10" t="n">
         <v>8.87923777216338</v>
       </c>
-      <c r="S30" s="10" t="n">
+      <c r="U30" s="10" t="n">
         <v>12.3327491631417</v>
       </c>
-      <c r="T30" s="10" t="n">
+      <c r="V30" s="10" t="n">
         <v>11.8477425359168</v>
       </c>
     </row>
@@ -9196,19 +9976,25 @@
       <c r="M31" s="10" t="n">
         <v>7.2191783541769</v>
       </c>
-      <c r="N31" s="9" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="10" t="n">
+      <c r="N31" s="10" t="n">
+        <v>1.04618873282607</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <v>1.57156777466251</v>
+      </c>
+      <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="10" t="n">
         <v>-1.27178811089417</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="S31" s="10" t="n">
         <v>-1.9394683901759</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="T31" s="10" t="n">
         <v>-2.33466929424159</v>
       </c>
-      <c r="S31" s="9" t="n"/>
-      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -9251,29 +10037,35 @@
         <v>-0.246592851139775</v>
       </c>
       <c r="N32" s="10" t="n">
+        <v>-0.579020339417653</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <v>-0.958417392223053</v>
+      </c>
+      <c r="P32" s="10" t="n">
         <v>-1.13213135656537</v>
       </c>
-      <c r="O32" s="10" t="n">
+      <c r="Q32" s="10" t="n">
         <v>-1.169406912519067</v>
       </c>
-      <c r="P32" s="10" t="n">
+      <c r="R32" s="10" t="n">
         <v>0.634213019981918</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="S32" s="10" t="n">
         <v>0.6112254293068889</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="T32" s="10" t="n">
         <v>1.3898930738796</v>
       </c>
-      <c r="S32" s="10" t="n">
+      <c r="U32" s="10" t="n">
         <v>-0.236428784750778</v>
       </c>
-      <c r="T32" s="10" t="n">
+      <c r="V32" s="10" t="n">
         <v>1.47555776466522</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:T32">
+  <conditionalFormatting sqref="B2:V32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3"/>
@@ -9295,7 +10087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9319,6 +10111,8 @@
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -9394,35 +10188,45 @@
       </c>
       <c r="O1" s="12" t="inlineStr">
         <is>
+          <t>S2 (benchmark v2) | H-bulk1 Roadmap fetal SI vs HPA adult SI [tier B]</t>
+        </is>
+      </c>
+      <c r="P1" s="12" t="inlineStr">
+        <is>
+          <t>S2 (benchmark v2) | H-bulk2 Roadmap fetal SI vs HPA duodenum [tier B subset]</t>
+        </is>
+      </c>
+      <c r="Q1" s="12" t="inlineStr">
+        <is>
           <t>S2 (benchmark v2) | H-new3 Gao fetal + Wang adult</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>S2 (benchmark v2) | H-new3-debug</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>S3 | TCGA COAD+READ (T1)</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>S3 | TCGA paired</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>S3 | TCGA vs GTEx</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="V1" s="12" t="inlineStr">
         <is>
           <t>S3 | Pelka 2021 (S2, GSE178341)</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="W1" s="12" t="inlineStr">
         <is>
           <t>S3 | Pelka progenitor check (P)</t>
         </is>
@@ -9534,6 +10338,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V2" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -9631,12 +10445,22 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="T3" s="13" t="inlineStr">
+      <c r="T3" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="U3" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V3" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="U3" s="13" t="inlineStr">
+      <c r="W3" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -9748,6 +10572,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V4" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -9855,6 +10689,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -9962,6 +10806,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -10069,6 +10923,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V7" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -10176,6 +11040,16 @@
           <t>no human one2one orthologue</t>
         </is>
       </c>
+      <c r="V8" s="13" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
+      <c r="W8" s="13" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -10248,26 +11122,26 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
       <c r="S9" s="9" t="inlineStr">
         <is>
           <t>measured</t>
@@ -10279,6 +11153,16 @@
         </is>
       </c>
       <c r="U9" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V9" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -10365,27 +11249,37 @@
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="R10" s="13" t="inlineStr">
         <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="inlineStr">
+        <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="S10" s="13" t="inlineStr">
+      <c r="U10" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="T10" s="13" t="inlineStr">
+      <c r="V10" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="U10" s="13" t="inlineStr">
+      <c r="W10" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -10497,6 +11391,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V11" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -10604,6 +11508,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V12" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -10711,6 +11625,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V13" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -10818,6 +11742,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -10900,27 +11834,37 @@
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="T15" s="13" t="inlineStr">
+      <c r="U15" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="U15" s="13" t="inlineStr">
+      <c r="W15" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -11032,6 +11976,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V16" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -11104,37 +12058,47 @@
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="O17" s="13" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr">
         <is>
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="P17" s="13" t="inlineStr">
+      <c r="R17" s="13" t="inlineStr">
         <is>
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
       <c r="S17" s="9" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="T17" s="13" t="inlineStr">
+      <c r="T17" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="U17" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V17" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="U17" s="13" t="inlineStr">
+      <c r="W17" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -11246,6 +12210,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V18" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -11353,6 +12327,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V19" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -11460,6 +12444,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V20" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -11567,6 +12561,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V21" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -11674,6 +12678,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -11781,6 +12795,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V23" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -11888,6 +12912,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -11995,6 +13029,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V25" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -12102,6 +13146,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V26" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -12209,6 +13263,16 @@
           <t>no human one2one orthologue</t>
         </is>
       </c>
+      <c r="V27" s="13" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -12316,6 +13380,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V28" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -12423,6 +13497,16 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="V29" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -12495,9 +13579,9 @@
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="O30" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="P30" s="9" t="inlineStr">
@@ -12526,6 +13610,16 @@
         </is>
       </c>
       <c r="U30" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V30" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -12602,37 +13696,47 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="O31" s="13" t="inlineStr">
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Q31" s="13" t="inlineStr">
         <is>
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="P31" s="13" t="inlineStr">
+      <c r="R31" s="13" t="inlineStr">
         <is>
           <t>not in dataset annotation</t>
         </is>
       </c>
-      <c r="Q31" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
       <c r="S31" s="9" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
       </c>
-      <c r="T31" s="13" t="inlineStr">
+      <c r="T31" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="U31" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="U31" s="13" t="inlineStr">
+      <c r="W31" s="13" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -12740,6 +13844,16 @@
         </is>
       </c>
       <c r="U32" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="V32" s="9" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -12756,7 +13870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -12800,47 +13914,54 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Benchmark v2 (purple headers): H-new1 Visium (adult n = 2 sections; fetal spots less epithelial), H-new2 (study confounded with stage), H-new3 and Gao-original recomputed (cross-platform, effect-only; Welch P descriptive). See step2_benchmark_v2/docs.</t>
+          <t>H-bulk1/H-bulk2: Roadmap fetal SI (6 donors, total RNA) vs HPA E-MTAB-1733 adult SI/duodenum (poly(A)); whole tissue; H-bulk2 is a subset of H-bulk1 (same fetal samples).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Step 2 primary datasets (HGCA, Gao, GSE230581) belong to an INVALIDATED analysis (failed biological QA); values are reported for audit, not as evidence.</t>
+          <t>Benchmark v2 (purple headers): H-new1 Visium (adult n = 2 sections; fetal spots less epithelial), H-new2 (study confounded with stage), H-new3 and Gao-original recomputed (cross-platform, effect-only; Welch P descriptive). See step2_benchmark_v2/docs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Symbols: CCN1/CCN2 are looked up as CYR61/CTGF in annotations that predate the HGNC rename (HGCA, Gao, Senger, Fawkner, TCGA/GENCODE v26, Pelka, Joanito).</t>
+          <t>Step 2 primary datasets (HGCA, Gao, GSE230581) belong to an INVALIDATED analysis (failed biological QA); values are reported for audit, not as evidence.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Mouse: Ensembl 116 one2one orthologues; LY6A/REG3B use the mouse-defined genes Ly6a/Reg3b; CXADR uses high-confidence Cxadr (one2many). Benchmarks map by one2one Entrez only, so these are blank there.</t>
+          <t>Symbols: CCN1/CCN2 are looked up as CYR61/CTGF in annotations that predate the HGNC rename (HGCA, Gao, Senger, Fawkner, TCGA/GENCODE v26, Pelka, Joanito).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>TCGA paired: 50 patients with tumour and normal; TCGA vs GTEx: source fully confounded, direction only.</t>
+          <t>Mouse: Ensembl 116 one2one orthologues; LY6A/REG3B use the mouse-defined genes Ly6a/Reg3b; CXADR uses high-confidence Cxadr (one2many). Benchmarks map by one2one Entrez only, so these are blank there.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Public version: Joanito (Synapse syn26844071) columns and the Joanito-derived Step 3 final label are omitted under its data-use terms.</t>
+          <t>TCGA paired: 50 patients with tumour and normal; TCGA vs GTEx: source fully confounded, direction only.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Public version: Joanito (Synapse syn26844071) columns and the Joanito-derived Step 3 final label are omitted under its data-use terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Regenerate: python3 marker_summary/scripts/build_marker_summary.py</t>
         </is>

--- a/marker_summary/results/Literature_31_marker_summary_statistics_public.xlsx
+++ b/marker_summary/results/Literature_31_marker_summary_statistics_public.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW35"/>
+  <dimension ref="A1:DF35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -626,9 +626,18 @@
     <col width="11" customWidth="1" min="96" max="96"/>
     <col width="11" customWidth="1" min="97" max="97"/>
     <col width="11" customWidth="1" min="98" max="98"/>
-    <col width="22" customWidth="1" min="99" max="99"/>
-    <col width="22" customWidth="1" min="100" max="100"/>
-    <col width="22" customWidth="1" min="101" max="101"/>
+    <col width="11" customWidth="1" min="99" max="99"/>
+    <col width="11" customWidth="1" min="100" max="100"/>
+    <col width="11" customWidth="1" min="101" max="101"/>
+    <col width="11" customWidth="1" min="102" max="102"/>
+    <col width="11" customWidth="1" min="103" max="103"/>
+    <col width="11" customWidth="1" min="104" max="104"/>
+    <col width="11" customWidth="1" min="105" max="105"/>
+    <col width="11" customWidth="1" min="106" max="106"/>
+    <col width="11" customWidth="1" min="107" max="107"/>
+    <col width="22" customWidth="1" min="108" max="108"/>
+    <col width="22" customWidth="1" min="109" max="109"/>
+    <col width="22" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -839,23 +848,23 @@
       </c>
       <c r="CD1" s="3" t="n"/>
       <c r="CE1" s="3" t="n"/>
-      <c r="CF1" s="7" t="inlineStr">
-        <is>
-          <t>Step 3</t>
+      <c r="CF1" s="6" t="inlineStr">
+        <is>
+          <t>Step 2 (benchmark v2, stage v1.2)</t>
         </is>
       </c>
       <c r="CG1" s="3" t="n"/>
       <c r="CH1" s="3" t="n"/>
-      <c r="CI1" s="7" t="inlineStr">
-        <is>
-          <t>Step 3</t>
+      <c r="CI1" s="6" t="inlineStr">
+        <is>
+          <t>Step 2 (benchmark v2, stage v1.2)</t>
         </is>
       </c>
       <c r="CJ1" s="3" t="n"/>
       <c r="CK1" s="3" t="n"/>
-      <c r="CL1" s="7" t="inlineStr">
-        <is>
-          <t>Step 3</t>
+      <c r="CL1" s="6" t="inlineStr">
+        <is>
+          <t>Step 2 (benchmark v2, stage v1.2)</t>
         </is>
       </c>
       <c r="CM1" s="3" t="n"/>
@@ -874,17 +883,38 @@
       </c>
       <c r="CS1" s="3" t="n"/>
       <c r="CT1" s="3" t="n"/>
-      <c r="CU1" s="8" t="inlineStr">
+      <c r="CU1" s="7" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="CV1" s="3" t="n"/>
+      <c r="CW1" s="3" t="n"/>
+      <c r="CX1" s="7" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="CY1" s="3" t="n"/>
+      <c r="CZ1" s="3" t="n"/>
+      <c r="DA1" s="7" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="DB1" s="3" t="n"/>
+      <c r="DC1" s="3" t="n"/>
+      <c r="DD1" s="8" t="inlineStr">
         <is>
           <t>Step2_final_(invalidated)</t>
         </is>
       </c>
-      <c r="CV1" s="8" t="inlineStr">
+      <c r="DE1" s="8" t="inlineStr">
         <is>
           <t>Step2_first_failed_gate</t>
         </is>
       </c>
-      <c r="CW1" s="8" t="inlineStr">
+      <c r="DF1" s="8" t="inlineStr">
         <is>
           <t>Step3_bulk_support</t>
         </is>
@@ -1078,44 +1108,65 @@
       </c>
       <c r="CD2" s="3" t="n"/>
       <c r="CE2" s="3" t="n"/>
-      <c r="CF2" s="7" t="inlineStr">
-        <is>
-          <t>TCGA COAD+READ (T1) [Human]</t>
+      <c r="CF2" s="6" t="inlineStr">
+        <is>
+          <t>Fawkner early fetal (&lt;9 PCW) vs Burclaff adult [stage-resolved] [Human]</t>
         </is>
       </c>
       <c r="CG2" s="3" t="n"/>
       <c r="CH2" s="3" t="n"/>
-      <c r="CI2" s="7" t="inlineStr">
-        <is>
-          <t>TCGA paired [Human]</t>
+      <c r="CI2" s="6" t="inlineStr">
+        <is>
+          <t>Fawkner mid/late fetal (&gt;=9 PCW) vs Burclaff adult [stage-resolved] [Human]</t>
         </is>
       </c>
       <c r="CJ2" s="3" t="n"/>
       <c r="CK2" s="3" t="n"/>
-      <c r="CL2" s="7" t="inlineStr">
-        <is>
-          <t>TCGA vs GTEx [Human]</t>
+      <c r="CL2" s="6" t="inlineStr">
+        <is>
+          <t>Fawkner mid/late vs early fetal [within-fetal] [Human]</t>
         </is>
       </c>
       <c r="CM2" s="3" t="n"/>
       <c r="CN2" s="3" t="n"/>
       <c r="CO2" s="7" t="inlineStr">
         <is>
-          <t>Pelka 2021 (S2, GSE178341) [Human]</t>
+          <t>TCGA COAD+READ (T1) [Human]</t>
         </is>
       </c>
       <c r="CP2" s="3" t="n"/>
       <c r="CQ2" s="3" t="n"/>
       <c r="CR2" s="7" t="inlineStr">
         <is>
-          <t>Pelka progenitor check (P) [Human]</t>
+          <t>TCGA paired [Human]</t>
         </is>
       </c>
       <c r="CS2" s="3" t="n"/>
       <c r="CT2" s="3" t="n"/>
-      <c r="CU2" s="3" t="n"/>
+      <c r="CU2" s="7" t="inlineStr">
+        <is>
+          <t>TCGA vs GTEx [Human]</t>
+        </is>
+      </c>
       <c r="CV2" s="3" t="n"/>
       <c r="CW2" s="3" t="n"/>
+      <c r="CX2" s="7" t="inlineStr">
+        <is>
+          <t>Pelka 2021 (S2, GSE178341) [Human]</t>
+        </is>
+      </c>
+      <c r="CY2" s="3" t="n"/>
+      <c r="CZ2" s="3" t="n"/>
+      <c r="DA2" s="7" t="inlineStr">
+        <is>
+          <t>Pelka progenitor check (P) [Human]</t>
+        </is>
+      </c>
+      <c r="DB2" s="3" t="n"/>
+      <c r="DC2" s="3" t="n"/>
+      <c r="DD2" s="3" t="n"/>
+      <c r="DE2" s="3" t="n"/>
+      <c r="DF2" s="3" t="n"/>
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="3" t="n"/>
@@ -1305,44 +1356,65 @@
       </c>
       <c r="CD3" s="3" t="n"/>
       <c r="CE3" s="3" t="n"/>
-      <c r="CF3" s="7" t="inlineStr">
-        <is>
-          <t>primary tumour vs normal, ~ tissue + project; + = tumour-high</t>
+      <c r="CF3" s="6" t="inlineStr">
+        <is>
+          <t>edgeR, 2 vs 3; + = fetal-high</t>
         </is>
       </c>
       <c r="CG3" s="3" t="n"/>
       <c r="CH3" s="3" t="n"/>
-      <c r="CI3" s="7" t="inlineStr">
-        <is>
-          <t>tumour vs matched normal (50 pairs); + = tumour-high</t>
+      <c r="CI3" s="6" t="inlineStr">
+        <is>
+          <t>edgeR, 20 vs 3; + = fetal-high</t>
         </is>
       </c>
       <c r="CJ3" s="3" t="n"/>
       <c r="CK3" s="3" t="n"/>
-      <c r="CL3" s="7" t="inlineStr">
-        <is>
-          <t>TCGA tumour vs GTEx transverse colon (direction only); + = tumour-high</t>
+      <c r="CL3" s="6" t="inlineStr">
+        <is>
+          <t>edgeR, 20 vs 2 units; positive = higher at &gt;=9 PCW; + = later fetal-high</t>
         </is>
       </c>
       <c r="CM3" s="3" t="n"/>
       <c r="CN3" s="3" t="n"/>
       <c r="CO3" s="7" t="inlineStr">
         <is>
-          <t>tumour vs normal epithelium; + = tumour-high</t>
+          <t>primary tumour vs normal, ~ tissue + project; + = tumour-high</t>
         </is>
       </c>
       <c r="CP3" s="3" t="n"/>
       <c r="CQ3" s="3" t="n"/>
       <c r="CR3" s="7" t="inlineStr">
         <is>
-          <t>tumour epithelium vs normal stem/TA (cE01-03); + = tumour-high</t>
+          <t>tumour vs matched normal (50 pairs); + = tumour-high</t>
         </is>
       </c>
       <c r="CS3" s="3" t="n"/>
       <c r="CT3" s="3" t="n"/>
-      <c r="CU3" s="3" t="n"/>
+      <c r="CU3" s="7" t="inlineStr">
+        <is>
+          <t>TCGA tumour vs GTEx transverse colon (direction only); + = tumour-high</t>
+        </is>
+      </c>
       <c r="CV3" s="3" t="n"/>
       <c r="CW3" s="3" t="n"/>
+      <c r="CX3" s="7" t="inlineStr">
+        <is>
+          <t>tumour vs normal epithelium; + = tumour-high</t>
+        </is>
+      </c>
+      <c r="CY3" s="3" t="n"/>
+      <c r="CZ3" s="3" t="n"/>
+      <c r="DA3" s="7" t="inlineStr">
+        <is>
+          <t>tumour epithelium vs normal stem/TA (cE01-03); + = tumour-high</t>
+        </is>
+      </c>
+      <c r="DB3" s="3" t="n"/>
+      <c r="DC3" s="3" t="n"/>
+      <c r="DD3" s="3" t="n"/>
+      <c r="DE3" s="3" t="n"/>
+      <c r="DF3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -1815,9 +1887,54 @@
           <t>FDR</t>
         </is>
       </c>
-      <c r="CU4" s="3" t="n"/>
-      <c r="CV4" s="3" t="n"/>
-      <c r="CW4" s="3" t="n"/>
+      <c r="CU4" s="9" t="inlineStr">
+        <is>
+          <t>log2FC</t>
+        </is>
+      </c>
+      <c r="CV4" s="9" t="inlineStr">
+        <is>
+          <t>P value</t>
+        </is>
+      </c>
+      <c r="CW4" s="9" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="CX4" s="9" t="inlineStr">
+        <is>
+          <t>log2FC</t>
+        </is>
+      </c>
+      <c r="CY4" s="9" t="inlineStr">
+        <is>
+          <t>P value</t>
+        </is>
+      </c>
+      <c r="CZ4" s="9" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="DA4" s="9" t="inlineStr">
+        <is>
+          <t>log2FC</t>
+        </is>
+      </c>
+      <c r="DB4" s="9" t="inlineStr">
+        <is>
+          <t>P value</t>
+        </is>
+      </c>
+      <c r="DC4" s="9" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="DD4" s="3" t="n"/>
+      <c r="DE4" s="3" t="n"/>
+      <c r="DF4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -2056,55 +2173,82 @@
         <v>0.260872289477834</v>
       </c>
       <c r="CF5" s="11" t="n">
+        <v>2.99456069495154</v>
+      </c>
+      <c r="CG5" s="12" t="n">
+        <v>0.0028503261148274</v>
+      </c>
+      <c r="CH5" s="12" t="n">
+        <v>0.0114077502442821</v>
+      </c>
+      <c r="CI5" s="11" t="n">
+        <v>4.08526804610829</v>
+      </c>
+      <c r="CJ5" s="12" t="n">
+        <v>4.03296851332847e-06</v>
+      </c>
+      <c r="CK5" s="12" t="n">
+        <v>1.82819733762252e-05</v>
+      </c>
+      <c r="CL5" s="11" t="n">
+        <v>1.10237856445083</v>
+      </c>
+      <c r="CM5" s="12" t="n">
+        <v>0.134090808615037</v>
+      </c>
+      <c r="CN5" s="12" t="n">
+        <v>0.292253268976417</v>
+      </c>
+      <c r="CO5" s="11" t="n">
         <v>5.05028632487126</v>
       </c>
-      <c r="CG5" s="12" t="n">
+      <c r="CP5" s="12" t="n">
         <v>5.475203508004971e-25</v>
       </c>
-      <c r="CH5" s="12" t="n">
+      <c r="CQ5" s="12" t="n">
         <v>3.99218920044355e-24</v>
       </c>
-      <c r="CI5" s="11" t="n">
+      <c r="CR5" s="11" t="n">
         <v>3.73497284492898</v>
       </c>
-      <c r="CJ5" s="10" t="n"/>
-      <c r="CK5" s="12" t="n">
+      <c r="CS5" s="10" t="n"/>
+      <c r="CT5" s="12" t="n">
         <v>2.21079248401646e-11</v>
       </c>
-      <c r="CL5" s="11" t="n">
+      <c r="CU5" s="11" t="n">
         <v>4.69300181571387</v>
       </c>
-      <c r="CM5" s="10" t="n"/>
-      <c r="CN5" s="12" t="n">
+      <c r="CV5" s="10" t="n"/>
+      <c r="CW5" s="12" t="n">
         <v>2.01876716899463e-167</v>
       </c>
-      <c r="CO5" s="11" t="n">
+      <c r="CX5" s="11" t="n">
         <v>4.25904379124654</v>
       </c>
-      <c r="CP5" s="12" t="n">
+      <c r="CY5" s="12" t="n">
         <v>7.182211571553239e-12</v>
       </c>
-      <c r="CQ5" s="12" t="n">
+      <c r="CZ5" s="12" t="n">
         <v>3.76963504484094e-11</v>
       </c>
-      <c r="CR5" s="11" t="n">
+      <c r="DA5" s="11" t="n">
         <v>6.05919277196155</v>
       </c>
-      <c r="CS5" s="12" t="n">
+      <c r="DB5" s="12" t="n">
         <v>1.16264903658604e-17</v>
       </c>
-      <c r="CT5" s="12" t="n">
+      <c r="DC5" s="12" t="n">
         <v>3.99566507033922e-16</v>
       </c>
-      <c r="CU5" s="10" t="b">
+      <c r="DD5" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV5" s="10" t="inlineStr">
+      <c r="DE5" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW5" s="10" t="b">
+      <c r="DF5" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2357,43 +2501,70 @@
         <v>0.315985854966968</v>
       </c>
       <c r="CF6" s="11" t="n">
+        <v>4.00610785770629</v>
+      </c>
+      <c r="CG6" s="12" t="n">
+        <v>1.62812715824449e-05</v>
+      </c>
+      <c r="CH6" s="12" t="n">
+        <v>0.0003703675378741</v>
+      </c>
+      <c r="CI6" s="11" t="n">
+        <v>2.77075537774903</v>
+      </c>
+      <c r="CJ6" s="12" t="n">
+        <v>0.0061981986054554</v>
+      </c>
+      <c r="CK6" s="12" t="n">
+        <v>0.0121391902825689</v>
+      </c>
+      <c r="CL6" s="11" t="n">
+        <v>-1.22630141228582</v>
+      </c>
+      <c r="CM6" s="12" t="n">
+        <v>0.169686857684379</v>
+      </c>
+      <c r="CN6" s="12" t="n">
+        <v>0.341717264203179</v>
+      </c>
+      <c r="CO6" s="11" t="n">
         <v>-0.0025247870000847</v>
       </c>
-      <c r="CG6" s="12" t="n">
+      <c r="CP6" s="12" t="n">
         <v>0.98611755278992</v>
       </c>
-      <c r="CH6" s="12" t="n">
+      <c r="CQ6" s="12" t="n">
         <v>0.98730775501906</v>
       </c>
-      <c r="CI6" s="11" t="n">
+      <c r="CR6" s="11" t="n">
         <v>-0.222650205328684</v>
       </c>
-      <c r="CJ6" s="10" t="n"/>
-      <c r="CK6" s="12" t="n">
+      <c r="CS6" s="10" t="n"/>
+      <c r="CT6" s="12" t="n">
         <v>0.151845230271159</v>
       </c>
-      <c r="CL6" s="11" t="n">
+      <c r="CU6" s="11" t="n">
         <v>-0.433294511714691</v>
       </c>
-      <c r="CM6" s="10" t="n"/>
-      <c r="CN6" s="12" t="n">
+      <c r="CV6" s="10" t="n"/>
+      <c r="CW6" s="12" t="n">
         <v>5.3412885963428e-12</v>
       </c>
-      <c r="CO6" s="10" t="n"/>
-      <c r="CP6" s="10" t="n"/>
-      <c r="CQ6" s="10" t="n"/>
-      <c r="CR6" s="10" t="n"/>
-      <c r="CS6" s="10" t="n"/>
-      <c r="CT6" s="10" t="n"/>
-      <c r="CU6" s="10" t="b">
+      <c r="CX6" s="10" t="n"/>
+      <c r="CY6" s="10" t="n"/>
+      <c r="CZ6" s="10" t="n"/>
+      <c r="DA6" s="10" t="n"/>
+      <c r="DB6" s="10" t="n"/>
+      <c r="DC6" s="10" t="n"/>
+      <c r="DD6" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="CV6" s="10" t="inlineStr">
+      <c r="DE6" s="10" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="CW6" s="10" t="b">
+      <c r="DF6" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2646,55 +2817,82 @@
         <v>0.0855535180959119</v>
       </c>
       <c r="CF7" s="11" t="n">
+        <v>-0.837069630855066</v>
+      </c>
+      <c r="CG7" s="12" t="n">
+        <v>0.253469148167601</v>
+      </c>
+      <c r="CH7" s="12" t="n">
+        <v>0.352443194867238</v>
+      </c>
+      <c r="CI7" s="11" t="n">
+        <v>-0.931228468737944</v>
+      </c>
+      <c r="CJ7" s="12" t="n">
+        <v>0.180218025785427</v>
+      </c>
+      <c r="CK7" s="12" t="n">
+        <v>0.239594547741475</v>
+      </c>
+      <c r="CL7" s="11" t="n">
+        <v>-0.0761228290537096</v>
+      </c>
+      <c r="CM7" s="12" t="n">
+        <v>0.937185488352694</v>
+      </c>
+      <c r="CN7" s="12" t="n">
+        <v>0.965507568168599</v>
+      </c>
+      <c r="CO7" s="11" t="n">
         <v>0.208594387468698</v>
       </c>
-      <c r="CG7" s="12" t="n">
+      <c r="CP7" s="12" t="n">
         <v>0.255907709246128</v>
       </c>
-      <c r="CH7" s="12" t="n">
+      <c r="CQ7" s="12" t="n">
         <v>0.288255163208507</v>
       </c>
-      <c r="CI7" s="11" t="n">
+      <c r="CR7" s="11" t="n">
         <v>-0.246222685380311</v>
       </c>
-      <c r="CJ7" s="10" t="n"/>
-      <c r="CK7" s="12" t="n">
+      <c r="CS7" s="10" t="n"/>
+      <c r="CT7" s="12" t="n">
         <v>0.154816687052447</v>
       </c>
-      <c r="CL7" s="11" t="n">
+      <c r="CU7" s="11" t="n">
         <v>-0.643732616070441</v>
       </c>
-      <c r="CM7" s="10" t="n"/>
-      <c r="CN7" s="12" t="n">
+      <c r="CV7" s="10" t="n"/>
+      <c r="CW7" s="12" t="n">
         <v>1.07492828195462e-17</v>
       </c>
-      <c r="CO7" s="11" t="n">
+      <c r="CX7" s="11" t="n">
         <v>2.84220968978987</v>
       </c>
-      <c r="CP7" s="12" t="n">
+      <c r="CY7" s="12" t="n">
         <v>1.17188992894437e-12</v>
       </c>
-      <c r="CQ7" s="12" t="n">
+      <c r="CZ7" s="12" t="n">
         <v>6.82874480403112e-12</v>
       </c>
-      <c r="CR7" s="11" t="n">
+      <c r="DA7" s="11" t="n">
         <v>4.55185303250578</v>
       </c>
-      <c r="CS7" s="12" t="n">
+      <c r="DB7" s="12" t="n">
         <v>2.91721323965648e-22</v>
       </c>
-      <c r="CT7" s="12" t="n">
+      <c r="DC7" s="12" t="n">
         <v>2.41656548771775e-20</v>
       </c>
-      <c r="CU7" s="10" t="b">
+      <c r="DD7" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV7" s="10" t="inlineStr">
+      <c r="DE7" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW7" s="10" t="b">
+      <c r="DF7" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2947,55 +3145,82 @@
         <v>0.1495318116972751</v>
       </c>
       <c r="CF8" s="11" t="n">
+        <v>1.47941744357466</v>
+      </c>
+      <c r="CG8" s="12" t="n">
+        <v>0.0038084404431366</v>
+      </c>
+      <c r="CH8" s="12" t="n">
+        <v>0.0141630130200952</v>
+      </c>
+      <c r="CI8" s="11" t="n">
+        <v>2.34510833736241</v>
+      </c>
+      <c r="CJ8" s="12" t="n">
+        <v>1.89352078133194e-05</v>
+      </c>
+      <c r="CK8" s="12" t="n">
+        <v>7.133106575596e-05</v>
+      </c>
+      <c r="CL8" s="11" t="n">
+        <v>0.857967972543863</v>
+      </c>
+      <c r="CM8" s="12" t="n">
+        <v>0.10294544189322</v>
+      </c>
+      <c r="CN8" s="12" t="n">
+        <v>0.246017222039641</v>
+      </c>
+      <c r="CO8" s="11" t="n">
         <v>-2.31154743014523</v>
       </c>
-      <c r="CG8" s="12" t="n">
+      <c r="CP8" s="12" t="n">
         <v>6.76752711472934e-38</v>
       </c>
-      <c r="CH8" s="12" t="n">
+      <c r="CQ8" s="12" t="n">
         <v>1.00194926374712e-36</v>
       </c>
-      <c r="CI8" s="11" t="n">
+      <c r="CR8" s="11" t="n">
         <v>-2.65163850649463</v>
       </c>
-      <c r="CJ8" s="10" t="n"/>
-      <c r="CK8" s="12" t="n">
+      <c r="CS8" s="10" t="n"/>
+      <c r="CT8" s="12" t="n">
         <v>5.5825482944821e-16</v>
       </c>
-      <c r="CL8" s="11" t="n">
+      <c r="CU8" s="11" t="n">
         <v>-2.77393099960309</v>
       </c>
-      <c r="CM8" s="10" t="n"/>
-      <c r="CN8" s="12" t="n">
+      <c r="CV8" s="10" t="n"/>
+      <c r="CW8" s="12" t="n">
         <v>5.18098494684006e-151</v>
       </c>
-      <c r="CO8" s="11" t="n">
+      <c r="CX8" s="11" t="n">
         <v>1.49510505291086</v>
       </c>
-      <c r="CP8" s="12" t="n">
+      <c r="CY8" s="12" t="n">
         <v>1.96773871980725e-06</v>
       </c>
-      <c r="CQ8" s="12" t="n">
+      <c r="CZ8" s="12" t="n">
         <v>4.95593628556767e-06</v>
       </c>
-      <c r="CR8" s="11" t="n">
+      <c r="DA8" s="11" t="n">
         <v>1.48820795285742</v>
       </c>
-      <c r="CS8" s="12" t="n">
+      <c r="DB8" s="12" t="n">
         <v>2.9929607006367e-06</v>
       </c>
-      <c r="CT8" s="12" t="n">
+      <c r="DC8" s="12" t="n">
         <v>1.03056510814091e-05</v>
       </c>
-      <c r="CU8" s="10" t="b">
+      <c r="DD8" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="CV8" s="10" t="inlineStr">
+      <c r="DE8" s="10" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="CW8" s="10" t="b">
+      <c r="DF8" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3248,55 +3473,82 @@
         <v>0.1522574762532724</v>
       </c>
       <c r="CF9" s="11" t="n">
+        <v>1.1300415638916</v>
+      </c>
+      <c r="CG9" s="12" t="n">
+        <v>0.0256854320194517</v>
+      </c>
+      <c r="CH9" s="12" t="n">
+        <v>0.059575203059892</v>
+      </c>
+      <c r="CI9" s="11" t="n">
+        <v>1.76569125688894</v>
+      </c>
+      <c r="CJ9" s="12" t="n">
+        <v>0.0013225792046715</v>
+      </c>
+      <c r="CK9" s="12" t="n">
+        <v>0.0030586054052522</v>
+      </c>
+      <c r="CL9" s="11" t="n">
+        <v>0.644209335321822</v>
+      </c>
+      <c r="CM9" s="12" t="n">
+        <v>0.281501222558551</v>
+      </c>
+      <c r="CN9" s="12" t="n">
+        <v>0.474387058544431</v>
+      </c>
+      <c r="CO9" s="11" t="n">
         <v>1.67776809443425</v>
       </c>
-      <c r="CG9" s="12" t="n">
+      <c r="CP9" s="12" t="n">
         <v>2.17096833252776e-28</v>
       </c>
-      <c r="CH9" s="12" t="n">
+      <c r="CQ9" s="12" t="n">
         <v>1.94937888731656e-27</v>
       </c>
-      <c r="CI9" s="11" t="n">
+      <c r="CR9" s="11" t="n">
         <v>1.35884211776825</v>
       </c>
-      <c r="CJ9" s="10" t="n"/>
-      <c r="CK9" s="12" t="n">
+      <c r="CS9" s="10" t="n"/>
+      <c r="CT9" s="12" t="n">
         <v>6.64233857783558e-10</v>
       </c>
-      <c r="CL9" s="11" t="n">
+      <c r="CU9" s="11" t="n">
         <v>1.93451996054779</v>
       </c>
-      <c r="CM9" s="10" t="n"/>
-      <c r="CN9" s="12" t="n">
+      <c r="CV9" s="10" t="n"/>
+      <c r="CW9" s="12" t="n">
         <v>5.53827226523876e-182</v>
       </c>
-      <c r="CO9" s="11" t="n">
+      <c r="CX9" s="11" t="n">
         <v>1.65228981386363</v>
       </c>
-      <c r="CP9" s="12" t="n">
+      <c r="CY9" s="12" t="n">
         <v>3.14204380887234e-18</v>
       </c>
-      <c r="CQ9" s="12" t="n">
+      <c r="CZ9" s="12" t="n">
         <v>4.53590135709114e-17</v>
       </c>
-      <c r="CR9" s="11" t="n">
+      <c r="DA9" s="11" t="n">
         <v>2.02638428887108</v>
       </c>
-      <c r="CS9" s="12" t="n">
+      <c r="DB9" s="12" t="n">
         <v>3.95123181281533e-24</v>
       </c>
-      <c r="CT9" s="12" t="n">
+      <c r="DC9" s="12" t="n">
         <v>4.96711430784706e-22</v>
       </c>
-      <c r="CU9" s="10" t="b">
+      <c r="DD9" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV9" s="10" t="inlineStr">
+      <c r="DE9" s="10" t="inlineStr">
         <is>
           <t>Mouse_M1</t>
         </is>
       </c>
-      <c r="CW9" s="10" t="b">
+      <c r="DF9" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3549,55 +3801,82 @@
         <v>0.113160852080421</v>
       </c>
       <c r="CF10" s="11" t="n">
+        <v>3.88722641396611</v>
+      </c>
+      <c r="CG10" s="12" t="n">
+        <v>5.54977807928861e-05</v>
+      </c>
+      <c r="CH10" s="12" t="n">
+        <v>0.0007429649958188</v>
+      </c>
+      <c r="CI10" s="11" t="n">
+        <v>2.50419699416761</v>
+      </c>
+      <c r="CJ10" s="12" t="n">
+        <v>0.0001056220241727</v>
+      </c>
+      <c r="CK10" s="12" t="n">
+        <v>0.0003250612605267</v>
+      </c>
+      <c r="CL10" s="11" t="n">
+        <v>-1.39527326008543</v>
+      </c>
+      <c r="CM10" s="12" t="n">
+        <v>0.0107387641972146</v>
+      </c>
+      <c r="CN10" s="12" t="n">
+        <v>0.0538286085678326</v>
+      </c>
+      <c r="CO10" s="11" t="n">
         <v>-0.332774350351039</v>
       </c>
-      <c r="CG10" s="12" t="n">
+      <c r="CP10" s="12" t="n">
         <v>0.004030261670043</v>
       </c>
-      <c r="CH10" s="12" t="n">
+      <c r="CQ10" s="12" t="n">
         <v>0.0056108149534475</v>
       </c>
-      <c r="CI10" s="11" t="n">
+      <c r="CR10" s="11" t="n">
         <v>-0.287899078091318</v>
       </c>
-      <c r="CJ10" s="10" t="n"/>
-      <c r="CK10" s="12" t="n">
+      <c r="CS10" s="10" t="n"/>
+      <c r="CT10" s="12" t="n">
         <v>0.0630958634561159</v>
       </c>
-      <c r="CL10" s="11" t="n">
+      <c r="CU10" s="11" t="n">
         <v>-0.870991369969248</v>
       </c>
-      <c r="CM10" s="10" t="n"/>
-      <c r="CN10" s="12" t="n">
+      <c r="CV10" s="10" t="n"/>
+      <c r="CW10" s="12" t="n">
         <v>1.96360039927566e-53</v>
       </c>
-      <c r="CO10" s="11" t="n">
+      <c r="CX10" s="11" t="n">
         <v>2.95811168926125</v>
       </c>
-      <c r="CP10" s="12" t="n">
+      <c r="CY10" s="12" t="n">
         <v>9.498025206415731e-15</v>
       </c>
-      <c r="CQ10" s="12" t="n">
+      <c r="CZ10" s="12" t="n">
         <v>7.4843420071574e-14</v>
       </c>
-      <c r="CR10" s="11" t="n">
+      <c r="DA10" s="11" t="n">
         <v>3.09931636991049</v>
       </c>
-      <c r="CS10" s="12" t="n">
+      <c r="DB10" s="12" t="n">
         <v>5.8326135795105e-14</v>
       </c>
-      <c r="CT10" s="12" t="n">
+      <c r="DC10" s="12" t="n">
         <v>8.90172366432001e-13</v>
       </c>
-      <c r="CU10" s="10" t="b">
+      <c r="DD10" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="CV10" s="10" t="inlineStr">
+      <c r="DE10" s="10" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="CW10" s="10" t="b">
+      <c r="DF10" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3717,12 +3996,21 @@
       <c r="CS11" s="10" t="n"/>
       <c r="CT11" s="10" t="n"/>
       <c r="CU11" s="10" t="n"/>
-      <c r="CV11" s="10" t="inlineStr">
+      <c r="CV11" s="10" t="n"/>
+      <c r="CW11" s="10" t="n"/>
+      <c r="CX11" s="10" t="n"/>
+      <c r="CY11" s="10" t="n"/>
+      <c r="CZ11" s="10" t="n"/>
+      <c r="DA11" s="10" t="n"/>
+      <c r="DB11" s="10" t="n"/>
+      <c r="DC11" s="10" t="n"/>
+      <c r="DD11" s="10" t="n"/>
+      <c r="DE11" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW11" s="10" t="n"/>
+      <c r="DF11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -3943,55 +4231,76 @@
         <v>0.4230720548210044</v>
       </c>
       <c r="CF12" s="11" t="n">
+        <v>8.033077507693999</v>
+      </c>
+      <c r="CG12" s="12" t="n">
+        <v>0.0002403481632008</v>
+      </c>
+      <c r="CH12" s="12" t="n">
+        <v>0.0019160728794273</v>
+      </c>
+      <c r="CI12" s="10" t="n"/>
+      <c r="CJ12" s="10" t="n"/>
+      <c r="CK12" s="10" t="n"/>
+      <c r="CL12" s="11" t="n">
+        <v>0.424416454313631</v>
+      </c>
+      <c r="CM12" s="12" t="n">
+        <v>0.768196840036792</v>
+      </c>
+      <c r="CN12" s="12" t="n">
+        <v>0.869490607643031</v>
+      </c>
+      <c r="CO12" s="11" t="n">
         <v>3.87915708772113</v>
       </c>
-      <c r="CG12" s="12" t="n">
+      <c r="CP12" s="12" t="n">
         <v>1.30269848302403e-18</v>
       </c>
-      <c r="CH12" s="12" t="n">
+      <c r="CQ12" s="12" t="n">
         <v>6.29239733091449e-18</v>
       </c>
-      <c r="CI12" s="11" t="n">
+      <c r="CR12" s="11" t="n">
         <v>3.31849537880916</v>
       </c>
-      <c r="CJ12" s="10" t="n"/>
-      <c r="CK12" s="12" t="n">
+      <c r="CS12" s="10" t="n"/>
+      <c r="CT12" s="12" t="n">
         <v>1.2530172240449e-09</v>
       </c>
-      <c r="CL12" s="11" t="n">
+      <c r="CU12" s="11" t="n">
         <v>2.96080985389408</v>
       </c>
-      <c r="CM12" s="10" t="n"/>
-      <c r="CN12" s="12" t="n">
+      <c r="CV12" s="10" t="n"/>
+      <c r="CW12" s="12" t="n">
         <v>1.26928993221417e-89</v>
       </c>
-      <c r="CO12" s="11" t="n">
+      <c r="CX12" s="11" t="n">
         <v>6.12870673194068</v>
       </c>
-      <c r="CP12" s="12" t="n">
+      <c r="CY12" s="12" t="n">
         <v>3.861565125239149e-18</v>
       </c>
-      <c r="CQ12" s="12" t="n">
+      <c r="CZ12" s="12" t="n">
         <v>5.47771298197193e-17</v>
       </c>
-      <c r="CR12" s="11" t="n">
+      <c r="DA12" s="11" t="n">
         <v>6.65778199848213</v>
       </c>
-      <c r="CS12" s="12" t="n">
+      <c r="DB12" s="12" t="n">
         <v>1.07801469203076e-15</v>
       </c>
-      <c r="CT12" s="12" t="n">
+      <c r="DC12" s="12" t="n">
         <v>2.40264829727727e-14</v>
       </c>
-      <c r="CU12" s="10" t="b">
+      <c r="DD12" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV12" s="10" t="inlineStr">
+      <c r="DE12" s="10" t="inlineStr">
         <is>
           <t>Gao_effect_size</t>
         </is>
       </c>
-      <c r="CW12" s="10" t="b">
+      <c r="DF12" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4135,34 +4444,43 @@
       <c r="CE13" s="12" t="n">
         <v>0.5167961546965525</v>
       </c>
-      <c r="CF13" s="11" t="n">
-        <v>7.36478688339062</v>
-      </c>
-      <c r="CG13" s="12" t="n">
-        <v>2.75951809166302e-12</v>
-      </c>
-      <c r="CH13" s="12" t="n">
-        <v>8.22286827863327e-12</v>
-      </c>
+      <c r="CF13" s="10" t="n"/>
+      <c r="CG13" s="10" t="n"/>
+      <c r="CH13" s="10" t="n"/>
       <c r="CI13" s="10" t="n"/>
       <c r="CJ13" s="10" t="n"/>
       <c r="CK13" s="10" t="n"/>
       <c r="CL13" s="10" t="n"/>
       <c r="CM13" s="10" t="n"/>
       <c r="CN13" s="10" t="n"/>
-      <c r="CO13" s="10" t="n"/>
-      <c r="CP13" s="10" t="n"/>
-      <c r="CQ13" s="10" t="n"/>
+      <c r="CO13" s="11" t="n">
+        <v>7.36478688339062</v>
+      </c>
+      <c r="CP13" s="12" t="n">
+        <v>2.75951809166302e-12</v>
+      </c>
+      <c r="CQ13" s="12" t="n">
+        <v>8.22286827863327e-12</v>
+      </c>
       <c r="CR13" s="10" t="n"/>
       <c r="CS13" s="10" t="n"/>
       <c r="CT13" s="10" t="n"/>
       <c r="CU13" s="10" t="n"/>
-      <c r="CV13" s="10" t="inlineStr">
+      <c r="CV13" s="10" t="n"/>
+      <c r="CW13" s="10" t="n"/>
+      <c r="CX13" s="10" t="n"/>
+      <c r="CY13" s="10" t="n"/>
+      <c r="CZ13" s="10" t="n"/>
+      <c r="DA13" s="10" t="n"/>
+      <c r="DB13" s="10" t="n"/>
+      <c r="DC13" s="10" t="n"/>
+      <c r="DD13" s="10" t="n"/>
+      <c r="DE13" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW13" s="10" t="b">
+      <c r="DF13" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4402,56 +4720,65 @@
       <c r="CE14" s="12" t="n">
         <v>0.196138116506484</v>
       </c>
-      <c r="CF14" s="11" t="n">
+      <c r="CF14" s="10" t="n"/>
+      <c r="CG14" s="10" t="n"/>
+      <c r="CH14" s="10" t="n"/>
+      <c r="CI14" s="10" t="n"/>
+      <c r="CJ14" s="10" t="n"/>
+      <c r="CK14" s="10" t="n"/>
+      <c r="CL14" s="10" t="n"/>
+      <c r="CM14" s="10" t="n"/>
+      <c r="CN14" s="10" t="n"/>
+      <c r="CO14" s="11" t="n">
         <v>0.745426223148137</v>
       </c>
-      <c r="CG14" s="12" t="n">
+      <c r="CP14" s="12" t="n">
         <v>0.004762342849978</v>
       </c>
-      <c r="CH14" s="12" t="n">
+      <c r="CQ14" s="12" t="n">
         <v>0.0065844952076465</v>
       </c>
-      <c r="CI14" s="11" t="n">
+      <c r="CR14" s="11" t="n">
         <v>-0.0554276379201352</v>
       </c>
-      <c r="CJ14" s="10" t="n"/>
-      <c r="CK14" s="12" t="n">
+      <c r="CS14" s="10" t="n"/>
+      <c r="CT14" s="12" t="n">
         <v>0.877606667692742</v>
       </c>
-      <c r="CL14" s="11" t="n">
+      <c r="CU14" s="11" t="n">
         <v>0.654734068205669</v>
       </c>
-      <c r="CM14" s="10" t="n"/>
-      <c r="CN14" s="12" t="n">
+      <c r="CV14" s="10" t="n"/>
+      <c r="CW14" s="12" t="n">
         <v>2.91727193989458e-10</v>
       </c>
-      <c r="CO14" s="11" t="n">
+      <c r="CX14" s="11" t="n">
         <v>4.55190891741079</v>
       </c>
-      <c r="CP14" s="12" t="n">
+      <c r="CY14" s="12" t="n">
         <v>3.26690738255902e-17</v>
       </c>
-      <c r="CQ14" s="12" t="n">
+      <c r="CZ14" s="12" t="n">
         <v>3.90964746694522e-16</v>
       </c>
-      <c r="CR14" s="11" t="n">
+      <c r="DA14" s="11" t="n">
         <v>4.66154103734362</v>
       </c>
-      <c r="CS14" s="12" t="n">
+      <c r="DB14" s="12" t="n">
         <v>1.95087802642985e-16</v>
       </c>
-      <c r="CT14" s="12" t="n">
+      <c r="DC14" s="12" t="n">
         <v>5.083278726684771e-15</v>
       </c>
-      <c r="CU14" s="10" t="b">
+      <c r="DD14" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV14" s="10" t="inlineStr">
+      <c r="DE14" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW14" s="10" t="b">
+      <c r="DF14" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4668,55 +4995,82 @@
       <c r="CD15" s="10" t="n"/>
       <c r="CE15" s="10" t="n"/>
       <c r="CF15" s="11" t="n">
+        <v>-1.37200412504424</v>
+      </c>
+      <c r="CG15" s="12" t="n">
+        <v>0.045467583664282</v>
+      </c>
+      <c r="CH15" s="12" t="n">
+        <v>0.0923969796406548</v>
+      </c>
+      <c r="CI15" s="11" t="n">
+        <v>-1.07750080237949</v>
+      </c>
+      <c r="CJ15" s="12" t="n">
+        <v>0.009031611015030401</v>
+      </c>
+      <c r="CK15" s="12" t="n">
+        <v>0.0170244497823767</v>
+      </c>
+      <c r="CL15" s="11" t="n">
+        <v>0.29990364285937</v>
+      </c>
+      <c r="CM15" s="12" t="n">
+        <v>0.580312956094862</v>
+      </c>
+      <c r="CN15" s="12" t="n">
+        <v>0.739040894535545</v>
+      </c>
+      <c r="CO15" s="11" t="n">
         <v>2.02713488622674</v>
       </c>
-      <c r="CG15" s="12" t="n">
+      <c r="CP15" s="12" t="n">
         <v>3.37605515080753e-27</v>
       </c>
-      <c r="CH15" s="12" t="n">
+      <c r="CQ15" s="12" t="n">
         <v>2.81710826844307e-26</v>
       </c>
-      <c r="CI15" s="11" t="n">
+      <c r="CR15" s="11" t="n">
         <v>1.67806283998944</v>
       </c>
-      <c r="CJ15" s="10" t="n"/>
-      <c r="CK15" s="12" t="n">
+      <c r="CS15" s="10" t="n"/>
+      <c r="CT15" s="12" t="n">
         <v>1.54280444497508e-13</v>
       </c>
-      <c r="CL15" s="11" t="n">
+      <c r="CU15" s="11" t="n">
         <v>2.23031464377784</v>
       </c>
-      <c r="CM15" s="10" t="n"/>
-      <c r="CN15" s="12" t="n">
+      <c r="CV15" s="10" t="n"/>
+      <c r="CW15" s="12" t="n">
         <v>2.8032069092347e-196</v>
       </c>
-      <c r="CO15" s="11" t="n">
+      <c r="CX15" s="11" t="n">
         <v>1.34994899681148</v>
       </c>
-      <c r="CP15" s="12" t="n">
+      <c r="CY15" s="12" t="n">
         <v>3.55649118340587e-07</v>
       </c>
-      <c r="CQ15" s="12" t="n">
+      <c r="CZ15" s="12" t="n">
         <v>9.80972117705192e-07</v>
       </c>
-      <c r="CR15" s="11" t="n">
+      <c r="DA15" s="11" t="n">
         <v>0.819685047138303</v>
       </c>
-      <c r="CS15" s="12" t="n">
+      <c r="DB15" s="12" t="n">
         <v>0.0008348816534986</v>
       </c>
-      <c r="CT15" s="12" t="n">
+      <c r="DC15" s="12" t="n">
         <v>0.0018452635682124</v>
       </c>
-      <c r="CU15" s="10" t="b">
+      <c r="DD15" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV15" s="10" t="inlineStr">
+      <c r="DE15" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW15" s="10" t="b">
+      <c r="DF15" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4969,53 +5323,80 @@
         <v>0.0214908097074646</v>
       </c>
       <c r="CF16" s="11" t="n">
+        <v>6.46064866295748</v>
+      </c>
+      <c r="CG16" s="12" t="n">
+        <v>8.56166556337317e-07</v>
+      </c>
+      <c r="CH16" s="12" t="n">
+        <v>7.56913879896506e-05</v>
+      </c>
+      <c r="CI16" s="11" t="n">
+        <v>6.36969425628561</v>
+      </c>
+      <c r="CJ16" s="12" t="n">
+        <v>1.02849644899664e-06</v>
+      </c>
+      <c r="CK16" s="12" t="n">
+        <v>5.64348640188959e-06</v>
+      </c>
+      <c r="CL16" s="11" t="n">
+        <v>-0.09608787284953101</v>
+      </c>
+      <c r="CM16" s="12" t="n">
+        <v>0.901534946335795</v>
+      </c>
+      <c r="CN16" s="12" t="n">
+        <v>0.947277672295731</v>
+      </c>
+      <c r="CO16" s="11" t="n">
         <v>0.221508245845491</v>
       </c>
-      <c r="CG16" s="12" t="n">
+      <c r="CP16" s="12" t="n">
         <v>0.173742792077452</v>
       </c>
-      <c r="CH16" s="12" t="n">
+      <c r="CQ16" s="12" t="n">
         <v>0.200599382174245</v>
       </c>
-      <c r="CI16" s="11" t="n">
+      <c r="CR16" s="11" t="n">
         <v>0.438961218681568</v>
       </c>
-      <c r="CJ16" s="10" t="n"/>
-      <c r="CK16" s="12" t="n">
+      <c r="CS16" s="10" t="n"/>
+      <c r="CT16" s="12" t="n">
         <v>0.0134024246828029</v>
       </c>
-      <c r="CL16" s="11" t="n">
+      <c r="CU16" s="11" t="n">
         <v>-0.963225217532367</v>
       </c>
-      <c r="CM16" s="10" t="n"/>
-      <c r="CN16" s="12" t="n">
+      <c r="CV16" s="10" t="n"/>
+      <c r="CW16" s="12" t="n">
         <v>3.40497651840545e-39</v>
       </c>
-      <c r="CO16" s="11" t="n">
+      <c r="CX16" s="11" t="n">
         <v>0.628181546646409</v>
       </c>
-      <c r="CP16" s="12" t="n">
+      <c r="CY16" s="12" t="n">
         <v>0.0182260506391194</v>
       </c>
-      <c r="CQ16" s="12" t="n">
+      <c r="CZ16" s="12" t="n">
         <v>0.0265645185155706</v>
       </c>
-      <c r="CR16" s="11" t="n">
+      <c r="DA16" s="11" t="n">
         <v>2.5517728210184</v>
       </c>
-      <c r="CS16" s="12" t="n">
+      <c r="DB16" s="12" t="n">
         <v>3.87588161752696e-16</v>
       </c>
-      <c r="CT16" s="12" t="n">
+      <c r="DC16" s="12" t="n">
         <v>9.52748875828112e-15</v>
       </c>
-      <c r="CU16" s="10" t="n"/>
-      <c r="CV16" s="10" t="inlineStr">
+      <c r="DD16" s="10" t="n"/>
+      <c r="DE16" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW16" s="10" t="b">
+      <c r="DF16" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5262,53 +5643,80 @@
         <v>0.0641323743436161</v>
       </c>
       <c r="CF17" s="11" t="n">
+        <v>7.87813890331585</v>
+      </c>
+      <c r="CG17" s="12" t="n">
+        <v>3.69613222250938e-07</v>
+      </c>
+      <c r="CH17" s="12" t="n">
+        <v>5.17327547957911e-05</v>
+      </c>
+      <c r="CI17" s="11" t="n">
+        <v>7.35140825550013</v>
+      </c>
+      <c r="CJ17" s="12" t="n">
+        <v>1.62741979236739e-14</v>
+      </c>
+      <c r="CK17" s="12" t="n">
+        <v>9.866397879417609e-13</v>
+      </c>
+      <c r="CL17" s="11" t="n">
+        <v>-0.523442393383548</v>
+      </c>
+      <c r="CM17" s="12" t="n">
+        <v>0.145327255543219</v>
+      </c>
+      <c r="CN17" s="12" t="n">
+        <v>0.308880717619424</v>
+      </c>
+      <c r="CO17" s="11" t="n">
         <v>-0.0713325886046302</v>
       </c>
-      <c r="CG17" s="12" t="n">
+      <c r="CP17" s="12" t="n">
         <v>0.6986181224745009</v>
       </c>
-      <c r="CH17" s="12" t="n">
+      <c r="CQ17" s="12" t="n">
         <v>0.727776668621956</v>
       </c>
-      <c r="CI17" s="11" t="n">
+      <c r="CR17" s="11" t="n">
         <v>0.163688982157025</v>
       </c>
-      <c r="CJ17" s="10" t="n"/>
-      <c r="CK17" s="12" t="n">
+      <c r="CS17" s="10" t="n"/>
+      <c r="CT17" s="12" t="n">
         <v>0.469274589335398</v>
       </c>
-      <c r="CL17" s="11" t="n">
+      <c r="CU17" s="11" t="n">
         <v>-2.00691071894571</v>
       </c>
-      <c r="CM17" s="10" t="n"/>
-      <c r="CN17" s="12" t="n">
+      <c r="CV17" s="10" t="n"/>
+      <c r="CW17" s="12" t="n">
         <v>2.59613475442048e-87</v>
       </c>
-      <c r="CO17" s="11" t="n">
+      <c r="CX17" s="11" t="n">
         <v>1.01939227713914</v>
       </c>
-      <c r="CP17" s="12" t="n">
+      <c r="CY17" s="12" t="n">
         <v>0.0004851373297352</v>
       </c>
-      <c r="CQ17" s="12" t="n">
+      <c r="CZ17" s="12" t="n">
         <v>0.0008941031098306</v>
       </c>
-      <c r="CR17" s="11" t="n">
+      <c r="DA17" s="11" t="n">
         <v>2.00247177995832</v>
       </c>
-      <c r="CS17" s="12" t="n">
+      <c r="DB17" s="12" t="n">
         <v>1.54928482128321e-09</v>
       </c>
-      <c r="CT17" s="12" t="n">
+      <c r="DC17" s="12" t="n">
         <v>1.01475323463481e-08</v>
       </c>
-      <c r="CU17" s="10" t="n"/>
-      <c r="CV17" s="10" t="inlineStr">
+      <c r="DD17" s="10" t="n"/>
+      <c r="DE17" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW17" s="10" t="b">
+      <c r="DF17" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5495,39 +5903,54 @@
         <v>0.7966641526807303</v>
       </c>
       <c r="CF18" s="11" t="n">
-        <v>2.49237551608169</v>
+        <v>9.35220034255593</v>
       </c>
       <c r="CG18" s="12" t="n">
-        <v>4.66122658012639e-08</v>
+        <v>6.75086798333578e-06</v>
       </c>
       <c r="CH18" s="12" t="n">
-        <v>9.89278609871959e-08</v>
+        <v>0.0002267684227792</v>
       </c>
       <c r="CI18" s="10" t="n"/>
       <c r="CJ18" s="10" t="n"/>
       <c r="CK18" s="10" t="n"/>
-      <c r="CL18" s="11" t="n">
-        <v>-5.1390419411966</v>
-      </c>
+      <c r="CL18" s="10" t="n"/>
       <c r="CM18" s="10" t="n"/>
-      <c r="CN18" s="12" t="n">
-        <v>2.06267277087821e-141</v>
-      </c>
-      <c r="CO18" s="10" t="n"/>
-      <c r="CP18" s="10" t="n"/>
-      <c r="CQ18" s="10" t="n"/>
+      <c r="CN18" s="10" t="n"/>
+      <c r="CO18" s="11" t="n">
+        <v>2.49237551608169</v>
+      </c>
+      <c r="CP18" s="12" t="n">
+        <v>4.66122658012639e-08</v>
+      </c>
+      <c r="CQ18" s="12" t="n">
+        <v>9.89278609871959e-08</v>
+      </c>
       <c r="CR18" s="10" t="n"/>
       <c r="CS18" s="10" t="n"/>
       <c r="CT18" s="10" t="n"/>
-      <c r="CU18" s="10" t="b">
+      <c r="CU18" s="11" t="n">
+        <v>-5.1390419411966</v>
+      </c>
+      <c r="CV18" s="10" t="n"/>
+      <c r="CW18" s="12" t="n">
+        <v>2.06267277087821e-141</v>
+      </c>
+      <c r="CX18" s="10" t="n"/>
+      <c r="CY18" s="10" t="n"/>
+      <c r="CZ18" s="10" t="n"/>
+      <c r="DA18" s="10" t="n"/>
+      <c r="DB18" s="10" t="n"/>
+      <c r="DC18" s="10" t="n"/>
+      <c r="DD18" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV18" s="10" t="inlineStr">
+      <c r="DE18" s="10" t="inlineStr">
         <is>
           <t>Gao_effect_size</t>
         </is>
       </c>
-      <c r="CW18" s="10" t="b">
+      <c r="DF18" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5780,55 +6203,82 @@
         <v>0.1984430612441762</v>
       </c>
       <c r="CF19" s="11" t="n">
+        <v>0.862516349577405</v>
+      </c>
+      <c r="CG19" s="12" t="n">
+        <v>0.0151237505805366</v>
+      </c>
+      <c r="CH19" s="12" t="n">
+        <v>0.039624002631286</v>
+      </c>
+      <c r="CI19" s="11" t="n">
+        <v>1.93596804565604</v>
+      </c>
+      <c r="CJ19" s="12" t="n">
+        <v>1.94296808530943e-06</v>
+      </c>
+      <c r="CK19" s="12" t="n">
+        <v>9.67203805884672e-06</v>
+      </c>
+      <c r="CL19" s="11" t="n">
+        <v>1.07566609044384</v>
+      </c>
+      <c r="CM19" s="12" t="n">
+        <v>0.007989982969948</v>
+      </c>
+      <c r="CN19" s="12" t="n">
+        <v>0.0437754758922713</v>
+      </c>
+      <c r="CO19" s="11" t="n">
         <v>2.29482738823638</v>
       </c>
-      <c r="CG19" s="12" t="n">
+      <c r="CP19" s="12" t="n">
         <v>6.31076114404677e-47</v>
       </c>
-      <c r="CH19" s="12" t="n">
+      <c r="CQ19" s="12" t="n">
         <v>1.42962817113811e-45</v>
       </c>
-      <c r="CI19" s="11" t="n">
+      <c r="CR19" s="11" t="n">
         <v>2.52306766993452</v>
       </c>
-      <c r="CJ19" s="10" t="n"/>
-      <c r="CK19" s="12" t="n">
+      <c r="CS19" s="10" t="n"/>
+      <c r="CT19" s="12" t="n">
         <v>2.4050331831309e-18</v>
       </c>
-      <c r="CL19" s="11" t="n">
+      <c r="CU19" s="11" t="n">
         <v>1.81120060518907</v>
       </c>
-      <c r="CM19" s="10" t="n"/>
-      <c r="CN19" s="12" t="n">
+      <c r="CV19" s="10" t="n"/>
+      <c r="CW19" s="12" t="n">
         <v>1.18830611185907e-99</v>
       </c>
-      <c r="CO19" s="11" t="n">
+      <c r="CX19" s="11" t="n">
         <v>2.68701270314905</v>
       </c>
-      <c r="CP19" s="12" t="n">
+      <c r="CY19" s="12" t="n">
         <v>1.48745023055985e-22</v>
       </c>
-      <c r="CQ19" s="12" t="n">
+      <c r="CZ19" s="12" t="n">
         <v>4.66088882479906e-21</v>
       </c>
-      <c r="CR19" s="11" t="n">
+      <c r="DA19" s="11" t="n">
         <v>2.78121905025346</v>
       </c>
-      <c r="CS19" s="12" t="n">
+      <c r="DB19" s="12" t="n">
         <v>6.22873200049136e-24</v>
       </c>
-      <c r="CT19" s="12" t="n">
+      <c r="DC19" s="12" t="n">
         <v>7.438663191586801e-22</v>
       </c>
-      <c r="CU19" s="10" t="b">
+      <c r="DD19" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV19" s="10" t="inlineStr">
+      <c r="DE19" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW19" s="10" t="b">
+      <c r="DF19" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6002,42 +6452,51 @@
       <c r="CE20" s="12" t="n">
         <v>0.4252654067488136</v>
       </c>
-      <c r="CF20" s="11" t="n">
+      <c r="CF20" s="10" t="n"/>
+      <c r="CG20" s="10" t="n"/>
+      <c r="CH20" s="10" t="n"/>
+      <c r="CI20" s="10" t="n"/>
+      <c r="CJ20" s="10" t="n"/>
+      <c r="CK20" s="10" t="n"/>
+      <c r="CL20" s="10" t="n"/>
+      <c r="CM20" s="10" t="n"/>
+      <c r="CN20" s="10" t="n"/>
+      <c r="CO20" s="11" t="n">
         <v>-1.02954992492292</v>
       </c>
-      <c r="CG20" s="12" t="n">
+      <c r="CP20" s="12" t="n">
         <v>6.752440950602e-15</v>
       </c>
-      <c r="CH20" s="12" t="n">
+      <c r="CQ20" s="12" t="n">
         <v>2.46117659047272e-14</v>
       </c>
-      <c r="CI20" s="11" t="n">
+      <c r="CR20" s="11" t="n">
         <v>-0.931053223313861</v>
       </c>
-      <c r="CJ20" s="10" t="n"/>
-      <c r="CK20" s="12" t="n">
+      <c r="CS20" s="10" t="n"/>
+      <c r="CT20" s="12" t="n">
         <v>1.39662055300777e-05</v>
       </c>
-      <c r="CL20" s="11" t="n">
+      <c r="CU20" s="11" t="n">
         <v>-2.59671603848386</v>
       </c>
-      <c r="CM20" s="10" t="n"/>
-      <c r="CN20" s="12" t="n">
+      <c r="CV20" s="10" t="n"/>
+      <c r="CW20" s="12" t="n">
         <v>9.064306931149109e-176</v>
       </c>
-      <c r="CO20" s="10" t="n"/>
-      <c r="CP20" s="10" t="n"/>
-      <c r="CQ20" s="10" t="n"/>
-      <c r="CR20" s="10" t="n"/>
-      <c r="CS20" s="10" t="n"/>
-      <c r="CT20" s="10" t="n"/>
-      <c r="CU20" s="10" t="n"/>
-      <c r="CV20" s="10" t="inlineStr">
+      <c r="CX20" s="10" t="n"/>
+      <c r="CY20" s="10" t="n"/>
+      <c r="CZ20" s="10" t="n"/>
+      <c r="DA20" s="10" t="n"/>
+      <c r="DB20" s="10" t="n"/>
+      <c r="DC20" s="10" t="n"/>
+      <c r="DD20" s="10" t="n"/>
+      <c r="DE20" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW20" s="10" t="b">
+      <c r="DF20" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6290,55 +6749,82 @@
         <v>0.0192839387114911</v>
       </c>
       <c r="CF21" s="11" t="n">
+        <v>4.60399826957088</v>
+      </c>
+      <c r="CG21" s="12" t="n">
+        <v>3.64816058735021e-07</v>
+      </c>
+      <c r="CH21" s="12" t="n">
+        <v>5.17327547957911e-05</v>
+      </c>
+      <c r="CI21" s="11" t="n">
+        <v>1.43478024952675</v>
+      </c>
+      <c r="CJ21" s="12" t="n">
+        <v>0.0881202978323723</v>
+      </c>
+      <c r="CK21" s="12" t="n">
+        <v>0.128530672065721</v>
+      </c>
+      <c r="CL21" s="11" t="n">
+        <v>-3.16833223633969</v>
+      </c>
+      <c r="CM21" s="12" t="n">
+        <v>9.237692867404029e-05</v>
+      </c>
+      <c r="CN21" s="12" t="n">
+        <v>0.0018434078978083</v>
+      </c>
+      <c r="CO21" s="11" t="n">
         <v>1.57367534695579</v>
       </c>
-      <c r="CG21" s="12" t="n">
+      <c r="CP21" s="12" t="n">
         <v>3.54012813986684e-07</v>
       </c>
-      <c r="CH21" s="12" t="n">
+      <c r="CQ21" s="12" t="n">
         <v>6.97929358708266e-07</v>
       </c>
-      <c r="CI21" s="11" t="n">
+      <c r="CR21" s="11" t="n">
         <v>0.646924522534852</v>
       </c>
-      <c r="CJ21" s="10" t="n"/>
-      <c r="CK21" s="12" t="n">
+      <c r="CS21" s="10" t="n"/>
+      <c r="CT21" s="12" t="n">
         <v>0.06882136244602841</v>
       </c>
-      <c r="CL21" s="11" t="n">
+      <c r="CU21" s="11" t="n">
         <v>1.11067385875638</v>
       </c>
-      <c r="CM21" s="10" t="n"/>
-      <c r="CN21" s="12" t="n">
+      <c r="CV21" s="10" t="n"/>
+      <c r="CW21" s="12" t="n">
         <v>6.36402812386608e-27</v>
       </c>
-      <c r="CO21" s="11" t="n">
+      <c r="CX21" s="11" t="n">
         <v>6.30648245228024</v>
       </c>
-      <c r="CP21" s="12" t="n">
+      <c r="CY21" s="12" t="n">
         <v>5.560599802299899e-12</v>
       </c>
-      <c r="CQ21" s="12" t="n">
+      <c r="CZ21" s="12" t="n">
         <v>2.97050435094872e-11</v>
       </c>
-      <c r="CR21" s="11" t="n">
+      <c r="DA21" s="11" t="n">
         <v>6.19072201370017</v>
       </c>
-      <c r="CS21" s="12" t="n">
+      <c r="DB21" s="12" t="n">
         <v>1.99201660424675e-09</v>
       </c>
-      <c r="CT21" s="12" t="n">
+      <c r="DC21" s="12" t="n">
         <v>1.28188549418321e-08</v>
       </c>
-      <c r="CU21" s="10" t="b">
+      <c r="DD21" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="CV21" s="10" t="inlineStr">
+      <c r="DE21" s="10" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="CW21" s="10" t="b">
+      <c r="DF21" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6591,55 +7077,82 @@
         <v>0.0249621809875017</v>
       </c>
       <c r="CF22" s="11" t="n">
+        <v>2.9650929695661</v>
+      </c>
+      <c r="CG22" s="12" t="n">
+        <v>1.89003981918737e-06</v>
+      </c>
+      <c r="CH22" s="12" t="n">
+        <v>0.0001126260091581</v>
+      </c>
+      <c r="CI22" s="11" t="n">
+        <v>3.87027366453888</v>
+      </c>
+      <c r="CJ22" s="12" t="n">
+        <v>1.03913191173216e-10</v>
+      </c>
+      <c r="CK22" s="12" t="n">
+        <v>2.01791840254862e-09</v>
+      </c>
+      <c r="CL22" s="11" t="n">
+        <v>0.900954697441033</v>
+      </c>
+      <c r="CM22" s="12" t="n">
+        <v>0.0215556910271509</v>
+      </c>
+      <c r="CN22" s="12" t="n">
+        <v>0.0856123683270905</v>
+      </c>
+      <c r="CO22" s="11" t="n">
         <v>1.88873842413568</v>
       </c>
-      <c r="CG22" s="12" t="n">
+      <c r="CP22" s="12" t="n">
         <v>8.052214826593391e-14</v>
       </c>
-      <c r="CH22" s="12" t="n">
+      <c r="CQ22" s="12" t="n">
         <v>2.71558850854047e-13</v>
       </c>
-      <c r="CI22" s="11" t="n">
+      <c r="CR22" s="11" t="n">
         <v>1.55366222585167</v>
       </c>
-      <c r="CJ22" s="10" t="n"/>
-      <c r="CK22" s="12" t="n">
+      <c r="CS22" s="10" t="n"/>
+      <c r="CT22" s="12" t="n">
         <v>4.34957901097087e-06</v>
       </c>
-      <c r="CL22" s="11" t="n">
+      <c r="CU22" s="11" t="n">
         <v>3.31365052381195</v>
       </c>
-      <c r="CM22" s="10" t="n"/>
-      <c r="CN22" s="12" t="n">
+      <c r="CV22" s="10" t="n"/>
+      <c r="CW22" s="12" t="n">
         <v>2.57161144762956e-140</v>
       </c>
-      <c r="CO22" s="11" t="n">
+      <c r="CX22" s="11" t="n">
         <v>0.89453255383055</v>
       </c>
-      <c r="CP22" s="12" t="n">
+      <c r="CY22" s="12" t="n">
         <v>0.0194193753110822</v>
       </c>
-      <c r="CQ22" s="12" t="n">
+      <c r="CZ22" s="12" t="n">
         <v>0.0282086724890446</v>
       </c>
-      <c r="CR22" s="11" t="n">
+      <c r="DA22" s="11" t="n">
         <v>3.08813339050379</v>
       </c>
-      <c r="CS22" s="12" t="n">
+      <c r="DB22" s="12" t="n">
         <v>7.167108070420469e-11</v>
       </c>
-      <c r="CT22" s="12" t="n">
+      <c r="DC22" s="12" t="n">
         <v>6.03832015033484e-10</v>
       </c>
-      <c r="CU22" s="10" t="b">
+      <c r="DD22" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV22" s="10" t="inlineStr">
+      <c r="DE22" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW22" s="10" t="b">
+      <c r="DF22" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6892,55 +7405,82 @@
         <v>0.1056460808608395</v>
       </c>
       <c r="CF23" s="11" t="n">
+        <v>7.41424214877531</v>
+      </c>
+      <c r="CG23" s="12" t="n">
+        <v>3.29721335773238e-08</v>
+      </c>
+      <c r="CH23" s="12" t="n">
+        <v>1.49309746139626e-05</v>
+      </c>
+      <c r="CI23" s="11" t="n">
+        <v>7.34274811127424</v>
+      </c>
+      <c r="CJ23" s="12" t="n">
+        <v>1.57217800387344e-06</v>
+      </c>
+      <c r="CK23" s="12" t="n">
+        <v>8.09649956829022e-06</v>
+      </c>
+      <c r="CL23" s="11" t="n">
+        <v>-0.0628151581920966</v>
+      </c>
+      <c r="CM23" s="12" t="n">
+        <v>0.941280045492381</v>
+      </c>
+      <c r="CN23" s="12" t="n">
+        <v>0.967560397666843</v>
+      </c>
+      <c r="CO23" s="11" t="n">
         <v>2.9979635592165</v>
       </c>
-      <c r="CG23" s="12" t="n">
+      <c r="CP23" s="12" t="n">
         <v>2.4024716743736e-15</v>
       </c>
-      <c r="CH23" s="12" t="n">
+      <c r="CQ23" s="12" t="n">
         <v>9.1037634158314e-15</v>
       </c>
-      <c r="CI23" s="11" t="n">
+      <c r="CR23" s="11" t="n">
         <v>1.76009229587045</v>
       </c>
-      <c r="CJ23" s="10" t="n"/>
-      <c r="CK23" s="12" t="n">
+      <c r="CS23" s="10" t="n"/>
+      <c r="CT23" s="12" t="n">
         <v>0.0003603481422587</v>
       </c>
-      <c r="CL23" s="11" t="n">
+      <c r="CU23" s="11" t="n">
         <v>4.21890908178643</v>
       </c>
-      <c r="CM23" s="10" t="n"/>
-      <c r="CN23" s="12" t="n">
+      <c r="CV23" s="10" t="n"/>
+      <c r="CW23" s="12" t="n">
         <v>6.612153004650101e-150</v>
       </c>
-      <c r="CO23" s="11" t="n">
+      <c r="CX23" s="11" t="n">
         <v>1.51085977279679</v>
       </c>
-      <c r="CP23" s="12" t="n">
+      <c r="CY23" s="12" t="n">
         <v>0.001401194065142</v>
       </c>
-      <c r="CQ23" s="12" t="n">
+      <c r="CZ23" s="12" t="n">
         <v>0.0024078517284058</v>
       </c>
-      <c r="CR23" s="11" t="n">
+      <c r="DA23" s="11" t="n">
         <v>3.74403292270937</v>
       </c>
-      <c r="CS23" s="12" t="n">
+      <c r="DB23" s="12" t="n">
         <v>3.13405927259939e-10</v>
       </c>
-      <c r="CT23" s="12" t="n">
+      <c r="DC23" s="12" t="n">
         <v>2.34294227624527e-09</v>
       </c>
-      <c r="CU23" s="10" t="b">
+      <c r="DD23" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV23" s="10" t="inlineStr">
+      <c r="DE23" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW23" s="10" t="b">
+      <c r="DF23" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7193,55 +7733,82 @@
         <v>0.4310353485112275</v>
       </c>
       <c r="CF24" s="11" t="n">
+        <v>-4.04071578384915</v>
+      </c>
+      <c r="CG24" s="12" t="n">
+        <v>1.89569371023579e-05</v>
+      </c>
+      <c r="CH24" s="12" t="n">
+        <v>0.0003999388444738</v>
+      </c>
+      <c r="CI24" s="11" t="n">
+        <v>-3.92423482458367</v>
+      </c>
+      <c r="CJ24" s="12" t="n">
+        <v>6.954897163013059e-11</v>
+      </c>
+      <c r="CK24" s="12" t="n">
+        <v>1.42675840837932e-09</v>
+      </c>
+      <c r="CL24" s="11" t="n">
+        <v>0.0874234303878506</v>
+      </c>
+      <c r="CM24" s="12" t="n">
+        <v>0.89809201905529</v>
+      </c>
+      <c r="CN24" s="12" t="n">
+        <v>0.945741949562192</v>
+      </c>
+      <c r="CO24" s="11" t="n">
         <v>1.36639206277824</v>
       </c>
-      <c r="CG24" s="12" t="n">
+      <c r="CP24" s="12" t="n">
         <v>2.03372402737343e-41</v>
       </c>
-      <c r="CH24" s="12" t="n">
+      <c r="CQ24" s="12" t="n">
         <v>3.52762315301601e-40</v>
       </c>
-      <c r="CI24" s="11" t="n">
+      <c r="CR24" s="11" t="n">
         <v>1.26799737584483</v>
       </c>
-      <c r="CJ24" s="10" t="n"/>
-      <c r="CK24" s="12" t="n">
+      <c r="CS24" s="10" t="n"/>
+      <c r="CT24" s="12" t="n">
         <v>1.49985004748258e-15</v>
       </c>
-      <c r="CL24" s="11" t="n">
+      <c r="CU24" s="11" t="n">
         <v>1.14584323905699</v>
       </c>
-      <c r="CM24" s="10" t="n"/>
-      <c r="CN24" s="12" t="n">
+      <c r="CV24" s="10" t="n"/>
+      <c r="CW24" s="12" t="n">
         <v>1.14963661364459e-101</v>
       </c>
-      <c r="CO24" s="11" t="n">
+      <c r="CX24" s="11" t="n">
         <v>2.10989447178502</v>
       </c>
-      <c r="CP24" s="12" t="n">
+      <c r="CY24" s="12" t="n">
         <v>2.88137668850818e-25</v>
       </c>
-      <c r="CQ24" s="12" t="n">
+      <c r="CZ24" s="12" t="n">
         <v>1.66711463835891e-23</v>
       </c>
-      <c r="CR24" s="11" t="n">
+      <c r="DA24" s="11" t="n">
         <v>1.38530001359927</v>
       </c>
-      <c r="CS24" s="12" t="n">
+      <c r="DB24" s="12" t="n">
         <v>6.65930047988967e-16</v>
       </c>
-      <c r="CT24" s="12" t="n">
+      <c r="DC24" s="12" t="n">
         <v>1.57482566299173e-14</v>
       </c>
-      <c r="CU24" s="10" t="b">
+      <c r="DD24" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV24" s="10" t="inlineStr">
+      <c r="DE24" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW24" s="10" t="b">
+      <c r="DF24" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7480,53 +8047,80 @@
         <v>0.1048839357952966</v>
       </c>
       <c r="CF25" s="11" t="n">
+        <v>-0.495920417345305</v>
+      </c>
+      <c r="CG25" s="12" t="n">
+        <v>0.1024173781896</v>
+      </c>
+      <c r="CH25" s="12" t="n">
+        <v>0.173743434454232</v>
+      </c>
+      <c r="CI25" s="11" t="n">
+        <v>-0.243976421699182</v>
+      </c>
+      <c r="CJ25" s="12" t="n">
+        <v>0.162443531840294</v>
+      </c>
+      <c r="CK25" s="12" t="n">
+        <v>0.219644862544528</v>
+      </c>
+      <c r="CL25" s="11" t="n">
+        <v>0.25144092000959</v>
+      </c>
+      <c r="CM25" s="12" t="n">
+        <v>0.254520616868706</v>
+      </c>
+      <c r="CN25" s="12" t="n">
+        <v>0.445486703663589</v>
+      </c>
+      <c r="CO25" s="11" t="n">
         <v>0.159515216698385</v>
       </c>
-      <c r="CG25" s="12" t="n">
+      <c r="CP25" s="12" t="n">
         <v>0.168997138922345</v>
       </c>
-      <c r="CH25" s="12" t="n">
+      <c r="CQ25" s="12" t="n">
         <v>0.195416149652159</v>
       </c>
-      <c r="CI25" s="11" t="n">
+      <c r="CR25" s="11" t="n">
         <v>-0.153171304696138</v>
       </c>
-      <c r="CJ25" s="10" t="n"/>
-      <c r="CK25" s="12" t="n">
+      <c r="CS25" s="10" t="n"/>
+      <c r="CT25" s="12" t="n">
         <v>0.394727350213552</v>
       </c>
-      <c r="CL25" s="11" t="n">
+      <c r="CU25" s="11" t="n">
         <v>1.74866833860967</v>
       </c>
-      <c r="CM25" s="10" t="n"/>
-      <c r="CN25" s="12" t="n">
+      <c r="CV25" s="10" t="n"/>
+      <c r="CW25" s="12" t="n">
         <v>7.290050415594039e-80</v>
       </c>
-      <c r="CO25" s="11" t="n">
+      <c r="CX25" s="11" t="n">
         <v>-0.200608496306742</v>
       </c>
-      <c r="CP25" s="12" t="n">
+      <c r="CY25" s="12" t="n">
         <v>0.0597691631926591</v>
       </c>
-      <c r="CQ25" s="12" t="n">
+      <c r="CZ25" s="12" t="n">
         <v>0.079764586113269</v>
       </c>
-      <c r="CR25" s="11" t="n">
+      <c r="DA25" s="11" t="n">
         <v>0.633311174348519</v>
       </c>
-      <c r="CS25" s="12" t="n">
+      <c r="DB25" s="12" t="n">
         <v>4.709231364377331e-09</v>
       </c>
-      <c r="CT25" s="12" t="n">
+      <c r="DC25" s="12" t="n">
         <v>2.78530725063523e-08</v>
       </c>
-      <c r="CU25" s="10" t="n"/>
-      <c r="CV25" s="10" t="inlineStr">
+      <c r="DD25" s="10" t="n"/>
+      <c r="DE25" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW25" s="10" t="b">
+      <c r="DF25" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7773,55 +8367,82 @@
         <v>0.0125449747456729</v>
       </c>
       <c r="CF26" s="11" t="n">
+        <v>5.06396739023882</v>
+      </c>
+      <c r="CG26" s="12" t="n">
+        <v>0.001222033117645</v>
+      </c>
+      <c r="CH26" s="12" t="n">
+        <v>0.0060888350552032</v>
+      </c>
+      <c r="CI26" s="11" t="n">
+        <v>3.31231450153575</v>
+      </c>
+      <c r="CJ26" s="12" t="n">
+        <v>0.0003725471598336</v>
+      </c>
+      <c r="CK26" s="12" t="n">
+        <v>0.0009932371007792</v>
+      </c>
+      <c r="CL26" s="11" t="n">
+        <v>-1.75462609408379</v>
+      </c>
+      <c r="CM26" s="12" t="n">
+        <v>0.0038953430581754</v>
+      </c>
+      <c r="CN26" s="12" t="n">
+        <v>0.0267656370050935</v>
+      </c>
+      <c r="CO26" s="11" t="n">
         <v>-0.455321176539081</v>
       </c>
-      <c r="CG26" s="12" t="n">
+      <c r="CP26" s="12" t="n">
         <v>0.0035334500330038</v>
       </c>
-      <c r="CH26" s="12" t="n">
+      <c r="CQ26" s="12" t="n">
         <v>0.0049482336013326</v>
       </c>
-      <c r="CI26" s="11" t="n">
+      <c r="CR26" s="11" t="n">
         <v>-0.729541570166073</v>
       </c>
-      <c r="CJ26" s="10" t="n"/>
-      <c r="CK26" s="12" t="n">
+      <c r="CS26" s="10" t="n"/>
+      <c r="CT26" s="12" t="n">
         <v>0.0002479126459842</v>
       </c>
-      <c r="CL26" s="11" t="n">
+      <c r="CU26" s="11" t="n">
         <v>-0.447888686877304</v>
       </c>
-      <c r="CM26" s="10" t="n"/>
-      <c r="CN26" s="12" t="n">
+      <c r="CV26" s="10" t="n"/>
+      <c r="CW26" s="12" t="n">
         <v>4.791976846312429e-11</v>
       </c>
-      <c r="CO26" s="11" t="n">
+      <c r="CX26" s="11" t="n">
         <v>-1.80161423745876</v>
       </c>
-      <c r="CP26" s="12" t="n">
+      <c r="CY26" s="12" t="n">
         <v>1.87116695254079e-07</v>
       </c>
-      <c r="CQ26" s="12" t="n">
+      <c r="CZ26" s="12" t="n">
         <v>5.3261029507146e-07</v>
       </c>
-      <c r="CR26" s="11" t="n">
+      <c r="DA26" s="11" t="n">
         <v>-2.212691629844</v>
       </c>
-      <c r="CS26" s="12" t="n">
+      <c r="DB26" s="12" t="n">
         <v>2.36840318624402e-09</v>
       </c>
-      <c r="CT26" s="12" t="n">
+      <c r="DC26" s="12" t="n">
         <v>1.49852477095201e-08</v>
       </c>
-      <c r="CU26" s="10" t="b">
+      <c r="DD26" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="CV26" s="10" t="inlineStr">
+      <c r="DE26" s="10" t="inlineStr">
         <is>
           <t>PASS_FINAL</t>
         </is>
       </c>
-      <c r="CW26" s="10" t="b">
+      <c r="DF26" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8074,55 +8695,82 @@
         <v>0.305671974816681</v>
       </c>
       <c r="CF27" s="11" t="n">
+        <v>4.72812504310472</v>
+      </c>
+      <c r="CG27" s="12" t="n">
+        <v>1.41156083952981e-05</v>
+      </c>
+      <c r="CH27" s="12" t="n">
+        <v>0.0003436286621457</v>
+      </c>
+      <c r="CI27" s="11" t="n">
+        <v>5.80090056105349</v>
+      </c>
+      <c r="CJ27" s="12" t="n">
+        <v>4.3080920664562e-12</v>
+      </c>
+      <c r="CK27" s="12" t="n">
+        <v>1.29277434766857e-10</v>
+      </c>
+      <c r="CL27" s="11" t="n">
+        <v>1.07591969354045</v>
+      </c>
+      <c r="CM27" s="12" t="n">
+        <v>0.009032681933286499</v>
+      </c>
+      <c r="CN27" s="12" t="n">
+        <v>0.0478160700328938</v>
+      </c>
+      <c r="CO27" s="11" t="n">
         <v>0.128296775049852</v>
       </c>
-      <c r="CG27" s="12" t="n">
+      <c r="CP27" s="12" t="n">
         <v>0.470593663854106</v>
       </c>
-      <c r="CH27" s="12" t="n">
+      <c r="CQ27" s="12" t="n">
         <v>0.50825445868746</v>
       </c>
-      <c r="CI27" s="11" t="n">
+      <c r="CR27" s="11" t="n">
         <v>-0.6703771259474079</v>
       </c>
-      <c r="CJ27" s="10" t="n"/>
-      <c r="CK27" s="12" t="n">
+      <c r="CS27" s="10" t="n"/>
+      <c r="CT27" s="12" t="n">
         <v>0.0049436734448703</v>
       </c>
-      <c r="CL27" s="11" t="n">
+      <c r="CU27" s="11" t="n">
         <v>0.47680047150071</v>
       </c>
-      <c r="CM27" s="10" t="n"/>
-      <c r="CN27" s="12" t="n">
+      <c r="CV27" s="10" t="n"/>
+      <c r="CW27" s="12" t="n">
         <v>1.29820904827584e-11</v>
       </c>
-      <c r="CO27" s="11" t="n">
+      <c r="CX27" s="11" t="n">
         <v>0.306216610417165</v>
       </c>
-      <c r="CP27" s="12" t="n">
+      <c r="CY27" s="12" t="n">
         <v>0.245848928862128</v>
       </c>
-      <c r="CQ27" s="12" t="n">
+      <c r="CZ27" s="12" t="n">
         <v>0.291959261297603</v>
       </c>
-      <c r="CR27" s="11" t="n">
+      <c r="DA27" s="11" t="n">
         <v>1.19639719691927</v>
       </c>
-      <c r="CS27" s="12" t="n">
+      <c r="DB27" s="12" t="n">
         <v>5.94894257428176e-05</v>
       </c>
-      <c r="CT27" s="12" t="n">
+      <c r="DC27" s="12" t="n">
         <v>0.000162699038229</v>
       </c>
-      <c r="CU27" s="10" t="b">
+      <c r="DD27" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV27" s="10" t="inlineStr">
+      <c r="DE27" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW27" s="10" t="b">
+      <c r="DF27" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8363,55 +9011,76 @@
         <v>0.1253817917542046</v>
       </c>
       <c r="CF28" s="11" t="n">
+        <v>-3.94943962082638</v>
+      </c>
+      <c r="CG28" s="12" t="n">
+        <v>0.0004886828367025</v>
+      </c>
+      <c r="CH28" s="12" t="n">
+        <v>0.0031715103938252</v>
+      </c>
+      <c r="CI28" s="11" t="n">
+        <v>-4.25910213294597</v>
+      </c>
+      <c r="CJ28" s="12" t="n">
+        <v>3.0169284166701e-15</v>
+      </c>
+      <c r="CK28" s="12" t="n">
+        <v>2.13243935574492e-13</v>
+      </c>
+      <c r="CL28" s="10" t="n"/>
+      <c r="CM28" s="10" t="n"/>
+      <c r="CN28" s="10" t="n"/>
+      <c r="CO28" s="11" t="n">
         <v>1.86614372016981</v>
       </c>
-      <c r="CG28" s="12" t="n">
+      <c r="CP28" s="12" t="n">
         <v>2.35138149658914e-12</v>
       </c>
-      <c r="CH28" s="12" t="n">
+      <c r="CQ28" s="12" t="n">
         <v>7.043156725764669e-12</v>
       </c>
-      <c r="CI28" s="11" t="n">
+      <c r="CR28" s="11" t="n">
         <v>1.5877270721957</v>
       </c>
-      <c r="CJ28" s="10" t="n"/>
-      <c r="CK28" s="12" t="n">
+      <c r="CS28" s="10" t="n"/>
+      <c r="CT28" s="12" t="n">
         <v>2.52111838606823e-06</v>
       </c>
-      <c r="CL28" s="11" t="n">
+      <c r="CU28" s="11" t="n">
         <v>2.44730481665509</v>
       </c>
-      <c r="CM28" s="10" t="n"/>
-      <c r="CN28" s="12" t="n">
+      <c r="CV28" s="10" t="n"/>
+      <c r="CW28" s="12" t="n">
         <v>1.66570347973818e-90</v>
       </c>
-      <c r="CO28" s="11" t="n">
+      <c r="CX28" s="11" t="n">
         <v>2.79300302421463</v>
       </c>
-      <c r="CP28" s="12" t="n">
+      <c r="CY28" s="12" t="n">
         <v>3.00157626785448e-10</v>
       </c>
-      <c r="CQ28" s="12" t="n">
+      <c r="CZ28" s="12" t="n">
         <v>1.23803437643529e-09</v>
       </c>
-      <c r="CR28" s="11" t="n">
+      <c r="DA28" s="11" t="n">
         <v>3.02209759317698</v>
       </c>
-      <c r="CS28" s="12" t="n">
+      <c r="DB28" s="12" t="n">
         <v>3.94351021309102e-11</v>
       </c>
-      <c r="CT28" s="12" t="n">
+      <c r="DC28" s="12" t="n">
         <v>3.49501823523855e-10</v>
       </c>
-      <c r="CU28" s="10" t="b">
+      <c r="DD28" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV28" s="10" t="inlineStr">
+      <c r="DE28" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW28" s="10" t="b">
+      <c r="DF28" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8658,55 +9327,82 @@
         <v>0.0856264488703655</v>
       </c>
       <c r="CF29" s="11" t="n">
+        <v>2.15940415604181</v>
+      </c>
+      <c r="CG29" s="12" t="n">
+        <v>0.0233123675942263</v>
+      </c>
+      <c r="CH29" s="12" t="n">
+        <v>0.0553133505406378</v>
+      </c>
+      <c r="CI29" s="11" t="n">
+        <v>3.83214790364178</v>
+      </c>
+      <c r="CJ29" s="12" t="n">
+        <v>1.42362661299867e-05</v>
+      </c>
+      <c r="CK29" s="12" t="n">
+        <v>5.53059841267574e-05</v>
+      </c>
+      <c r="CL29" s="11" t="n">
+        <v>1.6490164307099</v>
+      </c>
+      <c r="CM29" s="12" t="n">
+        <v>0.0304629351500527</v>
+      </c>
+      <c r="CN29" s="12" t="n">
+        <v>0.107791361353875</v>
+      </c>
+      <c r="CO29" s="11" t="n">
         <v>3.09412145953728</v>
       </c>
-      <c r="CG29" s="12" t="n">
+      <c r="CP29" s="12" t="n">
         <v>1.13067327573803e-14</v>
       </c>
-      <c r="CH29" s="12" t="n">
+      <c r="CQ29" s="12" t="n">
         <v>4.06154837206612e-14</v>
       </c>
-      <c r="CI29" s="11" t="n">
+      <c r="CR29" s="11" t="n">
         <v>1.84488141293706</v>
       </c>
-      <c r="CJ29" s="10" t="n"/>
-      <c r="CK29" s="12" t="n">
+      <c r="CS29" s="10" t="n"/>
+      <c r="CT29" s="12" t="n">
         <v>3.94250145793433e-05</v>
       </c>
-      <c r="CL29" s="11" t="n">
+      <c r="CU29" s="11" t="n">
         <v>4.30167686903167</v>
       </c>
-      <c r="CM29" s="10" t="n"/>
-      <c r="CN29" s="12" t="n">
+      <c r="CV29" s="10" t="n"/>
+      <c r="CW29" s="12" t="n">
         <v>4.35337184170717e-125</v>
       </c>
-      <c r="CO29" s="11" t="n">
+      <c r="CX29" s="11" t="n">
         <v>1.07357998097036</v>
       </c>
-      <c r="CP29" s="12" t="n">
+      <c r="CY29" s="12" t="n">
         <v>0.0078012924588847</v>
       </c>
-      <c r="CQ29" s="12" t="n">
+      <c r="CZ29" s="12" t="n">
         <v>0.0120441006382782</v>
       </c>
-      <c r="CR29" s="11" t="n">
+      <c r="DA29" s="11" t="n">
         <v>3.77985191517593</v>
       </c>
-      <c r="CS29" s="12" t="n">
+      <c r="DB29" s="12" t="n">
         <v>5.517907573401879e-13</v>
       </c>
-      <c r="CT29" s="12" t="n">
+      <c r="DC29" s="12" t="n">
         <v>7.060458342359139e-12</v>
       </c>
-      <c r="CU29" s="10" t="b">
+      <c r="DD29" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV29" s="10" t="inlineStr">
+      <c r="DE29" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW29" s="10" t="b">
+      <c r="DF29" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8832,12 +9528,21 @@
       <c r="CS30" s="10" t="n"/>
       <c r="CT30" s="10" t="n"/>
       <c r="CU30" s="10" t="n"/>
-      <c r="CV30" s="10" t="inlineStr">
+      <c r="CV30" s="10" t="n"/>
+      <c r="CW30" s="10" t="n"/>
+      <c r="CX30" s="10" t="n"/>
+      <c r="CY30" s="10" t="n"/>
+      <c r="CZ30" s="10" t="n"/>
+      <c r="DA30" s="10" t="n"/>
+      <c r="DB30" s="10" t="n"/>
+      <c r="DC30" s="10" t="n"/>
+      <c r="DD30" s="10" t="n"/>
+      <c r="DE30" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW30" s="10" t="n"/>
+      <c r="DF30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -9088,55 +9793,82 @@
         <v>0.0193543831710204</v>
       </c>
       <c r="CF31" s="11" t="n">
+        <v>-1.40586623064409</v>
+      </c>
+      <c r="CG31" s="12" t="n">
+        <v>0.0359842986672939</v>
+      </c>
+      <c r="CH31" s="12" t="n">
+        <v>0.07722568803712319</v>
+      </c>
+      <c r="CI31" s="11" t="n">
+        <v>0.168028315316068</v>
+      </c>
+      <c r="CJ31" s="12" t="n">
+        <v>0.805738855562671</v>
+      </c>
+      <c r="CK31" s="12" t="n">
+        <v>0.845776273357381</v>
+      </c>
+      <c r="CL31" s="11" t="n">
+        <v>1.57147420681761</v>
+      </c>
+      <c r="CM31" s="12" t="n">
+        <v>0.132522286751124</v>
+      </c>
+      <c r="CN31" s="12" t="n">
+        <v>0.289813112260064</v>
+      </c>
+      <c r="CO31" s="11" t="n">
         <v>-1.74925086901342</v>
       </c>
-      <c r="CG31" s="12" t="n">
+      <c r="CP31" s="12" t="n">
         <v>6.36003999521039e-38</v>
       </c>
-      <c r="CH31" s="12" t="n">
+      <c r="CQ31" s="12" t="n">
         <v>9.431049843581169e-37</v>
       </c>
-      <c r="CI31" s="11" t="n">
+      <c r="CR31" s="11" t="n">
         <v>-1.88846389833827</v>
       </c>
-      <c r="CJ31" s="10" t="n"/>
-      <c r="CK31" s="12" t="n">
+      <c r="CS31" s="10" t="n"/>
+      <c r="CT31" s="12" t="n">
         <v>2.95314931935462e-13</v>
       </c>
-      <c r="CL31" s="11" t="n">
+      <c r="CU31" s="11" t="n">
         <v>-0.6410066519484749</v>
       </c>
-      <c r="CM31" s="10" t="n"/>
-      <c r="CN31" s="12" t="n">
+      <c r="CV31" s="10" t="n"/>
+      <c r="CW31" s="12" t="n">
         <v>7.929595445820981e-23</v>
       </c>
-      <c r="CO31" s="11" t="n">
+      <c r="CX31" s="11" t="n">
         <v>-2.35874899425477</v>
       </c>
-      <c r="CP31" s="12" t="n">
+      <c r="CY31" s="12" t="n">
         <v>2.72833850957663e-16</v>
       </c>
-      <c r="CQ31" s="12" t="n">
+      <c r="CZ31" s="12" t="n">
         <v>2.80978715744486e-15</v>
       </c>
-      <c r="CR31" s="11" t="n">
+      <c r="DA31" s="11" t="n">
         <v>2.91285918504908</v>
       </c>
-      <c r="CS31" s="12" t="n">
+      <c r="DB31" s="12" t="n">
         <v>1.96116945597289e-18</v>
       </c>
-      <c r="CT31" s="12" t="n">
+      <c r="DC31" s="12" t="n">
         <v>7.82883550795194e-17</v>
       </c>
-      <c r="CU31" s="10" t="b">
+      <c r="DD31" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV31" s="10" t="inlineStr">
+      <c r="DE31" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW31" s="10" t="b">
+      <c r="DF31" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9389,55 +10121,82 @@
         <v>0.0198197891012144</v>
       </c>
       <c r="CF32" s="11" t="n">
+        <v>-0.587378359649917</v>
+      </c>
+      <c r="CG32" s="12" t="n">
+        <v>0.338965209051259</v>
+      </c>
+      <c r="CH32" s="12" t="n">
+        <v>0.44417342438836</v>
+      </c>
+      <c r="CI32" s="11" t="n">
+        <v>0.879660525837475</v>
+      </c>
+      <c r="CJ32" s="12" t="n">
+        <v>0.0189602578139942</v>
+      </c>
+      <c r="CK32" s="12" t="n">
+        <v>0.0330961241851486</v>
+      </c>
+      <c r="CL32" s="11" t="n">
+        <v>1.44740771806248</v>
+      </c>
+      <c r="CM32" s="12" t="n">
+        <v>0.0034316862480451</v>
+      </c>
+      <c r="CN32" s="12" t="n">
+        <v>0.0245213213852309</v>
+      </c>
+      <c r="CO32" s="11" t="n">
         <v>0.858694131588708</v>
       </c>
-      <c r="CG32" s="12" t="n">
+      <c r="CP32" s="12" t="n">
         <v>1.2510591854259e-09</v>
       </c>
-      <c r="CH32" s="12" t="n">
+      <c r="CQ32" s="12" t="n">
         <v>3.02692573267152e-09</v>
       </c>
-      <c r="CI32" s="11" t="n">
+      <c r="CR32" s="11" t="n">
         <v>0.792217431423037</v>
       </c>
-      <c r="CJ32" s="10" t="n"/>
-      <c r="CK32" s="12" t="n">
+      <c r="CS32" s="10" t="n"/>
+      <c r="CT32" s="12" t="n">
         <v>8.7223659275522e-06</v>
       </c>
-      <c r="CL32" s="11" t="n">
+      <c r="CU32" s="11" t="n">
         <v>2.82911022583707</v>
       </c>
-      <c r="CM32" s="10" t="n"/>
-      <c r="CN32" s="12" t="n">
+      <c r="CV32" s="10" t="n"/>
+      <c r="CW32" s="12" t="n">
         <v>6.671838293558619e-192</v>
       </c>
-      <c r="CO32" s="11" t="n">
+      <c r="CX32" s="11" t="n">
         <v>0.489424717717857</v>
       </c>
-      <c r="CP32" s="12" t="n">
+      <c r="CY32" s="12" t="n">
         <v>0.0045040967367715</v>
       </c>
-      <c r="CQ32" s="12" t="n">
+      <c r="CZ32" s="12" t="n">
         <v>0.0071971518586055</v>
       </c>
-      <c r="CR32" s="11" t="n">
+      <c r="DA32" s="11" t="n">
         <v>2.2350450017259</v>
       </c>
-      <c r="CS32" s="12" t="n">
+      <c r="DB32" s="12" t="n">
         <v>2.04608210820322e-25</v>
       </c>
-      <c r="CT32" s="12" t="n">
+      <c r="DC32" s="12" t="n">
         <v>3.71169654337473e-23</v>
       </c>
-      <c r="CU32" s="10" t="b">
+      <c r="DD32" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV32" s="10" t="inlineStr">
+      <c r="DE32" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW32" s="10" t="b">
+      <c r="DF32" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9635,54 +10394,63 @@
       <c r="CE33" s="12" t="n">
         <v>0.1077160988108302</v>
       </c>
-      <c r="CF33" s="11" t="n">
+      <c r="CF33" s="10" t="n"/>
+      <c r="CG33" s="10" t="n"/>
+      <c r="CH33" s="10" t="n"/>
+      <c r="CI33" s="10" t="n"/>
+      <c r="CJ33" s="10" t="n"/>
+      <c r="CK33" s="10" t="n"/>
+      <c r="CL33" s="10" t="n"/>
+      <c r="CM33" s="10" t="n"/>
+      <c r="CN33" s="10" t="n"/>
+      <c r="CO33" s="11" t="n">
         <v>7.50348409592738</v>
       </c>
-      <c r="CG33" s="12" t="n">
+      <c r="CP33" s="12" t="n">
         <v>2.07979190648398e-41</v>
       </c>
-      <c r="CH33" s="12" t="n">
+      <c r="CQ33" s="12" t="n">
         <v>3.60531351754604e-40</v>
       </c>
-      <c r="CI33" s="11" t="n">
+      <c r="CR33" s="11" t="n">
         <v>6.2725821018296</v>
       </c>
-      <c r="CJ33" s="10" t="n"/>
-      <c r="CK33" s="12" t="n">
+      <c r="CS33" s="10" t="n"/>
+      <c r="CT33" s="12" t="n">
         <v>1.16929054210059e-23</v>
       </c>
-      <c r="CL33" s="11" t="n">
+      <c r="CU33" s="11" t="n">
         <v>8.87923777216338</v>
       </c>
-      <c r="CM33" s="10" t="n"/>
-      <c r="CN33" s="12" t="n">
+      <c r="CV33" s="10" t="n"/>
+      <c r="CW33" s="12" t="n">
         <v>3.019877447075451e-319</v>
       </c>
-      <c r="CO33" s="11" t="n">
+      <c r="CX33" s="11" t="n">
         <v>12.3327491631417</v>
       </c>
-      <c r="CP33" s="12" t="n">
+      <c r="CY33" s="12" t="n">
         <v>3.986399857367541e-15</v>
       </c>
-      <c r="CQ33" s="12" t="n">
+      <c r="CZ33" s="12" t="n">
         <v>3.34003034799734e-14</v>
       </c>
-      <c r="CR33" s="11" t="n">
+      <c r="DA33" s="11" t="n">
         <v>11.8477425359168</v>
       </c>
-      <c r="CS33" s="12" t="n">
+      <c r="DB33" s="12" t="n">
         <v>6.19578584296296e-13</v>
       </c>
-      <c r="CT33" s="12" t="n">
+      <c r="DC33" s="12" t="n">
         <v>7.843799197482519e-12</v>
       </c>
-      <c r="CU33" s="10" t="n"/>
-      <c r="CV33" s="10" t="inlineStr">
+      <c r="DD33" s="10" t="n"/>
+      <c r="DE33" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW33" s="10" t="b">
+      <c r="DF33" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9887,41 +10655,62 @@
         <v>0.06389984309436531</v>
       </c>
       <c r="CF34" s="11" t="n">
+        <v>11.2900673225898</v>
+      </c>
+      <c r="CG34" s="12" t="n">
+        <v>8.868676865150829e-06</v>
+      </c>
+      <c r="CH34" s="12" t="n">
+        <v>0.0002692244308052</v>
+      </c>
+      <c r="CI34" s="10" t="n"/>
+      <c r="CJ34" s="10" t="n"/>
+      <c r="CK34" s="10" t="n"/>
+      <c r="CL34" s="11" t="n">
+        <v>-4.35932922379989</v>
+      </c>
+      <c r="CM34" s="12" t="n">
+        <v>2.12221858894844e-10</v>
+      </c>
+      <c r="CN34" s="12" t="n">
+        <v>4.88342393116307e-08</v>
+      </c>
+      <c r="CO34" s="11" t="n">
         <v>-1.27178811089417</v>
       </c>
-      <c r="CG34" s="12" t="n">
+      <c r="CP34" s="12" t="n">
         <v>3.47533264264383e-08</v>
       </c>
-      <c r="CH34" s="12" t="n">
+      <c r="CQ34" s="12" t="n">
         <v>7.454995577511909e-08</v>
       </c>
-      <c r="CI34" s="11" t="n">
+      <c r="CR34" s="11" t="n">
         <v>-1.9394683901759</v>
       </c>
-      <c r="CJ34" s="10" t="n"/>
-      <c r="CK34" s="12" t="n">
+      <c r="CS34" s="10" t="n"/>
+      <c r="CT34" s="12" t="n">
         <v>3.93681519092414e-09</v>
       </c>
-      <c r="CL34" s="11" t="n">
+      <c r="CU34" s="11" t="n">
         <v>-2.33466929424159</v>
       </c>
-      <c r="CM34" s="10" t="n"/>
-      <c r="CN34" s="12" t="n">
+      <c r="CV34" s="10" t="n"/>
+      <c r="CW34" s="12" t="n">
         <v>2.04373879451104e-93</v>
       </c>
-      <c r="CO34" s="10" t="n"/>
-      <c r="CP34" s="10" t="n"/>
-      <c r="CQ34" s="10" t="n"/>
-      <c r="CR34" s="10" t="n"/>
-      <c r="CS34" s="10" t="n"/>
-      <c r="CT34" s="10" t="n"/>
-      <c r="CU34" s="10" t="n"/>
-      <c r="CV34" s="10" t="inlineStr">
+      <c r="CX34" s="10" t="n"/>
+      <c r="CY34" s="10" t="n"/>
+      <c r="CZ34" s="10" t="n"/>
+      <c r="DA34" s="10" t="n"/>
+      <c r="DB34" s="10" t="n"/>
+      <c r="DC34" s="10" t="n"/>
+      <c r="DD34" s="10" t="n"/>
+      <c r="DE34" s="10" t="inlineStr">
         <is>
           <t>HGCA_not_tested</t>
         </is>
       </c>
-      <c r="CW34" s="10" t="b">
+      <c r="DF34" s="10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10168,60 +10957,87 @@
         <v>0.172164291561855</v>
       </c>
       <c r="CF35" s="11" t="n">
+        <v>0.351373229940042</v>
+      </c>
+      <c r="CG35" s="12" t="n">
+        <v>0.385393896880533</v>
+      </c>
+      <c r="CH35" s="12" t="n">
+        <v>0.491086556770947</v>
+      </c>
+      <c r="CI35" s="11" t="n">
+        <v>-0.297043596933865</v>
+      </c>
+      <c r="CJ35" s="12" t="n">
+        <v>0.290266895723539</v>
+      </c>
+      <c r="CK35" s="12" t="n">
+        <v>0.360693258025401</v>
+      </c>
+      <c r="CL35" s="11" t="n">
+        <v>-0.659777064267156</v>
+      </c>
+      <c r="CM35" s="12" t="n">
+        <v>0.0713455146809282</v>
+      </c>
+      <c r="CN35" s="12" t="n">
+        <v>0.19303791929194</v>
+      </c>
+      <c r="CO35" s="11" t="n">
         <v>0.634213019981918</v>
       </c>
-      <c r="CG35" s="12" t="n">
+      <c r="CP35" s="12" t="n">
         <v>1.60323395018238e-07</v>
       </c>
-      <c r="CH35" s="12" t="n">
+      <c r="CQ35" s="12" t="n">
         <v>3.25470455128078e-07</v>
       </c>
-      <c r="CI35" s="11" t="n">
+      <c r="CR35" s="11" t="n">
         <v>0.6112254293068889</v>
       </c>
-      <c r="CJ35" s="10" t="n"/>
-      <c r="CK35" s="12" t="n">
+      <c r="CS35" s="10" t="n"/>
+      <c r="CT35" s="12" t="n">
         <v>0.000321774337265</v>
       </c>
-      <c r="CL35" s="11" t="n">
+      <c r="CU35" s="11" t="n">
         <v>1.3898930738796</v>
       </c>
-      <c r="CM35" s="10" t="n"/>
-      <c r="CN35" s="12" t="n">
+      <c r="CV35" s="10" t="n"/>
+      <c r="CW35" s="12" t="n">
         <v>4.01779084547098e-66</v>
       </c>
-      <c r="CO35" s="11" t="n">
+      <c r="CX35" s="11" t="n">
         <v>-0.236428784750778</v>
       </c>
-      <c r="CP35" s="12" t="n">
+      <c r="CY35" s="12" t="n">
         <v>0.184853802115731</v>
       </c>
-      <c r="CQ35" s="12" t="n">
+      <c r="CZ35" s="12" t="n">
         <v>0.225201979266582</v>
       </c>
-      <c r="CR35" s="11" t="n">
+      <c r="DA35" s="11" t="n">
         <v>1.47555776466522</v>
       </c>
-      <c r="CS35" s="12" t="n">
+      <c r="DB35" s="12" t="n">
         <v>2.71003026009481e-14</v>
       </c>
-      <c r="CT35" s="12" t="n">
+      <c r="DC35" s="12" t="n">
         <v>4.41418137350751e-13</v>
       </c>
-      <c r="CU35" s="10" t="b">
+      <c r="DD35" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="CV35" s="10" t="inlineStr">
+      <c r="DE35" s="10" t="inlineStr">
         <is>
           <t>HGCA_primary</t>
         </is>
       </c>
-      <c r="CW35" s="10" t="b">
+      <c r="DF35" s="10" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="101">
+  <mergeCells count="110">
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="A1:A4"/>
@@ -10236,13 +11052,16 @@
     <mergeCell ref="CL3:CN3"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="DE1:DE4"/>
     <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CX3:CZ3"/>
     <mergeCell ref="CO1:CQ1"/>
     <mergeCell ref="D1:D4"/>
     <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="AP1:AR1"/>
     <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CU2:CW2"/>
     <mergeCell ref="AM1:AO1"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="L1:N1"/>
@@ -10251,6 +11070,8 @@
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="DA2:DC2"/>
     <mergeCell ref="BH1:BJ1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="BZ1:CB1"/>
@@ -10267,6 +11088,7 @@
     <mergeCell ref="CL2:CN2"/>
     <mergeCell ref="AS1:AU1"/>
     <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CU1:CW1"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="BH3:BJ3"/>
@@ -10274,9 +11096,8 @@
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="CU1:CU4"/>
     <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="CW1:CW4"/>
+    <mergeCell ref="DA1:DC1"/>
     <mergeCell ref="CI2:CK2"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="AS2:AU2"/>
@@ -10294,7 +11115,9 @@
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="BK2:BM2"/>
     <mergeCell ref="CC3:CE3"/>
-    <mergeCell ref="CV1:CV4"/>
+    <mergeCell ref="DD1:DD4"/>
+    <mergeCell ref="CU3:CW3"/>
+    <mergeCell ref="DF1:DF4"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="BT1:BV1"/>
@@ -10302,11 +11125,13 @@
     <mergeCell ref="CO2:CQ2"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="DA3:DC3"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="BZ2:CB2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="AV2:AX2"/>
     <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="CX2:CZ2"/>
     <mergeCell ref="BE1:BG1"/>
     <mergeCell ref="BH2:BJ2"/>
     <mergeCell ref="CR2:CT2"/>
@@ -10684,6 +11509,42 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="CU5:CU35">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="num" val="-3"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="002166AC"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00B2182B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CX5:CX35">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="num" val="-3"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="002166AC"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00B2182B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DA5:DA35">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="num" val="-3"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="002166AC"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00B2182B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10694,7 +11555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE32"/>
+  <dimension ref="A1:AH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10728,6 +11589,9 @@
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -10863,25 +11727,40 @@
       </c>
       <c r="AA1" s="13" t="inlineStr">
         <is>
+          <t>S2 (benchmark v2, stage v1.2) | Fawkner early fetal (&lt;9 PCW) vs Burclaff adult [stage-resolved]</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>S2 (benchmark v2, stage v1.2) | Fawkner mid/late fetal (&gt;=9 PCW) vs Burclaff adult [stage-resolved]</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>S2 (benchmark v2, stage v1.2) | Fawkner mid/late vs early fetal [within-fetal]</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
           <t>S3 | TCGA COAD+READ (T1)</t>
         </is>
       </c>
-      <c r="AB1" s="13" t="inlineStr">
+      <c r="AE1" s="13" t="inlineStr">
         <is>
           <t>S3 | TCGA paired</t>
         </is>
       </c>
-      <c r="AC1" s="13" t="inlineStr">
+      <c r="AF1" s="13" t="inlineStr">
         <is>
           <t>S3 | TCGA vs GTEx</t>
         </is>
       </c>
-      <c r="AD1" s="13" t="inlineStr">
+      <c r="AG1" s="13" t="inlineStr">
         <is>
           <t>S3 | Pelka 2021 (S2, GSE178341)</t>
         </is>
       </c>
-      <c r="AE1" s="13" t="inlineStr">
+      <c r="AH1" s="13" t="inlineStr">
         <is>
           <t>S3 | Pelka progenitor check (P)</t>
         </is>
@@ -10965,18 +11844,27 @@
         <v>1.804563890763444</v>
       </c>
       <c r="AA2" s="11" t="n">
+        <v>2.99456069495154</v>
+      </c>
+      <c r="AB2" s="11" t="n">
+        <v>4.08526804610829</v>
+      </c>
+      <c r="AC2" s="11" t="n">
+        <v>1.10237856445083</v>
+      </c>
+      <c r="AD2" s="11" t="n">
         <v>5.05028632487126</v>
       </c>
-      <c r="AB2" s="11" t="n">
+      <c r="AE2" s="11" t="n">
         <v>3.73497284492898</v>
       </c>
-      <c r="AC2" s="11" t="n">
+      <c r="AF2" s="11" t="n">
         <v>4.69300181571387</v>
       </c>
-      <c r="AD2" s="11" t="n">
+      <c r="AG2" s="11" t="n">
         <v>4.25904379124654</v>
       </c>
-      <c r="AE2" s="11" t="n">
+      <c r="AH2" s="11" t="n">
         <v>6.05919277196155</v>
       </c>
     </row>
@@ -11062,16 +11950,25 @@
         <v>-1.401751707140695</v>
       </c>
       <c r="AA3" s="11" t="n">
+        <v>4.00610785770629</v>
+      </c>
+      <c r="AB3" s="11" t="n">
+        <v>2.77075537774903</v>
+      </c>
+      <c r="AC3" s="11" t="n">
+        <v>-1.22630141228582</v>
+      </c>
+      <c r="AD3" s="11" t="n">
         <v>-0.0025247870000847</v>
       </c>
-      <c r="AB3" s="11" t="n">
+      <c r="AE3" s="11" t="n">
         <v>-0.222650205328684</v>
       </c>
-      <c r="AC3" s="11" t="n">
+      <c r="AF3" s="11" t="n">
         <v>-0.433294511714691</v>
       </c>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -11155,18 +12052,27 @@
         <v>1.334898020444873</v>
       </c>
       <c r="AA4" s="11" t="n">
+        <v>-0.837069630855066</v>
+      </c>
+      <c r="AB4" s="11" t="n">
+        <v>-0.931228468737944</v>
+      </c>
+      <c r="AC4" s="11" t="n">
+        <v>-0.0761228290537096</v>
+      </c>
+      <c r="AD4" s="11" t="n">
         <v>0.208594387468698</v>
       </c>
-      <c r="AB4" s="11" t="n">
+      <c r="AE4" s="11" t="n">
         <v>-0.246222685380311</v>
       </c>
-      <c r="AC4" s="11" t="n">
+      <c r="AF4" s="11" t="n">
         <v>-0.643732616070441</v>
       </c>
-      <c r="AD4" s="11" t="n">
+      <c r="AG4" s="11" t="n">
         <v>2.84220968978987</v>
       </c>
-      <c r="AE4" s="11" t="n">
+      <c r="AH4" s="11" t="n">
         <v>4.55185303250578</v>
       </c>
     </row>
@@ -11252,18 +12158,27 @@
         <v>1.739785295522536</v>
       </c>
       <c r="AA5" s="11" t="n">
+        <v>1.47941744357466</v>
+      </c>
+      <c r="AB5" s="11" t="n">
+        <v>2.34510833736241</v>
+      </c>
+      <c r="AC5" s="11" t="n">
+        <v>0.857967972543863</v>
+      </c>
+      <c r="AD5" s="11" t="n">
         <v>-2.31154743014523</v>
       </c>
-      <c r="AB5" s="11" t="n">
+      <c r="AE5" s="11" t="n">
         <v>-2.65163850649463</v>
       </c>
-      <c r="AC5" s="11" t="n">
+      <c r="AF5" s="11" t="n">
         <v>-2.77393099960309</v>
       </c>
-      <c r="AD5" s="11" t="n">
+      <c r="AG5" s="11" t="n">
         <v>1.49510505291086</v>
       </c>
-      <c r="AE5" s="11" t="n">
+      <c r="AH5" s="11" t="n">
         <v>1.48820795285742</v>
       </c>
     </row>
@@ -11349,18 +12264,27 @@
         <v>1.480035233896504</v>
       </c>
       <c r="AA6" s="11" t="n">
+        <v>1.1300415638916</v>
+      </c>
+      <c r="AB6" s="11" t="n">
+        <v>1.76569125688894</v>
+      </c>
+      <c r="AC6" s="11" t="n">
+        <v>0.644209335321822</v>
+      </c>
+      <c r="AD6" s="11" t="n">
         <v>1.67776809443425</v>
       </c>
-      <c r="AB6" s="11" t="n">
+      <c r="AE6" s="11" t="n">
         <v>1.35884211776825</v>
       </c>
-      <c r="AC6" s="11" t="n">
+      <c r="AF6" s="11" t="n">
         <v>1.93451996054779</v>
       </c>
-      <c r="AD6" s="11" t="n">
+      <c r="AG6" s="11" t="n">
         <v>1.65228981386363</v>
       </c>
-      <c r="AE6" s="11" t="n">
+      <c r="AH6" s="11" t="n">
         <v>2.02638428887108</v>
       </c>
     </row>
@@ -11446,18 +12370,27 @@
         <v>-1.624839349796439</v>
       </c>
       <c r="AA7" s="11" t="n">
+        <v>3.88722641396611</v>
+      </c>
+      <c r="AB7" s="11" t="n">
+        <v>2.50419699416761</v>
+      </c>
+      <c r="AC7" s="11" t="n">
+        <v>-1.39527326008543</v>
+      </c>
+      <c r="AD7" s="11" t="n">
         <v>-0.332774350351039</v>
       </c>
-      <c r="AB7" s="11" t="n">
+      <c r="AE7" s="11" t="n">
         <v>-0.287899078091318</v>
       </c>
-      <c r="AC7" s="11" t="n">
+      <c r="AF7" s="11" t="n">
         <v>-0.870991369969248</v>
       </c>
-      <c r="AD7" s="11" t="n">
+      <c r="AG7" s="11" t="n">
         <v>2.95811168926125</v>
       </c>
-      <c r="AE7" s="11" t="n">
+      <c r="AH7" s="11" t="n">
         <v>3.09931636991049</v>
       </c>
     </row>
@@ -11497,6 +12430,9 @@
       <c r="AC8" s="10" t="n"/>
       <c r="AD8" s="10" t="n"/>
       <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="10" t="n"/>
+      <c r="AH8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -11570,18 +12506,25 @@
         <v>0.6091130865759764</v>
       </c>
       <c r="AA9" s="11" t="n">
+        <v>8.033077507693999</v>
+      </c>
+      <c r="AB9" s="10" t="n"/>
+      <c r="AC9" s="11" t="n">
+        <v>0.424416454313631</v>
+      </c>
+      <c r="AD9" s="11" t="n">
         <v>3.87915708772113</v>
       </c>
-      <c r="AB9" s="11" t="n">
+      <c r="AE9" s="11" t="n">
         <v>3.31849537880916</v>
       </c>
-      <c r="AC9" s="11" t="n">
+      <c r="AF9" s="11" t="n">
         <v>2.96080985389408</v>
       </c>
-      <c r="AD9" s="11" t="n">
+      <c r="AG9" s="11" t="n">
         <v>6.12870673194068</v>
       </c>
-      <c r="AE9" s="11" t="n">
+      <c r="AH9" s="11" t="n">
         <v>6.65778199848213</v>
       </c>
     </row>
@@ -11630,13 +12573,16 @@
       <c r="Z10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="AA10" s="11" t="n">
-        <v>7.36478688339062</v>
-      </c>
+      <c r="AA10" s="10" t="n"/>
       <c r="AB10" s="10" t="n"/>
       <c r="AC10" s="10" t="n"/>
-      <c r="AD10" s="10" t="n"/>
+      <c r="AD10" s="11" t="n">
+        <v>7.36478688339062</v>
+      </c>
       <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="10" t="n"/>
+      <c r="AH10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -11715,19 +12661,22 @@
       <c r="Z11" s="11" t="n">
         <v>1.07623279007608</v>
       </c>
-      <c r="AA11" s="11" t="n">
+      <c r="AA11" s="10" t="n"/>
+      <c r="AB11" s="10" t="n"/>
+      <c r="AC11" s="10" t="n"/>
+      <c r="AD11" s="11" t="n">
         <v>0.745426223148137</v>
       </c>
-      <c r="AB11" s="11" t="n">
+      <c r="AE11" s="11" t="n">
         <v>-0.0554276379201352</v>
       </c>
-      <c r="AC11" s="11" t="n">
+      <c r="AF11" s="11" t="n">
         <v>0.654734068205669</v>
       </c>
-      <c r="AD11" s="11" t="n">
+      <c r="AG11" s="11" t="n">
         <v>4.55190891741079</v>
       </c>
-      <c r="AE11" s="11" t="n">
+      <c r="AH11" s="11" t="n">
         <v>4.66154103734362</v>
       </c>
     </row>
@@ -11801,18 +12750,27 @@
       </c>
       <c r="Z12" s="10" t="n"/>
       <c r="AA12" s="11" t="n">
+        <v>-1.37200412504424</v>
+      </c>
+      <c r="AB12" s="11" t="n">
+        <v>-1.07750080237949</v>
+      </c>
+      <c r="AC12" s="11" t="n">
+        <v>0.29990364285937</v>
+      </c>
+      <c r="AD12" s="11" t="n">
         <v>2.02713488622674</v>
       </c>
-      <c r="AB12" s="11" t="n">
+      <c r="AE12" s="11" t="n">
         <v>1.67806283998944</v>
       </c>
-      <c r="AC12" s="11" t="n">
+      <c r="AF12" s="11" t="n">
         <v>2.23031464377784</v>
       </c>
-      <c r="AD12" s="11" t="n">
+      <c r="AG12" s="11" t="n">
         <v>1.34994899681148</v>
       </c>
-      <c r="AE12" s="11" t="n">
+      <c r="AH12" s="11" t="n">
         <v>0.819685047138303</v>
       </c>
     </row>
@@ -11898,18 +12856,27 @@
         <v>-1.964680449364078</v>
       </c>
       <c r="AA13" s="11" t="n">
+        <v>6.46064866295748</v>
+      </c>
+      <c r="AB13" s="11" t="n">
+        <v>6.36969425628561</v>
+      </c>
+      <c r="AC13" s="11" t="n">
+        <v>-0.09608787284953101</v>
+      </c>
+      <c r="AD13" s="11" t="n">
         <v>0.221508245845491</v>
       </c>
-      <c r="AB13" s="11" t="n">
+      <c r="AE13" s="11" t="n">
         <v>0.438961218681568</v>
       </c>
-      <c r="AC13" s="11" t="n">
+      <c r="AF13" s="11" t="n">
         <v>-0.963225217532367</v>
       </c>
-      <c r="AD13" s="11" t="n">
+      <c r="AG13" s="11" t="n">
         <v>0.628181546646409</v>
       </c>
-      <c r="AE13" s="11" t="n">
+      <c r="AH13" s="11" t="n">
         <v>2.5517728210184</v>
       </c>
     </row>
@@ -11993,18 +12960,27 @@
         <v>-1.808293981817242</v>
       </c>
       <c r="AA14" s="11" t="n">
+        <v>7.87813890331585</v>
+      </c>
+      <c r="AB14" s="11" t="n">
+        <v>7.35140825550013</v>
+      </c>
+      <c r="AC14" s="11" t="n">
+        <v>-0.523442393383548</v>
+      </c>
+      <c r="AD14" s="11" t="n">
         <v>-0.0713325886046302</v>
       </c>
-      <c r="AB14" s="11" t="n">
+      <c r="AE14" s="11" t="n">
         <v>0.163688982157025</v>
       </c>
-      <c r="AC14" s="11" t="n">
+      <c r="AF14" s="11" t="n">
         <v>-2.00691071894571</v>
       </c>
-      <c r="AD14" s="11" t="n">
+      <c r="AG14" s="11" t="n">
         <v>1.01939227713914</v>
       </c>
-      <c r="AE14" s="11" t="n">
+      <c r="AH14" s="11" t="n">
         <v>2.00247177995832</v>
       </c>
     </row>
@@ -12068,14 +13044,19 @@
         <v>0.0021417758625438</v>
       </c>
       <c r="AA15" s="11" t="n">
+        <v>9.35220034255593</v>
+      </c>
+      <c r="AB15" s="10" t="n"/>
+      <c r="AC15" s="10" t="n"/>
+      <c r="AD15" s="11" t="n">
         <v>2.49237551608169</v>
       </c>
-      <c r="AB15" s="10" t="n"/>
-      <c r="AC15" s="11" t="n">
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="11" t="n">
         <v>-5.1390419411966</v>
       </c>
-      <c r="AD15" s="10" t="n"/>
-      <c r="AE15" s="10" t="n"/>
+      <c r="AG15" s="10" t="n"/>
+      <c r="AH15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -12159,18 +13140,27 @@
         <v>1.87013553279805</v>
       </c>
       <c r="AA16" s="11" t="n">
+        <v>0.862516349577405</v>
+      </c>
+      <c r="AB16" s="11" t="n">
+        <v>1.93596804565604</v>
+      </c>
+      <c r="AC16" s="11" t="n">
+        <v>1.07566609044384</v>
+      </c>
+      <c r="AD16" s="11" t="n">
         <v>2.29482738823638</v>
       </c>
-      <c r="AB16" s="11" t="n">
+      <c r="AE16" s="11" t="n">
         <v>2.52306766993452</v>
       </c>
-      <c r="AC16" s="11" t="n">
+      <c r="AF16" s="11" t="n">
         <v>1.81120060518907</v>
       </c>
-      <c r="AD16" s="11" t="n">
+      <c r="AG16" s="11" t="n">
         <v>2.68701270314905</v>
       </c>
-      <c r="AE16" s="11" t="n">
+      <c r="AH16" s="11" t="n">
         <v>2.78121905025346</v>
       </c>
     </row>
@@ -12229,17 +13219,20 @@
       <c r="Z17" s="11" t="n">
         <v>1.078145771525832</v>
       </c>
-      <c r="AA17" s="11" t="n">
+      <c r="AA17" s="10" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="11" t="n">
         <v>-1.02954992492292</v>
       </c>
-      <c r="AB17" s="11" t="n">
+      <c r="AE17" s="11" t="n">
         <v>-0.931053223313861</v>
       </c>
-      <c r="AC17" s="11" t="n">
+      <c r="AF17" s="11" t="n">
         <v>-2.59671603848386</v>
       </c>
-      <c r="AD17" s="10" t="n"/>
-      <c r="AE17" s="10" t="n"/>
+      <c r="AG17" s="10" t="n"/>
+      <c r="AH17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -12323,18 +13316,27 @@
         <v>-1.591389150616544</v>
       </c>
       <c r="AA18" s="11" t="n">
+        <v>4.60399826957088</v>
+      </c>
+      <c r="AB18" s="11" t="n">
+        <v>1.43478024952675</v>
+      </c>
+      <c r="AC18" s="11" t="n">
+        <v>-3.16833223633969</v>
+      </c>
+      <c r="AD18" s="11" t="n">
         <v>1.57367534695579</v>
       </c>
-      <c r="AB18" s="11" t="n">
+      <c r="AE18" s="11" t="n">
         <v>0.646924522534852</v>
       </c>
-      <c r="AC18" s="11" t="n">
+      <c r="AF18" s="11" t="n">
         <v>1.11067385875638</v>
       </c>
-      <c r="AD18" s="11" t="n">
+      <c r="AG18" s="11" t="n">
         <v>6.30648245228024</v>
       </c>
-      <c r="AE18" s="11" t="n">
+      <c r="AH18" s="11" t="n">
         <v>6.19072201370017</v>
       </c>
     </row>
@@ -12420,18 +13422,27 @@
         <v>1.542686598819681</v>
       </c>
       <c r="AA19" s="11" t="n">
+        <v>2.9650929695661</v>
+      </c>
+      <c r="AB19" s="11" t="n">
+        <v>3.87027366453888</v>
+      </c>
+      <c r="AC19" s="11" t="n">
+        <v>0.900954697441033</v>
+      </c>
+      <c r="AD19" s="11" t="n">
         <v>1.88873842413568</v>
       </c>
-      <c r="AB19" s="11" t="n">
+      <c r="AE19" s="11" t="n">
         <v>1.55366222585167</v>
       </c>
-      <c r="AC19" s="11" t="n">
+      <c r="AF19" s="11" t="n">
         <v>3.31365052381195</v>
       </c>
-      <c r="AD19" s="11" t="n">
+      <c r="AG19" s="11" t="n">
         <v>0.89453255383055</v>
       </c>
-      <c r="AE19" s="11" t="n">
+      <c r="AH19" s="11" t="n">
         <v>3.08813339050379</v>
       </c>
     </row>
@@ -12517,18 +13528,27 @@
         <v>1.548309321751487</v>
       </c>
       <c r="AA20" s="11" t="n">
+        <v>7.41424214877531</v>
+      </c>
+      <c r="AB20" s="11" t="n">
+        <v>7.34274811127424</v>
+      </c>
+      <c r="AC20" s="11" t="n">
+        <v>-0.0628151581920966</v>
+      </c>
+      <c r="AD20" s="11" t="n">
         <v>2.9979635592165</v>
       </c>
-      <c r="AB20" s="11" t="n">
+      <c r="AE20" s="11" t="n">
         <v>1.76009229587045</v>
       </c>
-      <c r="AC20" s="11" t="n">
+      <c r="AF20" s="11" t="n">
         <v>4.21890908178643</v>
       </c>
-      <c r="AD20" s="11" t="n">
+      <c r="AG20" s="11" t="n">
         <v>1.51085977279679</v>
       </c>
-      <c r="AE20" s="11" t="n">
+      <c r="AH20" s="11" t="n">
         <v>3.74403292270937</v>
       </c>
     </row>
@@ -12614,18 +13634,27 @@
         <v>0.3915979624236544</v>
       </c>
       <c r="AA21" s="11" t="n">
+        <v>-4.04071578384915</v>
+      </c>
+      <c r="AB21" s="11" t="n">
+        <v>-3.92423482458367</v>
+      </c>
+      <c r="AC21" s="11" t="n">
+        <v>0.0874234303878506</v>
+      </c>
+      <c r="AD21" s="11" t="n">
         <v>1.36639206277824</v>
       </c>
-      <c r="AB21" s="11" t="n">
+      <c r="AE21" s="11" t="n">
         <v>1.26799737584483</v>
       </c>
-      <c r="AC21" s="11" t="n">
+      <c r="AF21" s="11" t="n">
         <v>1.14584323905699</v>
       </c>
-      <c r="AD21" s="11" t="n">
+      <c r="AG21" s="11" t="n">
         <v>2.10989447178502</v>
       </c>
-      <c r="AE21" s="11" t="n">
+      <c r="AH21" s="11" t="n">
         <v>1.38530001359927</v>
       </c>
     </row>
@@ -12705,18 +13734,27 @@
         <v>1.760036589186307</v>
       </c>
       <c r="AA22" s="11" t="n">
+        <v>-0.495920417345305</v>
+      </c>
+      <c r="AB22" s="11" t="n">
+        <v>-0.243976421699182</v>
+      </c>
+      <c r="AC22" s="11" t="n">
+        <v>0.25144092000959</v>
+      </c>
+      <c r="AD22" s="11" t="n">
         <v>0.159515216698385</v>
       </c>
-      <c r="AB22" s="11" t="n">
+      <c r="AE22" s="11" t="n">
         <v>-0.153171304696138</v>
       </c>
-      <c r="AC22" s="11" t="n">
+      <c r="AF22" s="11" t="n">
         <v>1.74866833860967</v>
       </c>
-      <c r="AD22" s="11" t="n">
+      <c r="AG22" s="11" t="n">
         <v>-0.200608496306742</v>
       </c>
-      <c r="AE22" s="11" t="n">
+      <c r="AH22" s="11" t="n">
         <v>0.633311174348519</v>
       </c>
     </row>
@@ -12800,18 +13838,27 @@
         <v>-2.023473010652002</v>
       </c>
       <c r="AA23" s="11" t="n">
+        <v>5.06396739023882</v>
+      </c>
+      <c r="AB23" s="11" t="n">
+        <v>3.31231450153575</v>
+      </c>
+      <c r="AC23" s="11" t="n">
+        <v>-1.75462609408379</v>
+      </c>
+      <c r="AD23" s="11" t="n">
         <v>-0.455321176539081</v>
       </c>
-      <c r="AB23" s="11" t="n">
+      <c r="AE23" s="11" t="n">
         <v>-0.729541570166073</v>
       </c>
-      <c r="AC23" s="11" t="n">
+      <c r="AF23" s="11" t="n">
         <v>-0.447888686877304</v>
       </c>
-      <c r="AD23" s="11" t="n">
+      <c r="AG23" s="11" t="n">
         <v>-1.80161423745876</v>
       </c>
-      <c r="AE23" s="11" t="n">
+      <c r="AH23" s="11" t="n">
         <v>-2.212691629844</v>
       </c>
     </row>
@@ -12897,18 +13944,27 @@
         <v>0.7787538287923085</v>
       </c>
       <c r="AA24" s="11" t="n">
+        <v>4.72812504310472</v>
+      </c>
+      <c r="AB24" s="11" t="n">
+        <v>5.80090056105349</v>
+      </c>
+      <c r="AC24" s="11" t="n">
+        <v>1.07591969354045</v>
+      </c>
+      <c r="AD24" s="11" t="n">
         <v>0.128296775049852</v>
       </c>
-      <c r="AB24" s="11" t="n">
+      <c r="AE24" s="11" t="n">
         <v>-0.6703771259474079</v>
       </c>
-      <c r="AC24" s="11" t="n">
+      <c r="AF24" s="11" t="n">
         <v>0.47680047150071</v>
       </c>
-      <c r="AD24" s="11" t="n">
+      <c r="AG24" s="11" t="n">
         <v>0.306216610417165</v>
       </c>
-      <c r="AE24" s="11" t="n">
+      <c r="AH24" s="11" t="n">
         <v>1.19639719691927</v>
       </c>
     </row>
@@ -12990,18 +14046,25 @@
         <v>1.418365065382192</v>
       </c>
       <c r="AA25" s="11" t="n">
+        <v>-3.94943962082638</v>
+      </c>
+      <c r="AB25" s="11" t="n">
+        <v>-4.25910213294597</v>
+      </c>
+      <c r="AC25" s="10" t="n"/>
+      <c r="AD25" s="11" t="n">
         <v>1.86614372016981</v>
       </c>
-      <c r="AB25" s="11" t="n">
+      <c r="AE25" s="11" t="n">
         <v>1.5877270721957</v>
       </c>
-      <c r="AC25" s="11" t="n">
+      <c r="AF25" s="11" t="n">
         <v>2.44730481665509</v>
       </c>
-      <c r="AD25" s="11" t="n">
+      <c r="AG25" s="11" t="n">
         <v>2.79300302421463</v>
       </c>
-      <c r="AE25" s="11" t="n">
+      <c r="AH25" s="11" t="n">
         <v>3.02209759317698</v>
       </c>
     </row>
@@ -13085,18 +14148,27 @@
         <v>3.712488055470509</v>
       </c>
       <c r="AA26" s="11" t="n">
+        <v>2.15940415604181</v>
+      </c>
+      <c r="AB26" s="11" t="n">
+        <v>3.83214790364178</v>
+      </c>
+      <c r="AC26" s="11" t="n">
+        <v>1.6490164307099</v>
+      </c>
+      <c r="AD26" s="11" t="n">
         <v>3.09412145953728</v>
       </c>
-      <c r="AB26" s="11" t="n">
+      <c r="AE26" s="11" t="n">
         <v>1.84488141293706</v>
       </c>
-      <c r="AC26" s="11" t="n">
+      <c r="AF26" s="11" t="n">
         <v>4.30167686903167</v>
       </c>
-      <c r="AD26" s="11" t="n">
+      <c r="AG26" s="11" t="n">
         <v>1.07357998097036</v>
       </c>
-      <c r="AE26" s="11" t="n">
+      <c r="AH26" s="11" t="n">
         <v>3.77985191517593</v>
       </c>
     </row>
@@ -13138,6 +14210,9 @@
       <c r="AC27" s="10" t="n"/>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="10" t="n"/>
+      <c r="AF27" s="10" t="n"/>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -13221,18 +14296,27 @@
         <v>2.416098901896552</v>
       </c>
       <c r="AA28" s="11" t="n">
+        <v>-1.40586623064409</v>
+      </c>
+      <c r="AB28" s="11" t="n">
+        <v>0.168028315316068</v>
+      </c>
+      <c r="AC28" s="11" t="n">
+        <v>1.57147420681761</v>
+      </c>
+      <c r="AD28" s="11" t="n">
         <v>-1.74925086901342</v>
       </c>
-      <c r="AB28" s="11" t="n">
+      <c r="AE28" s="11" t="n">
         <v>-1.88846389833827</v>
       </c>
-      <c r="AC28" s="11" t="n">
+      <c r="AF28" s="11" t="n">
         <v>-0.6410066519484749</v>
       </c>
-      <c r="AD28" s="11" t="n">
+      <c r="AG28" s="11" t="n">
         <v>-2.35874899425477</v>
       </c>
-      <c r="AE28" s="11" t="n">
+      <c r="AH28" s="11" t="n">
         <v>2.91285918504908</v>
       </c>
     </row>
@@ -13318,18 +14402,27 @@
         <v>2.39343351109546</v>
       </c>
       <c r="AA29" s="11" t="n">
+        <v>-0.587378359649917</v>
+      </c>
+      <c r="AB29" s="11" t="n">
+        <v>0.879660525837475</v>
+      </c>
+      <c r="AC29" s="11" t="n">
+        <v>1.44740771806248</v>
+      </c>
+      <c r="AD29" s="11" t="n">
         <v>0.858694131588708</v>
       </c>
-      <c r="AB29" s="11" t="n">
+      <c r="AE29" s="11" t="n">
         <v>0.792217431423037</v>
       </c>
-      <c r="AC29" s="11" t="n">
+      <c r="AF29" s="11" t="n">
         <v>2.82911022583707</v>
       </c>
-      <c r="AD29" s="11" t="n">
+      <c r="AG29" s="11" t="n">
         <v>0.489424717717857</v>
       </c>
-      <c r="AE29" s="11" t="n">
+      <c r="AH29" s="11" t="n">
         <v>2.2350450017259</v>
       </c>
     </row>
@@ -13396,19 +14489,22 @@
       <c r="Z30" s="11" t="n">
         <v>0.7152319777182148</v>
       </c>
-      <c r="AA30" s="11" t="n">
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="10" t="n"/>
+      <c r="AC30" s="10" t="n"/>
+      <c r="AD30" s="11" t="n">
         <v>7.50348409592738</v>
       </c>
-      <c r="AB30" s="11" t="n">
+      <c r="AE30" s="11" t="n">
         <v>6.2725821018296</v>
       </c>
-      <c r="AC30" s="11" t="n">
+      <c r="AF30" s="11" t="n">
         <v>8.87923777216338</v>
       </c>
-      <c r="AD30" s="11" t="n">
+      <c r="AG30" s="11" t="n">
         <v>12.3327491631417</v>
       </c>
-      <c r="AE30" s="11" t="n">
+      <c r="AH30" s="11" t="n">
         <v>11.8477425359168</v>
       </c>
     </row>
@@ -13478,16 +14574,23 @@
         <v>-1.945972376740518</v>
       </c>
       <c r="AA31" s="11" t="n">
+        <v>11.2900673225898</v>
+      </c>
+      <c r="AB31" s="10" t="n"/>
+      <c r="AC31" s="11" t="n">
+        <v>-4.35932922379989</v>
+      </c>
+      <c r="AD31" s="11" t="n">
         <v>-1.27178811089417</v>
       </c>
-      <c r="AB31" s="11" t="n">
+      <c r="AE31" s="11" t="n">
         <v>-1.9394683901759</v>
       </c>
-      <c r="AC31" s="11" t="n">
+      <c r="AF31" s="11" t="n">
         <v>-2.33466929424159</v>
       </c>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="10" t="n"/>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -13569,23 +14672,32 @@
         <v>1.212853183434121</v>
       </c>
       <c r="AA32" s="11" t="n">
+        <v>0.351373229940042</v>
+      </c>
+      <c r="AB32" s="11" t="n">
+        <v>-0.297043596933865</v>
+      </c>
+      <c r="AC32" s="11" t="n">
+        <v>-0.659777064267156</v>
+      </c>
+      <c r="AD32" s="11" t="n">
         <v>0.634213019981918</v>
       </c>
-      <c r="AB32" s="11" t="n">
+      <c r="AE32" s="11" t="n">
         <v>0.6112254293068889</v>
       </c>
-      <c r="AC32" s="11" t="n">
+      <c r="AF32" s="11" t="n">
         <v>1.3898930738796</v>
       </c>
-      <c r="AD32" s="11" t="n">
+      <c r="AG32" s="11" t="n">
         <v>-0.236428784750778</v>
       </c>
-      <c r="AE32" s="11" t="n">
+      <c r="AH32" s="11" t="n">
         <v>1.47555776466522</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:AE32">
+  <conditionalFormatting sqref="B2:AH32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3"/>
@@ -13607,7 +14719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF32"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13642,6 +14754,9 @@
     <col width="16" customWidth="1" min="30" max="30"/>
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -13782,25 +14897,40 @@
       </c>
       <c r="AB1" s="13" t="inlineStr">
         <is>
+          <t>S2 (benchmark v2, stage v1.2) | Fawkner early fetal (&lt;9 PCW) vs Burclaff adult [stage-resolved]</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>S2 (benchmark v2, stage v1.2) | Fawkner mid/late fetal (&gt;=9 PCW) vs Burclaff adult [stage-resolved]</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
+          <t>S2 (benchmark v2, stage v1.2) | Fawkner mid/late vs early fetal [within-fetal]</t>
+        </is>
+      </c>
+      <c r="AE1" s="13" t="inlineStr">
+        <is>
           <t>S3 | TCGA COAD+READ (T1)</t>
         </is>
       </c>
-      <c r="AC1" s="13" t="inlineStr">
+      <c r="AF1" s="13" t="inlineStr">
         <is>
           <t>S3 | TCGA paired</t>
         </is>
       </c>
-      <c r="AD1" s="13" t="inlineStr">
+      <c r="AG1" s="13" t="inlineStr">
         <is>
           <t>S3 | TCGA vs GTEx</t>
         </is>
       </c>
-      <c r="AE1" s="13" t="inlineStr">
+      <c r="AH1" s="13" t="inlineStr">
         <is>
           <t>S3 | Pelka 2021 (S2, GSE178341)</t>
         </is>
       </c>
-      <c r="AF1" s="13" t="inlineStr">
+      <c r="AI1" s="13" t="inlineStr">
         <is>
           <t>S3 | Pelka progenitor check (P)</t>
         </is>
@@ -13967,6 +15097,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG2" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH2" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI2" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -14119,12 +15264,27 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AE3" s="14" t="inlineStr">
+      <c r="AE3" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG3" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH3" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AF3" s="14" t="inlineStr">
+      <c r="AI3" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -14291,6 +15451,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG4" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH4" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI4" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -14453,6 +15628,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG5" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH5" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI5" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -14615,6 +15805,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG6" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH6" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -14777,6 +15982,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG7" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH7" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI7" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -14939,6 +16159,21 @@
           <t>no human one2one orthologue</t>
         </is>
       </c>
+      <c r="AG8" s="14" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
+      <c r="AH8" s="14" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
+      <c r="AI8" s="14" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -15081,9 +16316,9 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AC9" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="AC9" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="AD9" s="10" t="inlineStr">
@@ -15097,6 +16332,21 @@
         </is>
       </c>
       <c r="AF9" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG9" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH9" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI9" s="10" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -15238,27 +16488,42 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AB10" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="AB10" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="AC10" s="14" t="inlineStr">
         <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AD10" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AE10" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AF10" s="14" t="inlineStr">
+        <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AD10" s="14" t="inlineStr">
+      <c r="AG10" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AE10" s="14" t="inlineStr">
+      <c r="AH10" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AF10" s="14" t="inlineStr">
+      <c r="AI10" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -15400,19 +16665,19 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AB11" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AC11" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AD11" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="AB11" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AC11" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AD11" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="AE11" s="10" t="inlineStr">
@@ -15421,6 +16686,21 @@
         </is>
       </c>
       <c r="AF11" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG11" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH11" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI11" s="10" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -15587,6 +16867,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG12" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH12" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI12" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -15749,6 +17044,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG13" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH13" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI13" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -15911,6 +17221,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG14" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH14" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI14" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -16055,20 +17380,35 @@
       </c>
       <c r="AC15" s="14" t="inlineStr">
         <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AD15" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AE15" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AF15" s="14" t="inlineStr">
+        <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AD15" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AE15" s="14" t="inlineStr">
+      <c r="AG15" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH15" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AF15" s="14" t="inlineStr">
+      <c r="AI15" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -16235,6 +17575,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG16" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH16" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI16" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -16372,27 +17727,42 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AB17" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AC17" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AD17" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AE17" s="14" t="inlineStr">
+      <c r="AB17" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AC17" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AD17" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AE17" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AF17" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG17" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH17" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AF17" s="14" t="inlineStr">
+      <c r="AI17" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -16559,6 +17929,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG18" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH18" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI18" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -16721,6 +18106,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH19" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -16883,6 +18283,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG20" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH20" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI20" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -17045,6 +18460,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG21" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH21" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI21" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -17207,6 +18637,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG22" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH22" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI22" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -17369,6 +18814,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG23" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH23" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI23" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -17531,6 +18991,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG24" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH24" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI24" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -17678,9 +19153,9 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AD25" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="AD25" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="AE25" s="10" t="inlineStr">
@@ -17689,6 +19164,21 @@
         </is>
       </c>
       <c r="AF25" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH25" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI25" s="10" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -17855,6 +19345,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG26" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH26" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI26" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -18017,6 +19522,21 @@
           <t>no human one2one orthologue</t>
         </is>
       </c>
+      <c r="AG27" s="14" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
+      <c r="AH27" s="14" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
+      <c r="AI27" s="14" t="inlineStr">
+        <is>
+          <t>no human one2one orthologue</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -18179,6 +19699,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG28" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH28" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI28" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -18341,6 +19876,21 @@
           <t>measured</t>
         </is>
       </c>
+      <c r="AG29" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH29" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI29" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -18478,19 +20028,19 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AB30" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AC30" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
-        </is>
-      </c>
-      <c r="AD30" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="AB30" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AC30" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
+        </is>
+      </c>
+      <c r="AD30" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="AE30" s="10" t="inlineStr">
@@ -18499,6 +20049,21 @@
         </is>
       </c>
       <c r="AF30" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH30" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI30" s="10" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
@@ -18645,9 +20210,9 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AC31" s="10" t="inlineStr">
-        <is>
-          <t>measured</t>
+      <c r="AC31" s="14" t="inlineStr">
+        <is>
+          <t>not in dataset annotation</t>
         </is>
       </c>
       <c r="AD31" s="10" t="inlineStr">
@@ -18655,12 +20220,27 @@
           <t>measured</t>
         </is>
       </c>
-      <c r="AE31" s="14" t="inlineStr">
+      <c r="AE31" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AF31" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH31" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
       </c>
-      <c r="AF31" s="14" t="inlineStr">
+      <c r="AI31" s="14" t="inlineStr">
         <is>
           <t>filtered (low expression)</t>
         </is>
@@ -18823,6 +20403,21 @@
         </is>
       </c>
       <c r="AF32" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AH32" s="10" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="AI32" s="10" t="inlineStr">
         <is>
           <t>measured</t>
         </is>
